--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.7%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.3%</t>
+          <t>-583.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1155,42 +1155,42 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.9%</t>
+          <t>143.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.0%</t>
+          <t>-322.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-67.3%</t>
+          <t>-66.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.1%</t>
+          <t>133.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>135.0%</t>
+          <t>135.4%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.168348744068675</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1357825831261859</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-0.9973597802270264</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.533497470678817</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.222420243577034</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1545176266079569</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.051431279735386</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.503948127295373</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.225996029668782</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1504347439260139</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.076960201651879</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.49414397126412</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.259648868177255</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1594133248449672</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.177373569568916</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.438378504998334</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.398734982796112</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1996760691990889</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.316459684187773</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.370298537720441</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.573859400182656</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2551706154061892</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.491584101574317</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.279779108036031</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.808311494197145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3561706179135813</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.491584101574317</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.272559943134435</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.912686225223592</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.4045927010981361</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.595958832600762</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.203262913744592</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.075199690922176</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.4684822975390133</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.693592263019449</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.145798645331936</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.201236484290465</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.5162032862572143</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.668340640209707</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.163643347646896</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.144164712394534</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4893842418124414</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.668340640209707</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.167633683333297</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.285836554118655</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5475282054008312</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.668340640209707</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.166158456434555</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.23624570969382</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.512638457466025</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.618749795784873</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.210966373254328</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.087327375221964</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4661222573239656</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.5875002050497</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.216664994048749</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.861482222502554</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3662051231999928</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.545573529462536</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.251400072437256</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.736903566164962</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3152345161088972</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.545573529462536</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.252539216993314</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.711866884596452</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.3025860693193856</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.5202444419118</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.270370443685863</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.639733709308571</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2679990949655964</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.5202444419118</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.2761041479245</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.576075471757756</v>
+        <v>-8.568367316698923</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2522730623391358</v>
+        <v>-0.2491898003156026</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.448878049302152</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.304561828061122</v>
+        <v>2.309186721096423</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.482616437772531</v>
+        <v>-8.474908282713699</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2247729300579535</v>
+        <v>-0.2216896680344207</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.448878049302152</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.294678346748215</v>
+        <v>2.299303239783516</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.4719632562191</v>
+        <v>-8.464255101160267</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2223462179359545</v>
+        <v>-0.2192629559124217</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.448878049302152</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.292843786248842</v>
+        <v>2.297468679284142</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.374056217542609</v>
+        <v>-8.366348062483777</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1834837174388193</v>
+        <v>-0.180400455415286</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.388600454500431</v>
+        <v>-1.380892299441596</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.333334921191714</v>
+        <v>2.337959814227015</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.350102676566651</v>
+        <v>-8.342394521507819</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1732337949029423</v>
+        <v>-0.1701505328794095</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.364646913524473</v>
+        <v>-1.356938758465638</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.348375551922782</v>
+        <v>2.353000444958083</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.086042738243854</v>
+        <v>-8.078334583185022</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08087013573557567</v>
+        <v>-0.07778687371204285</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.092878820142842</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.498176091790009</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.378963114739016</v>
+        <v>-7.371254959680184</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1991746800060588</v>
+        <v>0.2022579420295916</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.092878820142842</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.495389058129708</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.331070661313993</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.2186752852639091</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-1.052694521776651</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.519843261037264</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.167670790374631</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.283402054860411</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.889294650837289</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.617250004821638</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.017261566054688</v>
+        <v>-7.009553410995855</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3514901734262406</v>
+        <v>0.3545734354497734</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7388854265173482</v>
+        <v>-0.7311772714585135</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.715419968251455</v>
+        <v>2.720044861286756</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.867595175047173</v>
+        <v>-6.85988701998834</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4084645195162873</v>
+        <v>0.4115477815398205</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6459819352748123</v>
+        <v>-0.6382737802159776</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.768269852684018</v>
+        <v>2.772894745719318</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.735319701416286</v>
+        <v>-6.727611546357454</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3626354949757968</v>
+        <v>0.3657187569993297</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5137064616439256</v>
+        <v>-0.5059983065850909</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.748895922869704</v>
+        <v>2.753520815905005</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.563458485851384</v>
+        <v>-6.555750330792551</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4341950418893945</v>
+        <v>0.4372783039129273</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3418452460790228</v>
+        <v>-0.3341370910201881</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.854827712896283</v>
+        <v>2.859452605931583</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.478493819122065</v>
+        <v>-6.470785664063232</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4810872498047809</v>
+        <v>0.4841705118283137</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2568805793497032</v>
+        <v>-0.2491724242908685</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.918712854157533</v>
+        <v>2.923337747192834</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.584083808895169</v>
+        <v>-6.576375653836337</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3108753242963203</v>
+        <v>0.3139585863198535</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3624705691228076</v>
+        <v>-0.3547624140639729</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727382930694452</v>
+        <v>2.732007823729753</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.515849224269742</v>
+        <v>-6.508141069210909</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3867135000235775</v>
+        <v>0.3897967620471108</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3440552462502716</v>
+        <v>-0.3363470911914369</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.78697646629506</v>
+        <v>2.791601359330361</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.367909182862142</v>
+        <v>-6.36020102780331</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3292687079482102</v>
+        <v>0.3323519699717434</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.323734330341714</v>
+        <v>-0.3160261752828793</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.682548207201787</v>
+        <v>2.687173100237088</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.314939660608154</v>
+        <v>-6.307231505549321</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3417425305963278</v>
+        <v>0.3448257926198606</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2630566530288904</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.705615934300702</v>
+        <v>2.710240827336003</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.149151464647863</v>
+        <v>-6.141443309589031</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4010971968853507</v>
+        <v>0.4041804589088835</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2630566530288904</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.698655322205609</v>
+        <v>2.70328021524091</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.115788258169094</v>
+        <v>-6.108080103110262</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4289048338580015</v>
+        <v>0.4319880958815343</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2630566530288904</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713117676586752</v>
+        <v>2.717742569622053</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.007529121046573</v>
+        <v>-5.99982096598774</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4667406091662052</v>
+        <v>0.469823871189738</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2630566530288904</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.707649797045947</v>
+        <v>2.712274690081248</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.884237986229442</v>
+        <v>-5.876529831170609</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5135551571036343</v>
+        <v>0.5166384191271671</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1474736732705946</v>
+        <v>-0.1397655182117599</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779122571946802</v>
+        <v>2.783747464982103</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.831541119098151</v>
+        <v>-5.823832964039318</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5423348821934759</v>
+        <v>0.5454181442170092</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09477680613930345</v>
+        <v>-0.08706865108046874</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.818441670462903</v>
+        <v>2.823066563498203</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.587775677114706</v>
+        <v>-5.580067522055874</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356217673339044</v>
+        <v>0.6387050293574372</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09477680613930345</v>
+        <v>-0.08706865108046874</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814222378809953</v>
+        <v>2.818847271845254</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.498000004738234</v>
+        <v>-5.490291849679402</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6736563502045092</v>
+        <v>0.6767396122280425</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.02546920616615872</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853306359678555</v>
+        <v>2.857931252713856</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.248149610789159</v>
+        <v>-5.240441455730327</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7663385827678413</v>
+        <v>0.7694218447913741</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.02546920616615872</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846048434662257</v>
+        <v>2.850673327697558</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.072257518321727</v>
+        <v>-5.064549363262895</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8402945432754629</v>
+        <v>0.8433778052989958</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.02546920616615872</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.849647558182906</v>
+        <v>2.854272451218207</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.900811055299264</v>
+        <v>-4.893102900240431</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9222006345390019</v>
+        <v>0.925283896562535</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1382691017974697</v>
+        <v>0.1459772568563044</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.965842942050938</v>
+        <v>2.970467835086239</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.820788768190143</v>
+        <v>-4.81308061313131</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9532300269989473</v>
+        <v>0.9563132890224804</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2182913889065907</v>
+        <v>0.2259995439654254</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.012876791932707</v>
+        <v>3.017501684968008</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.757153025956208</v>
+        <v>-4.749444870897376</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9833791249468384</v>
+        <v>0.9864623869703713</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2819271311405252</v>
+        <v>0.2896352861993599</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.055753038327385</v>
+        <v>3.060377931362686</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.663455707739813</v>
+        <v>-4.655747552680981</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.002052311017192</v>
+        <v>1.005135573040725</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2819271311405252</v>
+        <v>0.2896352861993599</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.036947297111181</v>
+        <v>3.041572190146482</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.673958330805102</v>
+        <v>-4.66625017574627</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9995943384159538</v>
+        <v>1.002677600439487</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2714245080752363</v>
+        <v>0.279132663134071</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032388799896885</v>
+        <v>3.037013692932186</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.561472070136228</v>
+        <v>-4.553763915077395</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.048518156518324</v>
+        <v>1.051601418541857</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2714245080752363</v>
+        <v>0.279132663134071</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036318113731705</v>
+        <v>3.040943006767006</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.543758383258362</v>
+        <v>-4.53605022819953</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05628221518681</v>
+        <v>1.059365477210343</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2746058369721531</v>
+        <v>0.2823139920309878</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.038905494987195</v>
+        <v>3.043530388022496</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.420284111945344</v>
+        <v>-4.412575956886512</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.102669994932011</v>
+        <v>1.105753256955544</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2746058369721531</v>
+        <v>0.2823139920309878</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.035903566207188</v>
+        <v>3.040528459242489</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.200263313908334</v>
+        <v>-4.192555158849501</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.192257351157429</v>
+        <v>1.195340613180962</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4158256820401334</v>
+        <v>0.4235338370989681</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122214510258591</v>
+        <v>3.126839403293892</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.067395624845056</v>
+        <v>-4.059687469786224</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.261298609584564</v>
+        <v>1.264381871608097</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4158256820401334</v>
+        <v>0.4235338370989681</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138108693060414</v>
+        <v>3.142733586095715</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.947222541480557</v>
+        <v>-3.939514386421725</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.310513687370665</v>
+        <v>1.313596949394198</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5359987654046323</v>
+        <v>0.543706920463467</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211358387519415</v>
+        <v>3.215983280554716</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.81196918015058</v>
+        <v>-3.804261025091748</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.374703134464096</v>
+        <v>1.377786396487628</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6712521267346094</v>
+        <v>0.6789602817934441</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.302598506878842</v>
+        <v>3.307223399914142</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.871844007508273</v>
+        <v>-3.86413585244944</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336790694922444</v>
+        <v>1.339873956945977</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6113772993769173</v>
+        <v>0.619085454435752</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.252711101865652</v>
+        <v>3.257335994900953</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.752023776597435</v>
+        <v>-3.744315621538603</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.400007956520988</v>
+        <v>1.403091218544521</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6113772993769173</v>
+        <v>0.619085454435752</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268000271099861</v>
+        <v>3.272625164135162</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.754493483059241</v>
+        <v>-3.746785328000409</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.306664273258707</v>
+        <v>1.30974753528224</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6089075929151111</v>
+        <v>0.6166157479739458</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174162646545219</v>
+        <v>3.178787539580519</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.822863669383251</v>
+        <v>-3.815155514324418</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198578060214404</v>
+        <v>1.201661322237938</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6258914470101608</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.098989927452249</v>
+        <v>3.10361482048755</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.934735949009402</v>
+        <v>-3.927027793950569</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144265856995835</v>
+        <v>1.147349119019369</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6258914470101608</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.08942663608414</v>
+        <v>3.094051529119441</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.918761283523134</v>
+        <v>-3.911053128464301</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.11723024811437</v>
+        <v>1.120313510137903</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6258914470101608</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.056001161008167</v>
+        <v>3.060626054043468</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.743287023730665</v>
+        <v>-3.735578868671832</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.191987184023146</v>
+        <v>1.195070446046679</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6258914470101608</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.060568392999955</v>
+        <v>3.065193286035256</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.73536264914575</v>
+        <v>-3.727654494086918</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.170898962618318</v>
+        <v>1.173982224641851</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6258914470101608</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.036310421761162</v>
+        <v>3.040935314796463</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.729084446575901</v>
+        <v>-3.721376291517069</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.101948557047708</v>
+        <v>1.105031819071241</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.6321696495800098</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.968615656704522</v>
+        <v>2.973240549739822</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.669231827372178</v>
+        <v>-3.661523672313346</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.136061991161329</v>
+        <v>1.139145253184862</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.6321696495800098</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.978788043136654</v>
+        <v>2.983412936171955</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.582988364345801</v>
+        <v>-3.575280209286968</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165505646945741</v>
+        <v>1.168588908969274</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.6321696495800098</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.973734313710514</v>
+        <v>2.978359206745815</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.628295183744781</v>
+        <v>-3.620587028685948</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.139158694630674</v>
+        <v>1.142241956654207</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5836513315119443</v>
+        <v>0.591359486570779</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.941023991349501</v>
+        <v>2.945648884384802</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.657328288447082</v>
+        <v>-3.64962013338825</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.128097325782855</v>
+        <v>1.131180587806388</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5836513315119443</v>
+        <v>0.591359486570779</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.941575864382603</v>
+        <v>2.946200757417904</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.564517806996223</v>
+        <v>-3.556809651937391</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.094494210254565</v>
+        <v>1.097577472278097</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6764618129628036</v>
+        <v>0.6841699680216383</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.926534845144484</v>
+        <v>2.931159738179785</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.608907276325651</v>
+        <v>-3.601199121266818</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.078611898447394</v>
+        <v>1.081695160470927</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6320723436333759</v>
+        <v>0.6397804986922107</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.901774639471428</v>
+        <v>2.906399532506729</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.588403582440153</v>
+        <v>-3.580695427381321</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.081889084513316</v>
+        <v>1.084972346536849</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6525760375188733</v>
+        <v>0.660284192577708</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.90915256431445</v>
+        <v>2.913777457349751</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628327677022726</v>
+        <v>-3.620619521963893</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.071410742510954</v>
+        <v>1.074494004534488</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6525760375188733</v>
+        <v>0.660284192577708</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.914643860145117</v>
+        <v>2.919268753180418</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.656108074924079</v>
+        <v>-3.648399919865246</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.071795785118952</v>
+        <v>1.074879047142485</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6247956396175203</v>
+        <v>0.632503794676355</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.909472823172844</v>
+        <v>2.914097716208145</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.774488747654217</v>
+        <v>-3.766780592595385</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8627992360275503</v>
+        <v>0.8658824980510833</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.5652859425253788</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.707497831882912</v>
+        <v>2.712122724918212</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.883102826097548</v>
+        <v>-3.875394671038716</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9395032653694235</v>
+        <v>0.9425865273929563</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.5652859425253788</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.827647492602118</v>
+        <v>2.832272385637418</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.847693787849405</v>
+        <v>-3.839985632790573</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9681799067710035</v>
+        <v>0.9712631687945366</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.5652859425253788</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.842160518704441</v>
+        <v>2.846785411739741</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.856154956504867</v>
+        <v>-3.848446801446034</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9622148806511879</v>
+        <v>0.9652981426747207</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.549116618811083</v>
+        <v>0.5568247738699177</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834503258853533</v>
+        <v>2.839128151888833</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.6790386264697</v>
+        <v>-3.671330471410868</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.029790441510557</v>
+        <v>1.03287370353409</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.549116618811083</v>
+        <v>0.5568247738699177</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831232287698835</v>
+        <v>2.835857180734136</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.724130871303246</v>
+        <v>-3.716422716244414</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.012436935339051</v>
+        <v>1.015520197362584</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4872205756416932</v>
+        <v>0.4949287307005279</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794778053559114</v>
+        <v>2.799402946594415</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.544755450064478</v>
+        <v>-3.537047295005646</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.077974079140973</v>
+        <v>1.081057341164506</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6439973338124119</v>
+        <v>0.6517054888712466</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88263108376796</v>
+        <v>2.88725597680326</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.589769663585085</v>
+        <v>-3.582061508526252</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.04077584906432</v>
+        <v>1.043859111087853</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6136484384978073</v>
+        <v>0.621356593556642</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845229201910787</v>
+        <v>2.849854094946088</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.85677417385752</v>
+        <v>-3.849066018798688</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9396656072942917</v>
+        <v>0.9427488693178248</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4192854004548587</v>
+        <v>0.4269935555136934</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734302941423963</v>
+        <v>2.738927834459264</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.957971955294693</v>
+        <v>-3.95026380023586</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.898390416615924</v>
+        <v>0.901473678639457</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.3585847419683742</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692461575193273</v>
+        <v>2.697086468228574</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.95146098868038</v>
+        <v>-3.943752833621548</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8985947648159658</v>
+        <v>0.9016780268394988</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.3585847419683742</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.69006153674759</v>
+        <v>2.694686429782891</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.932422860973083</v>
+        <v>-3.92471470591425</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9027347351071295</v>
+        <v>0.9058179971306626</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.3004011306371797</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651676089157118</v>
+        <v>2.656300982192419</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.984938663247903</v>
+        <v>-3.97723050818907</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001022815831392</v>
+        <v>1.004106077854925</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.3004011306371797</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770970490791308</v>
+        <v>2.775595383826609</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.988346974682483</v>
+        <v>-3.98063881962365</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.000492820243694</v>
+        <v>1.003576082267227</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.332917699646557</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.791313761183068</v>
+        <v>2.795938654218369</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.968990838788636</v>
+        <v>-3.961282683729803</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014243804998158</v>
+        <v>1.017327067021691</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.332917699646557</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.797322291579994</v>
+        <v>2.801947184615295</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.821247868553634</v>
+        <v>-3.813539713494801</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9712912143693586</v>
+        <v>0.9743744763928917</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.5007250568814402</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795956927198123</v>
+        <v>2.800581820233425</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.905069089828332</v>
+        <v>-3.897360934769499</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9405563473909604</v>
+        <v>0.9436396094144934</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.5007250568814402</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798750548729604</v>
+        <v>2.803375441764905</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.898916383775547</v>
+        <v>-3.891208228716715</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9436797782037325</v>
+        <v>0.9467630402272655</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4991696078753898</v>
+        <v>0.5068777629342245</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.803104520752933</v>
+        <v>2.807729413788234</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.915725681926049</v>
+        <v>-3.908017526867216</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9360365356836422</v>
+        <v>0.9391197977071752</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4823603097248881</v>
+        <v>0.4900684647837228</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.792099418602743</v>
+        <v>2.796724311638044</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.853427683149927</v>
+        <v>-3.845719528091094</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027291288990912</v>
+        <v>1.030374551014445</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5276545739993301</v>
+        <v>0.5353627290581648</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.885611530964229</v>
+        <v>2.89023642399953</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.651637485484769</v>
+        <v>-3.643929330425936</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9102993697711022</v>
+        <v>0.9133826317946352</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7256727661684845</v>
+        <v>0.7333809212273192</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.806714447979849</v>
+        <v>2.811339341015149</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.702524198170964</v>
+        <v>-3.694816043112131</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9602349170187994</v>
+        <v>0.9633181790423324</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.67478605348229</v>
+        <v>0.6824942085411247</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846472652690307</v>
+        <v>2.851097545725608</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.615913455521156</v>
+        <v>-3.608205300462324</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009506950194766</v>
+        <v>1.012590212218299</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7534117846874483</v>
+        <v>0.761119939746283</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.908275827529446</v>
+        <v>2.912900720564747</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.676122753526441</v>
+        <v>-3.668414598467608</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9839592118173239</v>
+        <v>0.987042473840857</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.7009106417409985</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.870686229550947</v>
+        <v>2.875311122586247</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.626936104842089</v>
+        <v>-3.619227949783257</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002125489330993</v>
+        <v>1.005208751354526</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.7009106417409985</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.869177847590875</v>
+        <v>2.873802740626176</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.582562973203521</v>
+        <v>-3.574854818144688</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019737609421857</v>
+        <v>1.02282087144539</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.7452837733795671</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.895664594009453</v>
+        <v>2.900289487044753</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.605043324062406</v>
+        <v>-3.597335169003573</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005139263216893</v>
+        <v>1.008222525240426</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.7452837733795671</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.890058388148043</v>
+        <v>2.894683281183344</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.55738759350135</v>
+        <v>-3.549679438442517</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03058331246912</v>
+        <v>1.033666574492653</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.785231348881788</v>
+        <v>0.7929395039406227</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.925033583512481</v>
+        <v>2.929658476547782</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.456869435002595</v>
+        <v>-3.449161279943763</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075682949243347</v>
+        <v>1.07876621126688</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8857495073805426</v>
+        <v>0.8934576624393773</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.990236851986459</v>
+        <v>2.99486174502176</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.440964105570242</v>
+        <v>-3.43325595051141</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.06879975349216</v>
+        <v>1.071883015515693</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8066368466713036</v>
+        <v>0.8143450017301384</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929523928036788</v>
+        <v>2.934148821072089</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.396125703961844</v>
+        <v>-3.388417548903012</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090832816746148</v>
+        <v>1.093916078769681</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8111802796161731</v>
+        <v>0.8188884346750078</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936347690414338</v>
+        <v>2.940972583449639</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.415624160203853</v>
+        <v>-3.40791600514502</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087194373880423</v>
+        <v>1.090277635903956</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7630956383362688</v>
+        <v>0.7708037933951035</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.911657845277473</v>
+        <v>2.916282738312774</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.371421323117952</v>
+        <v>-3.36371316805912</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.11075511124262</v>
+        <v>1.113838373266153</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8072984754221693</v>
+        <v>0.815006630481004</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.944059150056851</v>
+        <v>2.948684043092151</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.378980988954999</v>
+        <v>-3.371272833896167</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106141245377049</v>
+        <v>1.109224507400582</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.8698100344908233</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.97535119293199</v>
+        <v>2.979976085967291</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.220689571415727</v>
+        <v>-3.212981416356894</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220705577575797</v>
+        <v>1.22378883959933</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.8698100344908233</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.026598958115029</v>
+        <v>3.03122385115033</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.013047567781251</v>
+        <v>-3.005339412722418</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.302203083623841</v>
+        <v>1.305286345647374</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.069743883066465</v>
+        <v>1.077452038125299</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.149624864889968</v>
+        <v>3.154249757925269</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.962015475058723</v>
+        <v>-2.95430731999989</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317564148951122</v>
+        <v>1.320647410974655</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.120775975788993</v>
+        <v>1.128484130847828</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175192348761755</v>
+        <v>3.179817241797056</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.896791293931517</v>
+        <v>-2.889083138872684</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.36084122549471</v>
+        <v>1.363924487518242</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.186000156916198</v>
+        <v>1.193708311975033</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.231514261530783</v>
+        <v>3.236139154566084</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.859364273860383</v>
+        <v>-2.851656118801551</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371773005822443</v>
+        <v>1.374856267845976</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19125169494538</v>
+        <v>1.198959850004215</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.230626156647573</v>
+        <v>3.235251049682874</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.858006288886838</v>
+        <v>-2.850298133828005</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.373572992143102</v>
+        <v>1.376656254166635</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.265589820483199</v>
+        <v>1.273297975542033</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.276485824301504</v>
+        <v>3.281110717336805</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.829593025786954</v>
+        <v>-2.821884870728121</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.545496068404266</v>
+        <v>1.548579330427799</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.20661425773677</v>
+        <v>1.214322412795605</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.401658257674858</v>
+        <v>3.406283150710159</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.754810764761941</v>
+        <v>-2.747102609703109</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.695521882032088</v>
+        <v>1.698605144055621</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.281396518761783</v>
+        <v>1.289104673820617</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.566640523507683</v>
+        <v>3.571265416542984</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.728726680498133</v>
+        <v>-2.721018525439301</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.69766349175147</v>
+        <v>1.700746753775003</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.281396518761783</v>
+        <v>1.289104673820617</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.558348499521542</v>
+        <v>3.562973392556843</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.640848767389013</v>
+        <v>-2.63314061233018</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.731007852578898</v>
+        <v>1.734091114602431</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.397322161185134</v>
+        <v>1.405030316243968</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626097080559332</v>
+        <v>3.630721973594632</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.63195630599573</v>
+        <v>-2.624248150936897</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.752119242863003</v>
+        <v>1.755202504886536</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.397322161185134</v>
+        <v>1.405030316243968</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.643651486286123</v>
+        <v>3.648276379321424</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.800432422965608</v>
+        <v>-2.792724267906775</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.676583843479636</v>
+        <v>1.679667105503168</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.369374325468553</v>
+        <v>1.377082480527388</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.618737832260758</v>
+        <v>3.623362725296059</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.354176230336168</v>
+        <v>-2.346468075277335</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.836356017719273</v>
+        <v>1.839439279742806</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.27465565579892</v>
+        <v>1.282363810857755</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.543176327646841</v>
+        <v>3.547801220682142</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.331455126653015</v>
+        <v>-2.323746971594183</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.836108481689439</v>
+        <v>1.839191743712972</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.27465565579892</v>
+        <v>1.282363810857755</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533840350143745</v>
+        <v>3.538465243179046</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.460656939947058</v>
+        <v>-2.452948784888225</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.943333882222991</v>
+        <v>1.946417144246524</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.145453842504878</v>
+        <v>1.153161997563713</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.615225388018489</v>
+        <v>3.61985028105379</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.486531338421083</v>
+        <v>-2.478823183362251</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.970061945327027</v>
+        <v>1.97314520735056</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.190365451216619</v>
+        <v>1.198073606275454</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67925017573918</v>
+        <v>3.683875068774481</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.47947664820591</v>
+        <v>-2.471768493147077</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.969559177402642</v>
+        <v>1.972642439426175</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.197420141431793</v>
+        <v>1.205128296490628</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.684783238893131</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.452525423879422</v>
+        <v>-2.444817268820589</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.990345820777979</v>
+        <v>1.993429082801511</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.212300487459512</v>
+        <v>1.220008642518347</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.703717600154504</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.474069651710209</v>
+        <v>-2.466361496651376</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.165831261790624</v>
+        <v>2.168914523814157</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.212300487459512</v>
+        <v>1.220008642518347</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.887820732299463</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.496477769515081</v>
+        <v>-2.488769614456249</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.148984709571668</v>
+        <v>2.152067971595201</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.212300487459512</v>
+        <v>1.220008642518347</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.879937427202456</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.524702005092681</v>
+        <v>-2.516993850033849</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.139749014890265</v>
+        <v>2.142832276913798</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.230277239910821</v>
+        <v>1.237985394969655</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.892777478222879</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.534142930981211</v>
+        <v>-2.526434775922379</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.1922263622567</v>
+        <v>2.195309624280233</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.352704357454212</v>
+        <v>1.360412512513047</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>4.022487466470761</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.623019562149685</v>
+        <v>-2.615311407090853</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.159566804334611</v>
+        <v>2.162650066358144</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>1.271535881344573</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.972052582314977</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.699349539750591</v>
+        <v>-2.691641384691759</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.127146626188024</v>
+        <v>2.130229888211558</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>1.271535881344573</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.970164395208752</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.793013484428132</v>
+        <v>-2.7853053293693</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.08450127791987</v>
+        <v>2.087584539943403</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.170163781608197</v>
+        <v>1.177871936667032</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.904161364969789</v>
+        <v>3.90878625800509</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.954581909955388</v>
+        <v>-2.946873754896555</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.01830791791912</v>
+        <v>2.021391179942653</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.043380857810317</v>
+        <v>1.051089012869152</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.826525620901214</v>
+        <v>3.831150513936515</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.062882571825507</v>
+        <v>-3.055174416766675</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.988061060036991</v>
+        <v>1.991144322060524</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.043380857810317</v>
+        <v>1.051089012869152</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.839599027767133</v>
+        <v>3.844223920802433</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.080686543546251</v>
+        <v>-3.072978388487419</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.972944668131634</v>
+        <v>1.976027930155166</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9728462349051163</v>
+        <v>0.9805543899639511</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.789283450806952</v>
+        <v>3.793908343842253</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.108587330655724</v>
+        <v>-3.100879175596892</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.960308394414846</v>
+        <v>1.963391656438379</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9382493107621815</v>
+        <v>0.9459574658210163</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.767049337448193</v>
+        <v>3.771674230483494</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.231113433358618</v>
+        <v>-3.223405278299786</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.908062397310887</v>
+        <v>1.91114565933442</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8157232080592877</v>
+        <v>0.8234313631181224</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.690298119803656</v>
+        <v>3.694923012838956</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.461627929544207</v>
+        <v>-3.453919774485374</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.882562558427156</v>
+        <v>1.885645820450689</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5852087118736989</v>
+        <v>0.5929168669325336</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.618695381682806</v>
+        <v>3.623320274718107</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.810373014768651</v>
+        <v>-3.802664859709818</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.883376243339225</v>
+        <v>1.886459505362758</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4841689130136358</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.693758328333314</v>
+        <v>3.698383221368615</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.964359432544791</v>
+        <v>-3.956651277485959</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.890761945374409</v>
+        <v>1.893845207397942</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4841689130136358</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.762738597478954</v>
+        <v>3.767363490514255</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.1689588674078</v>
+        <v>-4.161250712348967</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.794973373549326</v>
+        <v>1.798056635572859</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4841689130136358</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.748789799599075</v>
+        <v>3.753414692634376</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.421434021415524</v>
+        <v>-4.413725866356692</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.705853801001651</v>
+        <v>1.708937063025183</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4841689130136358</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.760660288654489</v>
+        <v>3.76528518168979</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.714329777894936</v>
+        <v>-4.706621622836104</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.589906032928829</v>
+        <v>1.592989294952362</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4841689130136358</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.761870823173433</v>
+        <v>3.766495716208734</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.900993906029744</v>
+        <v>-4.893285750970912</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.519362123902228</v>
+        <v>1.522445385925761</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4497217871302412</v>
+        <v>0.457429942189076</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.749949182906018</v>
+        <v>3.754574075941319</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.047014592943706</v>
+        <v>-5.039306437884874</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.456031701872832</v>
+        <v>1.459114963896365</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4406386953363843</v>
+        <v>0.448346850395219</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.739577180565893</v>
+        <v>3.744202073601195</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.138728602053291</v>
+        <v>-5.131020446994459</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.581550154928042</v>
+        <v>1.584633416951575</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4406386953363843</v>
+        <v>0.448346850395219</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.901781237264938</v>
+        <v>3.906406130300239</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.170380261113261</v>
+        <v>-5.162672106054428</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.563736129267869</v>
+        <v>1.566819391291402</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4354702380919441</v>
+        <v>0.4431783931507788</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.893526800882088</v>
+        <v>3.898151693917388</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.252315079382144</v>
+        <v>-5.244606924323311</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.541191619528806</v>
+        <v>1.54427488155234</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4255354925048639</v>
+        <v>0.4332436475636986</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.897795371098331</v>
+        <v>3.902420264133632</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.354291201630551</v>
+        <v>-5.346583046571719</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.509326809085346</v>
+        <v>1.512410071108879</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3235593702564563</v>
+        <v>0.331267525315291</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.845535336205189</v>
+        <v>3.85016022924049</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.24428491815333</v>
+        <v>-5.236576763094497</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.54548220972041</v>
+        <v>1.548565471743943</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3467639421737315</v>
+        <v>0.3544720972325662</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.851610966599729</v>
+        <v>3.85623585963503</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.101225342412404</v>
+        <v>-5.093517187353571</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.606956050738755</v>
+        <v>1.610039312762288</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3547773687637108</v>
+        <v>0.3624855238225455</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.860669033275691</v>
+        <v>3.865293926310992</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.799778616940566</v>
+        <v>-4.792070461881734</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.734795623810026</v>
+        <v>1.737878885833559</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6562240942355481</v>
+        <v>0.6639322492943828</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.04879795144133</v>
+        <v>4.05342284447663</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.82436886117575</v>
+        <v>-4.816660706116918</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.725930703868663</v>
+        <v>1.729013965892196</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6562240942355481</v>
+        <v>0.6639322492943828</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.04976912919404</v>
+        <v>4.05439402222934</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.77333048516923</v>
+        <v>-4.765622330110397</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.747188958651027</v>
+        <v>1.75027222067456</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6562240942355481</v>
+        <v>0.6639322492943828</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.050612033573795</v>
+        <v>4.055236926609096</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.732191190302599</v>
+        <v>-4.724483035243766</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.782682775471824</v>
+        <v>1.785766037495357</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6973633891021789</v>
+        <v>0.7050715441610136</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.09433370936792</v>
+        <v>4.09895860240322</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.635556278283959</v>
+        <v>-4.627848123225126</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.637520736403215</v>
+        <v>1.640603998426748</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7939983011208188</v>
+        <v>0.8017064561796535</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.968498652703038</v>
+        <v>3.973123545738339</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.566518267335491</v>
+        <v>-4.558810112276658</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.668637984856566</v>
+        <v>1.671721246880099</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8630363120692869</v>
+        <v>0.8707444671281216</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.013423503346083</v>
+        <v>4.018048396381384</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.402021933144529</v>
+        <v>-4.394313778085697</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.718863337609033</v>
+        <v>1.721946599632566</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.027532646260249</v>
+        <v>1.035240801319083</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.096548122936743</v>
+        <v>4.101173015972043</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.324923331602657</v>
+        <v>-4.317215176543824</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.748890488662212</v>
+        <v>1.751973750685745</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.027532646260249</v>
+        <v>1.035240801319083</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.095735833373173</v>
+        <v>4.100360726408473</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.335308526492546</v>
+        <v>-4.327600371433713</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.754605189831329</v>
+        <v>1.757688451854862</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.017147451370359</v>
+        <v>1.024855606429194</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.099373495564311</v>
+        <v>4.103998388599612</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.353896685214771</v>
+        <v>-4.346188530155938</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.818006932118864</v>
+        <v>1.821090194142397</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9985592926481339</v>
+        <v>1.006267447706969</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.159057606107401</v>
+        <v>4.163682499142702</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.354195231910807</v>
+        <v>-4.346487076851974</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.814756524258748</v>
+        <v>1.817839786282281</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.998260745952098</v>
+        <v>1.005968901010933</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.155747488908078</v>
+        <v>4.160372381943379</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.253372098220379</v>
+        <v>-4.245663943161547</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.859616672674311</v>
+        <v>1.862699934697844</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.010724961436452</v>
+        <v>1.018433116495287</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.167756913138081</v>
+        <v>4.172381806173383</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.062590737467971</v>
+        <v>-4.054882582409139</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.936058470453817</v>
+        <v>1.93914173247735</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.201506322188859</v>
+        <v>1.209214477247694</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.282354983068069</v>
+        <v>4.28697987610337</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.95562737961855</v>
+        <v>-3.947919224559717</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.958680659331182</v>
+        <v>1.961763921354716</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.259970930148661</v>
+        <v>1.267679085207496</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.297270593581547</v>
+        <v>4.301895486616848</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.900296791716788</v>
+        <v>-3.892588636657955</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.015779831103945</v>
+        <v>2.018863093127479</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.315301518050423</v>
+        <v>1.323009673109258</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.365435882934663</v>
+        <v>4.370060775969963</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.888242664803825</v>
+        <v>-3.880534509744992</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.014288049770569</v>
+        <v>2.017371311794101</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.327355644963386</v>
+        <v>1.33506380002222</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.366354926983878</v>
+        <v>4.370979820019179</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.929397784372046</v>
+        <v>-3.921689629313213</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.999706632127416</v>
+        <v>2.002789894150949</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.286200525395165</v>
+        <v>1.293908680453999</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.343542485427081</v>
+        <v>4.348167378462382</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.861349221680516</v>
+        <v>-3.853641066621683</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.03977708308191</v>
+        <v>2.042860345105443</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.354249088086695</v>
+        <v>1.361957243145529</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.397222648919882</v>
+        <v>4.401847541955182</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.092949614850017</v>
+        <v>-4.085241459791185</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.967339595987704</v>
+        <v>1.970422858011237</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.354249088086695</v>
+        <v>1.361957243145529</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.417425319093476</v>
+        <v>4.422050212128776</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.143001160379237</v>
+        <v>-4.135293005320404</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.930925213842898</v>
+        <v>1.934008475866431</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.354249088086695</v>
+        <v>1.361957243145529</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.401031555160358</v>
+        <v>4.405656448195659</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.318107992955682</v>
+        <v>-4.310399837896849</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.821134394405787</v>
+        <v>1.82421765642932</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.354249088086695</v>
+        <v>1.361957243145529</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.361283468753824</v>
+        <v>4.365908361789125</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.122007839525159</v>
+        <v>-4.114299684466326</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.906597074774936</v>
+        <v>1.909680336798469</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.550349241517218</v>
+        <v>1.558057396576052</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.485966179809078</v>
+        <v>4.490591072844379</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.968982447411875</v>
+        <v>-3.961274292353042</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.066978231193154</v>
+        <v>2.070061493216687</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.703374633630502</v>
+        <v>1.711082788689336</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.676952414649953</v>
+        <v>4.681577307685254</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.997289761285145</v>
+        <v>-3.989581606226312</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.243121530552139</v>
+        <v>2.246204792575671</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.703374633630502</v>
+        <v>1.711082788689336</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.864418639558245</v>
+        <v>4.869043532593547</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.163882986398667</v>
+        <v>-4.156174831339834</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.145887191860813</v>
+        <v>2.148970453884345</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.536781408516979</v>
+        <v>1.544489563575814</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.733865655844215</v>
+        <v>4.738490548879516</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.140847193037101</v>
+        <v>-4.133139037978268</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.158777911867157</v>
+        <v>2.161861173890689</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.536781408516979</v>
+        <v>1.544489563575814</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.737542058505933</v>
+        <v>4.742166951541233</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.111601212581404</v>
+        <v>-4.103893057522572</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.16809435917293</v>
+        <v>2.171177621196463</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.536781408516979</v>
+        <v>1.544489563575814</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.735160113629428</v>
+        <v>4.739785006664729</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.218526760459255</v>
+        <v>-4.210818605400423</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.122617379179425</v>
+        <v>2.125700641202958</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.429855860639128</v>
+        <v>1.437564015697963</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.668298024060352</v>
+        <v>4.672922917095653</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.363545318966504</v>
+        <v>-4.355837163907672</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.06603875791976</v>
+        <v>2.069122019943293</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.284837302131879</v>
+        <v>1.292545457190714</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.582715691099237</v>
+        <v>4.587340584134538</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.481887084751222</v>
+        <v>-4.474178929692389</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.118633290863626</v>
+        <v>2.121716552887159</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.295523340694769</v>
+        <v>1.303231495753604</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.689058553494724</v>
+        <v>4.693683446530025</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.533297507071929</v>
+        <v>-4.525589352013097</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.095854819061282</v>
+        <v>2.098938081084815</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.295523340694769</v>
+        <v>1.303231495753604</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.686844250620664</v>
+        <v>4.691469143655964</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.612716958279681</v>
+        <v>-4.605008803220849</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.06399016665247</v>
+        <v>2.067073428676003</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.295523340694769</v>
+        <v>1.303231495753604</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.686747378694952</v>
+        <v>4.691372271730254</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.708179956196899</v>
+        <v>-4.700471801138066</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.025798861043626</v>
+        <v>2.028882123067159</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.295523340694769</v>
+        <v>1.303231495753604</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.686741272252996</v>
+        <v>4.691366165288296</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.643804045346184</v>
+        <v>-4.636095890287351</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.049645621946523</v>
+        <v>2.052728883970055</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.359899251545485</v>
+        <v>1.367607406604319</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.723463215326035</v>
+        <v>4.728088108361336</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.699173207478378</v>
+        <v>-4.691465052419545</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.033231774841372</v>
+        <v>2.036315036864905</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.359899251545485</v>
+        <v>1.367607406604319</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.729197033073762</v>
+        <v>4.733821926109063</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.744610987309205</v>
+        <v>-4.736902832250372</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.014595026251973</v>
+        <v>2.017678288275507</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.317054260867325</v>
+        <v>1.32476241592616</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.703028402009799</v>
+        <v>4.707653295045099</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.656404153161627</v>
+        <v>-4.648695998102794</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.069752152761323</v>
+        <v>2.072835414784857</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.317054260867325</v>
+        <v>1.32476241592616</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.722902794860118</v>
+        <v>4.727527687895418</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.550369157956317</v>
+        <v>-4.542661002897485</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.095866851368175</v>
+        <v>2.098950113391708</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.317054260867325</v>
+        <v>1.32476241592616</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.706603495384845</v>
+        <v>4.711228388420146</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.367157494823222</v>
+        <v>-4.35944933976439</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.171582466085459</v>
+        <v>2.174665728108992</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.317054260867325</v>
+        <v>1.32476241592616</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.709034444848891</v>
+        <v>4.713659337884192</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.295436047809371</v>
+        <v>-4.287727892750539</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.166062230738889</v>
+        <v>2.169145492762422</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.388775707881176</v>
+        <v>1.39648386294001</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.717858498905091</v>
+        <v>4.722483391940392</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.273063022201665</v>
+        <v>-4.265354867142833</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.121927186903143</v>
+        <v>2.125010448926676</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.400031458994077</v>
+        <v>1.407739614052912</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.671527695494003</v>
+        <v>4.676152588529304</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.30607931811241</v>
+        <v>-4.298371163053577</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.2939188734242</v>
+        <v>2.297002135447733</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.330594082327326</v>
+        <v>1.33830223738616</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.815063474379308</v>
+        <v>4.819688367414608</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.294551682462801</v>
+        <v>-4.286843527403969</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.290451153512293</v>
+        <v>2.293534415535825</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.389594740528688</v>
+        <v>1.397302895587523</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.842385095128374</v>
+        <v>4.847009988163675</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.39189318380517</v>
+        <v>-4.384185028746337</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.255182665497133</v>
+        <v>2.258265927520667</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.3451745583632</v>
+        <v>1.352882713422034</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.81940109835087</v>
+        <v>4.82402599138617</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.477749213145136</v>
+        <v>-4.470041058086304</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.222091335953985</v>
+        <v>2.225174597977518</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.302798489137065</v>
+        <v>1.310506644195899</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.795226539008027</v>
+        <v>4.799851432043328</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.486586010561256</v>
+        <v>-4.478877855502423</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.200975818808039</v>
+        <v>2.204059080831573</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.295356316495714</v>
+        <v>1.303064471554549</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.773180437243719</v>
+        <v>4.777805330279019</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.577968573126714</v>
+        <v>-4.570260418067882</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.174587304826905</v>
+        <v>2.177670566850439</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.258791431776369</v>
+        <v>1.266499586835204</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.761406017457161</v>
+        <v>4.766030910492462</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.566261855139708</v>
+        <v>-4.558553700080876</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.281398249845975</v>
+        <v>2.284481511869508</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.270498149763376</v>
+        <v>1.278206304822211</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.870558306073632</v>
+        <v>4.875183199108933</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.466598351056046</v>
+        <v>-4.458890195997213</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.324295990210845</v>
+        <v>2.327379252234378</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.333685232967062</v>
+        <v>1.341393388025897</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.911502894727249</v>
+        <v>4.91612778776255</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.476914449222398</v>
+        <v>-4.469206294163565</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.533074384222362</v>
+        <v>2.536157646245895</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.333685232967062</v>
+        <v>1.341393388025897</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.124407728005307</v>
+        <v>5.129032621040608</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.476820481205025</v>
+        <v>-4.469112326146193</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.532290638341401</v>
+        <v>2.535373900364934</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.123808311725787</v>
+        <v>5.128433204761088</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.48403930540487</v>
+        <v>-4.476331150346037</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.523635094605817</v>
+        <v>2.52671835662935</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.118040297670142</v>
+        <v>5.122665190705442</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.483090882286831</v>
+        <v>-4.475382727227998</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.524014463853033</v>
+        <v>2.527097725876565</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.118040297670142</v>
+        <v>5.122665190705442</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.640159340542455</v>
+        <v>-4.632451185483623</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.473914688531875</v>
+        <v>2.476997950555408</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.130767905651233</v>
+        <v>5.135392798686534</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.634167093753644</v>
+        <v>-4.626458938694811</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.478257585671787</v>
+        <v>2.48134084769532</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.13271390407562</v>
+        <v>5.137338797110922</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.545609132622876</v>
+        <v>-4.537900977564044</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.507334906141863</v>
+        <v>2.510418168165396</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.126368040093389</v>
+        <v>5.130992933128691</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.527850055119802</v>
+        <v>-4.520141900060969</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.513747214582088</v>
+        <v>2.516830476605621</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.33405509431438</v>
+        <v>1.341763249373215</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.125676717532386</v>
+        <v>5.130301610567686</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.428219904070734</v>
+        <v>-4.420511749011902</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.566381460910302</v>
+        <v>2.569464722933835</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.433685245363448</v>
+        <v>1.441393400422283</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.198236994070413</v>
+        <v>5.202861887105714</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.477619412759745</v>
+        <v>-4.469911257700913</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.735775922933424</v>
+        <v>2.738859184956957</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.443944078795193</v>
+        <v>1.451652233854027</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.393546559628186</v>
+        <v>5.398171452663487</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.270934939117369</v>
+        <v>-4.263226784058537</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.805638385493237</v>
+        <v>2.808721647516769</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.650628552437568</v>
+        <v>1.658336707496403</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.504745916916473</v>
+        <v>5.509370809951775</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.305091834114895</v>
+        <v>-4.297383679056063</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.793977141148331</v>
+        <v>2.797060403171864</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.567044782896756</v>
+        <v>1.574752937955591</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.456597168846091</v>
+        <v>5.461222061881392</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.633842949272774</v>
+        <v>3.892802473902468</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.216867346367674</v>
+        <v>-4.215459379353895</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.182764050236887</v>
+        <v>3.183327237042398</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.567044782896756</v>
+        <v>1.574752937955591</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.810094282835759</v>
+        <v>5.814719175871059</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.4%</t>
+          <t>168.8%</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.1%</t>
+          <t>-583.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-64.5%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.1%</t>
+          <t>-322.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>130.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>128.9%</t>
         </is>
       </c>
     </row>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.436734329019526</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.908017526867216</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9391197977071752</v>
+        <v>0.8731708939588914</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4900684647837228</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.796724311638044</v>
+        <v>2.73077540788976</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.503069882816347</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.845719528091094</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.030374551014445</v>
+        <v>0.964425647266161</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5353627290581648</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.89023642399953</v>
+        <v>2.824287520251246</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.305361884530474</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.643929330425936</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9133826317946352</v>
+        <v>0.8474337280463513</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7333809212273192</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.811339341015149</v>
+        <v>2.745390437266865</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.375652116852649</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.694816043112131</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9633181790423324</v>
+        <v>0.8973692752940485</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6824942085411247</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.851097545725608</v>
+        <v>2.785148641977324</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.390279852968693</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.608205300462324</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.012590212218299</v>
+        <v>0.9466413084700152</v>
       </c>
       <c r="F1973" t="n">
         <v>0.761119939746283</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.912900720564747</v>
+        <v>2.846951816816463</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.388815833793364</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.668414598467608</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.987042473840857</v>
+        <v>0.9210935700925731</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7009106417409985</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.875311122586247</v>
+        <v>2.809362218837963</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.387307451833293</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.619227949783257</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.005208751354526</v>
+        <v>0.9392598476062421</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7009106417409985</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.873802740626176</v>
+        <v>2.807853836877892</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.387170319268729</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.574854818144688</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.02282087144539</v>
+        <v>0.9568719676971058</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7452837733795671</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.900289487044753</v>
+        <v>2.834340583296469</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.38156411340732</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.597335169003573</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.008222525240426</v>
+        <v>0.9422736214921423</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7452837733795671</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.894683281183344</v>
+        <v>2.82873437743506</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.387945870435124</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.549679438442517</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.033666574492653</v>
+        <v>0.9677176707443693</v>
       </c>
       <c r="F1978" t="n">
         <v>0.7929395039406227</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.929658476547782</v>
+        <v>2.863709572799498</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.392838243809849</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.449161279943763</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.07876621126688</v>
+        <v>1.012817307518596</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8934576624393773</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.99486174502176</v>
+        <v>2.928912841273476</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.379592916285721</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.43325595051141</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.071883015515693</v>
+        <v>1.005934111767409</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8143450017301384</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.934148821072089</v>
+        <v>2.868199917323805</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.38369061889635</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.388417548903012</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.093916078769681</v>
+        <v>1.027967175021397</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8188884346750078</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.940972583449639</v>
+        <v>2.875023679701355</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.387851558527428</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.40791600514502</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.090277635903956</v>
+        <v>1.024328732155672</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7708037933951035</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.916282738312774</v>
+        <v>2.85033383456449</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.393731161055265</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.36371316805912</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.113838373266153</v>
+        <v>1.047889469517869</v>
       </c>
       <c r="F1983" t="n">
         <v>0.815006630481004</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.948684043092151</v>
+        <v>2.882735139343867</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.392141161524513</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.371272833896167</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.109224507400582</v>
+        <v>1.043275603652298</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8698100344908233</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.979976085967291</v>
+        <v>2.914027182219007</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.443388926707552</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.212981416356894</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.22378883959933</v>
+        <v>1.157839935851046</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8698100344908233</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.03122385115033</v>
+        <v>2.965274947402047</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.441829631301805</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.005339412722418</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.305286345647374</v>
+        <v>1.23933744189909</v>
       </c>
       <c r="F1986" t="n">
         <v>1.077452038125299</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.154249757925269</v>
+        <v>3.088300854176985</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.436777859540075</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.95430731999989</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.320647410974655</v>
+        <v>1.254698507226371</v>
       </c>
       <c r="F1987" t="n">
         <v>1.128484130847828</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.179817241797056</v>
+        <v>3.113868338048772</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.45396526363278</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.889083138872684</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.363924487518242</v>
+        <v>1.297975583769958</v>
       </c>
       <c r="F1988" t="n">
         <v>1.193708311975033</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.236139154566084</v>
+        <v>3.1701902508178</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.449926235932061</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.851656118801551</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.374856267845976</v>
+        <v>1.308907364097692</v>
       </c>
       <c r="F1989" t="n">
         <v>1.198959850004215</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.235251049682874</v>
+        <v>3.16930214593459</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.451183028263301</v>
       </c>
       <c r="D1990" t="n">
         <v>-2.850298133828005</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.376656254166635</v>
+        <v>1.310707350418351</v>
       </c>
       <c r="F1990" t="n">
         <v>1.273297975542033</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.281110717336805</v>
+        <v>3.215161813588521</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.611740799284512</v>
       </c>
       <c r="D1991" t="n">
         <v>-2.821884870728121</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.548579330427799</v>
+        <v>1.482630426679515</v>
       </c>
       <c r="F1991" t="n">
         <v>1.214322412795605</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.406283150710159</v>
+        <v>3.340334246961875</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.731853708502329</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.747102609703109</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.698605144055621</v>
+        <v>1.632656240307337</v>
       </c>
       <c r="F1992" t="n">
         <v>1.289104673820617</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.571265416542984</v>
+        <v>3.5053165127947</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.723561684516188</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.721018525439301</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.700746753775003</v>
+        <v>1.63479785002672</v>
       </c>
       <c r="F1993" t="n">
         <v>1.289104673820617</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.562973392556843</v>
+        <v>3.497024488808559</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.721754880099967</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.63314061233018</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.734091114602431</v>
+        <v>1.668142210854147</v>
       </c>
       <c r="F1994" t="n">
         <v>1.405030316243968</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.630721973594632</v>
+        <v>3.564773069846348</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.739309285826759</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.624248150936897</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.755202504886536</v>
+        <v>1.689253601138252</v>
       </c>
       <c r="F1995" t="n">
         <v>1.405030316243968</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.648276379321424</v>
+        <v>3.58232747557314</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.731164333231343</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.792724267906775</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.679667105503168</v>
+        <v>1.613718201754885</v>
       </c>
       <c r="F1996" t="n">
         <v>1.377082480527388</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.623362725296059</v>
+        <v>3.557413821547776</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.712434030419205</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.346468075277335</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.839439279742806</v>
+        <v>1.773490375994522</v>
       </c>
       <c r="F1997" t="n">
         <v>1.282363810857755</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.547801220682142</v>
+        <v>3.481852316933858</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.703098052916109</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.323746971594183</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.839191743712972</v>
+        <v>1.773242839964688</v>
       </c>
       <c r="F1998" t="n">
         <v>1.282363810857755</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.538465243179046</v>
+        <v>3.472516339430762</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.862004178767278</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.452948784888225</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.946417144246524</v>
+        <v>1.88046824049824</v>
       </c>
       <c r="F1999" t="n">
         <v>1.153161997563713</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.61985028105379</v>
+        <v>3.553901377305506</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.899082001260925</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.478823183362251</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.97314520735056</v>
+        <v>1.907196303602276</v>
       </c>
       <c r="F2000" t="n">
         <v>1.198073606275454</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.683875068774481</v>
+        <v>3.617926165026197</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.89575735725047</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.471768493147077</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.972642439426175</v>
+        <v>1.906693535677891</v>
       </c>
       <c r="F2001" t="n">
         <v>1.205128296490628</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.684783238893131</v>
+        <v>3.618834335144847</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.905763510895211</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.444817268820589</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.993429082801511</v>
+        <v>1.927480179053227</v>
       </c>
       <c r="F2002" t="n">
         <v>1.220008642518347</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.703717600154504</v>
+        <v>3.63776869640622</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.089866643040171</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.466361496651376</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.168914523814157</v>
+        <v>2.102965620065873</v>
       </c>
       <c r="F2003" t="n">
         <v>1.220008642518347</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.887820732299463</v>
+        <v>3.821871828551179</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.081983337943164</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.488769614456249</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.152067971595201</v>
+        <v>2.086119067846917</v>
       </c>
       <c r="F2004" t="n">
         <v>1.220008642518347</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.879937427202456</v>
+        <v>3.813988523454173</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.084037337492802</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.516993850033849</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.142832276913798</v>
+        <v>2.076883373165514</v>
       </c>
       <c r="F2005" t="n">
         <v>1.237985394969655</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.892777478222879</v>
+        <v>3.826828574474595</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.140291055214649</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.526434775922379</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.195309624280233</v>
+        <v>2.129360720531949</v>
       </c>
       <c r="F2006" t="n">
         <v>1.360412512513047</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.022487466470761</v>
+        <v>3.956538562722477</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.14318214975995</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.615311407090853</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.162650066358144</v>
+        <v>2.096701162609861</v>
       </c>
       <c r="F2007" t="n">
         <v>1.271535881344573</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.972052582314977</v>
+        <v>3.906103678566694</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.141293962653725</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.691641384691759</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.130229888211558</v>
+        <v>2.064280984463274</v>
       </c>
       <c r="F2008" t="n">
         <v>1.271535881344573</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.970164395208752</v>
+        <v>3.904215491460469</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.136114192256587</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.7853053293693</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.087584539943403</v>
+        <v>2.02163563619512</v>
       </c>
       <c r="F2009" t="n">
         <v>1.177871936667032</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.90878625800509</v>
+        <v>3.842837354256806</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.134548202466739</v>
       </c>
       <c r="D2010" t="n">
         <v>-2.946873754896555</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.021391179942653</v>
+        <v>1.955442276194369</v>
       </c>
       <c r="F2010" t="n">
         <v>1.051089012869152</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.831150513936515</v>
+        <v>3.765201610188231</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.147621609332658</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.055174416766675</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.991144322060524</v>
+        <v>1.92519541831224</v>
       </c>
       <c r="F2011" t="n">
         <v>1.051089012869152</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.844223920802433</v>
+        <v>3.778275017054149</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.139626806115598</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.072978388487419</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.976027930155166</v>
+        <v>1.910079026406883</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9805543899639511</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.793908343842253</v>
+        <v>3.727959440093969</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.1381508472426</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.100879175596892</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.963391656438379</v>
+        <v>1.897442752690095</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9459574658210163</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.771674230483494</v>
+        <v>3.70572532673521</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.134915291219799</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.223405278299786</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.91114565933442</v>
+        <v>1.845196755586137</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8234313631181224</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.694923012838956</v>
+        <v>3.628974109090672</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.201621250810303</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.453919774485374</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.885645820450689</v>
+        <v>1.819696916702405</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5929168669325336</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.623320274718107</v>
+        <v>3.557371370969823</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.34193296981215</v>
       </c>
       <c r="D2016" t="n">
         <v>-3.802664859709818</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.886459505362758</v>
+        <v>1.820510601614474</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4841689130136358</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.698383221368615</v>
+        <v>3.632434317620331</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.410913238957789</v>
       </c>
       <c r="D2017" t="n">
         <v>-3.956651277485959</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.893845207397942</v>
+        <v>1.827896303649658</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4841689130136358</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.767363490514255</v>
+        <v>3.701414586765971</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.39696444107791</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.161250712348967</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.798056635572859</v>
+        <v>1.732107731824575</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4841689130136358</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.753414692634376</v>
+        <v>3.687465788886092</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.408834930133324</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.413725866356692</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.708937063025183</v>
+        <v>1.6429881592769</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4841689130136358</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.76528518168979</v>
+        <v>3.699336277941506</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.410045464652268</v>
       </c>
       <c r="D2020" t="n">
         <v>-4.706621622836104</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.592989294952362</v>
+        <v>1.527040391204078</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4841689130136358</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.766495716208734</v>
+        <v>3.70054681246045</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.414167206879589</v>
       </c>
       <c r="D2021" t="n">
         <v>-4.893285750970912</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.522445385925761</v>
+        <v>1.456496482177477</v>
       </c>
       <c r="F2021" t="n">
         <v>0.457429942189076</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.754574075941319</v>
+        <v>3.688625172193035</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.409245059615779</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.039306437884874</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.459114963896365</v>
+        <v>1.393166060148081</v>
       </c>
       <c r="F2022" t="n">
         <v>0.448346850395219</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.744202073601195</v>
+        <v>3.678253169852911</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.571449116314823</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.131020446994459</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.584633416951575</v>
+        <v>1.518684513203291</v>
       </c>
       <c r="F2023" t="n">
         <v>0.448346850395219</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.906406130300239</v>
+        <v>3.840457226551955</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.566295754278637</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.162672106054428</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.566819391291402</v>
+        <v>1.500870487543118</v>
       </c>
       <c r="F2024" t="n">
         <v>0.4431783931507788</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.898151693917388</v>
+        <v>3.832202790169104</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.576525171847128</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.244606924323311</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.54427488155234</v>
+        <v>1.478325977804056</v>
       </c>
       <c r="F2025" t="n">
         <v>0.4332436475636986</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.902420264133632</v>
+        <v>3.836471360385348</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.585450810303031</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.346583046571719</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.512410071108879</v>
+        <v>1.446461167360595</v>
       </c>
       <c r="F2026" t="n">
         <v>0.331267525315291</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.85016022924049</v>
+        <v>3.784211325492206</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.577603697547206</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.236576763094497</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.548565471743943</v>
+        <v>1.482616567995659</v>
       </c>
       <c r="F2027" t="n">
         <v>0.3544720972325662</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.85623585963503</v>
+        <v>3.790286955886746</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.58185370826918</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.093517187353571</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.610039312762288</v>
+        <v>1.544090409014004</v>
       </c>
       <c r="F2028" t="n">
         <v>0.3624855238225455</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.865293926310992</v>
+        <v>3.799345022562708</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.589114591151716</v>
       </c>
       <c r="D2029" t="n">
         <v>-4.792070461881734</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.737878885833559</v>
+        <v>1.671929982085275</v>
       </c>
       <c r="F2029" t="n">
         <v>0.6639322492943828</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.05342284447663</v>
+        <v>3.987473940728346</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.590085768904427</v>
       </c>
       <c r="D2030" t="n">
         <v>-4.816660706116918</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.729013965892196</v>
+        <v>1.663065062143912</v>
       </c>
       <c r="F2030" t="n">
         <v>0.6639322492943828</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.05439402222934</v>
+        <v>3.988445118481057</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.590928673284183</v>
       </c>
       <c r="D2031" t="n">
         <v>-4.765622330110397</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.75027222067456</v>
+        <v>1.684323316926276</v>
       </c>
       <c r="F2031" t="n">
         <v>0.6639322492943828</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.055236926609096</v>
+        <v>3.989288022860812</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.609966772158328</v>
       </c>
       <c r="D2032" t="n">
         <v>-4.724483035243766</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.785766037495357</v>
+        <v>1.719817133747073</v>
       </c>
       <c r="F2032" t="n">
         <v>0.7050715441610136</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.09895860240322</v>
+        <v>4.033009698654936</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.426150768282263</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.627848123225126</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.640603998426748</v>
+        <v>1.574655094678464</v>
       </c>
       <c r="F2033" t="n">
         <v>0.8017064561796535</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.973123545738339</v>
+        <v>3.907174641990055</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.429652812356227</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.558810112276658</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.671721246880099</v>
+        <v>1.605772343131815</v>
       </c>
       <c r="F2034" t="n">
         <v>0.8707444671281216</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.018048396381384</v>
+        <v>3.9520994926331</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.414079631432309</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.394313778085697</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.721946599632566</v>
+        <v>1.655997695884283</v>
       </c>
       <c r="F2035" t="n">
         <v>1.035240801319083</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.101173015972043</v>
+        <v>4.03522411222376</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.413267341868739</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.317215176543824</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.751973750685745</v>
+        <v>1.686024846937461</v>
       </c>
       <c r="F2036" t="n">
         <v>1.035240801319083</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.100360726408473</v>
+        <v>4.034411822660189</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.423136120993811</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.327600371433713</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.757688451854862</v>
+        <v>1.691739548106578</v>
       </c>
       <c r="F2037" t="n">
         <v>1.024855606429194</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.103998388599612</v>
+        <v>4.038049484851328</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.493973126770237</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.346188530155938</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.821090194142397</v>
+        <v>1.755141290394113</v>
       </c>
       <c r="F2038" t="n">
         <v>1.006267447706969</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.163682499142702</v>
+        <v>4.097733595394418</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.490842137588535</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.346487076851974</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.817839786282281</v>
+        <v>1.751890882533997</v>
       </c>
       <c r="F2039" t="n">
         <v>1.005968901010933</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.160372381943379</v>
+        <v>4.094423478195095</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.495373032527926</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.245663943161547</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.862699934697844</v>
+        <v>1.79675103094956</v>
       </c>
       <c r="F2040" t="n">
         <v>1.018433116495287</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.172381806173383</v>
+        <v>4.106432902425099</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.49550228600647</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.054882582409139</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.93914173247735</v>
+        <v>1.873192828729066</v>
       </c>
       <c r="F2041" t="n">
         <v>1.209214477247694</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.28697987610337</v>
+        <v>4.221030972355086</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.475339131744066</v>
       </c>
       <c r="D2042" t="n">
         <v>-3.947919224559717</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.961763921354716</v>
+        <v>1.895815017606431</v>
       </c>
       <c r="F2042" t="n">
         <v>1.267679085207496</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.301895486616848</v>
+        <v>4.235946582868564</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.510306068356125</v>
       </c>
       <c r="D2043" t="n">
         <v>-3.892588636657955</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.018863093127479</v>
+        <v>1.952914189379195</v>
       </c>
       <c r="F2043" t="n">
         <v>1.323009673109258</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.370060775969963</v>
+        <v>4.30411187222168</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.503992636257562</v>
       </c>
       <c r="D2044" t="n">
         <v>-3.880534509744992</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017371311794101</v>
+        <v>1.951422408045818</v>
       </c>
       <c r="F2044" t="n">
         <v>1.33506380002222</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.370979820019179</v>
+        <v>4.305030916270895</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.505873266441698</v>
       </c>
       <c r="D2045" t="n">
         <v>-3.921689629313213</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.002789894150949</v>
+        <v>1.936840990402665</v>
       </c>
       <c r="F2045" t="n">
         <v>1.293908680453999</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.348167378462382</v>
+        <v>4.282218474714099</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.518724292319581</v>
       </c>
       <c r="D2046" t="n">
         <v>-3.853641066621683</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.042860345105443</v>
+        <v>1.976911441357159</v>
       </c>
       <c r="F2046" t="n">
         <v>1.361957243145529</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.401847541955182</v>
+        <v>4.335898638206898</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.538926962493175</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.085241459791185</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970422858011237</v>
+        <v>1.904473954262953</v>
       </c>
       <c r="F2047" t="n">
         <v>1.361957243145529</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.422050212128776</v>
+        <v>4.356101308380492</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.522533198560057</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.135293005320404</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934008475866431</v>
+        <v>1.868059572118147</v>
       </c>
       <c r="F2048" t="n">
         <v>1.361957243145529</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.405656448195659</v>
+        <v>4.339707544447375</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.482785112153524</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.310399837896849</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.82421765642932</v>
+        <v>1.758268752681036</v>
       </c>
       <c r="F2049" t="n">
         <v>1.361957243145529</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.365908361789125</v>
+        <v>4.299959458040841</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.489807731150464</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.114299684466326</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.909680336798469</v>
+        <v>1.843731433050185</v>
       </c>
       <c r="F2050" t="n">
         <v>1.558057396576052</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.490591072844379</v>
+        <v>4.424642169096095</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.588978730723368</v>
       </c>
       <c r="D2051" t="n">
         <v>-3.961274292353042</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070061493216687</v>
+        <v>2.004112589468403</v>
       </c>
       <c r="F2051" t="n">
         <v>1.711082788689336</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.681577307685254</v>
+        <v>4.61562840393697</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.776444955631661</v>
       </c>
       <c r="D2052" t="n">
         <v>-3.989581606226312</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246204792575671</v>
+        <v>2.180255888827388</v>
       </c>
       <c r="F2052" t="n">
         <v>1.711082788689336</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.869043532593547</v>
+        <v>4.803094628845263</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.745847906985743</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.156174831339834</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.148970453884345</v>
+        <v>2.083021550136062</v>
       </c>
       <c r="F2053" t="n">
         <v>1.544489563575814</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.738490548879516</v>
+        <v>4.672541645131232</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.749524309647461</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.133139037978268</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.161861173890689</v>
+        <v>2.095912270142406</v>
       </c>
       <c r="F2054" t="n">
         <v>1.544489563575814</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.742166951541233</v>
+        <v>4.67621804779295</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.747142364770956</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.103893057522572</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171177621196463</v>
+        <v>2.105228717448179</v>
       </c>
       <c r="F2055" t="n">
         <v>1.544489563575814</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.739785006664729</v>
+        <v>4.673836102916445</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.744435603928591</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.210818605400423</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.125700641202958</v>
+        <v>2.059751737454674</v>
       </c>
       <c r="F2056" t="n">
         <v>1.437564015697963</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.672922917095653</v>
+        <v>4.606974013347369</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.745864406071826</v>
       </c>
       <c r="D2057" t="n">
         <v>-4.355837163907672</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069122019943293</v>
+        <v>2.003173116195009</v>
       </c>
       <c r="F2057" t="n">
         <v>1.292545457190714</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.587340584134538</v>
+        <v>4.521391680386254</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.845795645329579</v>
       </c>
       <c r="D2058" t="n">
         <v>-4.474178929692389</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.121716552887159</v>
+        <v>2.055767649138875</v>
       </c>
       <c r="F2058" t="n">
         <v>1.303231495753604</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.693683446530025</v>
+        <v>4.627734542781742</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.843581342455518</v>
       </c>
       <c r="D2059" t="n">
         <v>-4.525589352013097</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.098938081084815</v>
+        <v>2.032989177336531</v>
       </c>
       <c r="F2059" t="n">
         <v>1.303231495753604</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.691469143655964</v>
+        <v>4.62552023990768</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.843484470529807</v>
       </c>
       <c r="D2060" t="n">
         <v>-4.605008803220849</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067073428676003</v>
+        <v>2.001124524927719</v>
       </c>
       <c r="F2060" t="n">
         <v>1.303231495753604</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.691372271730254</v>
+        <v>4.62542336798197</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.84347836408785</v>
       </c>
       <c r="D2061" t="n">
         <v>-4.700471801138066</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.028882123067159</v>
+        <v>1.962933219318876</v>
       </c>
       <c r="F2061" t="n">
         <v>1.303231495753604</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.691366165288296</v>
+        <v>4.625417261540012</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217997</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.84157476065046</v>
       </c>
       <c r="D2062" t="n">
         <v>-4.636095890287351</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.052728883970055</v>
+        <v>1.986779980221772</v>
       </c>
       <c r="F2062" t="n">
         <v>1.367607406604319</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.728088108361336</v>
+        <v>4.662139204613053</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.847308578398187</v>
       </c>
       <c r="D2063" t="n">
         <v>-4.691465052419545</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036315036864905</v>
+        <v>1.970366133116621</v>
       </c>
       <c r="F2063" t="n">
         <v>1.367607406604319</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.733821926109063</v>
+        <v>4.667873022360779</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.84684694174112</v>
       </c>
       <c r="D2064" t="n">
         <v>-4.736902832250372</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.017678288275507</v>
+        <v>1.951729384527223</v>
       </c>
       <c r="F2064" t="n">
         <v>1.32476241592616</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.707653295045099</v>
+        <v>4.641704391296815</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.866721334591438</v>
       </c>
       <c r="D2065" t="n">
         <v>-4.648695998102794</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.072835414784857</v>
+        <v>2.006886511036573</v>
       </c>
       <c r="F2065" t="n">
         <v>1.32476241592616</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.727527687895418</v>
+        <v>4.661578784147134</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.850422035116166</v>
       </c>
       <c r="D2066" t="n">
         <v>-4.542661002897485</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.098950113391708</v>
+        <v>2.033001209643424</v>
       </c>
       <c r="F2066" t="n">
         <v>1.32476241592616</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.711228388420146</v>
+        <v>4.645279484671862</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.852852984580212</v>
       </c>
       <c r="D2067" t="n">
         <v>-4.35944933976439</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.174665728108992</v>
+        <v>2.108716824360708</v>
       </c>
       <c r="F2067" t="n">
         <v>1.32476241592616</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.713659337884192</v>
+        <v>4.647710434135908</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.818644170428102</v>
       </c>
       <c r="D2068" t="n">
         <v>-4.287727892750539</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.169145492762422</v>
+        <v>2.103196589014138</v>
       </c>
       <c r="F2068" t="n">
         <v>1.39648386294001</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.722483391940392</v>
+        <v>4.656534488192109</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.765559916349273</v>
       </c>
       <c r="D2069" t="n">
         <v>-4.265354867142833</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.125010448926676</v>
+        <v>2.059061545178392</v>
       </c>
       <c r="F2069" t="n">
         <v>1.407739614052912</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.676152588529304</v>
+        <v>4.610203684781021</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>3.950758121234629</v>
       </c>
       <c r="D2070" t="n">
         <v>-4.298371163053577</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.297002135447733</v>
+        <v>2.23105323169945</v>
       </c>
       <c r="F2070" t="n">
         <v>1.33830223738616</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.819688367414608</v>
+        <v>4.753739463666325</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.942679347062878</v>
       </c>
       <c r="D2071" t="n">
         <v>-4.286843527403969</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.293534415535825</v>
+        <v>2.227585511787542</v>
       </c>
       <c r="F2071" t="n">
         <v>1.397302895587523</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.847009988163675</v>
+        <v>4.781061084415392</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.946347459584667</v>
       </c>
       <c r="D2072" t="n">
         <v>-4.384185028746337</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258265927520667</v>
+        <v>2.192317023772384</v>
       </c>
       <c r="F2072" t="n">
         <v>1.352882713422034</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.82402599138617</v>
+        <v>4.758077087637887</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.947598541777505</v>
       </c>
       <c r="D2073" t="n">
         <v>-4.470041058086304</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.225174597977518</v>
+        <v>2.159225694229235</v>
       </c>
       <c r="F2073" t="n">
         <v>1.310506644195899</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.799851432043328</v>
+        <v>4.733902528295045</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.930017743598007</v>
       </c>
       <c r="D2074" t="n">
         <v>-4.478877855502423</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.204059080831573</v>
+        <v>2.13811017708329</v>
       </c>
       <c r="F2074" t="n">
         <v>1.303064471554549</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.777805330279019</v>
+        <v>4.711856426530736</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.940182254643056</v>
       </c>
       <c r="D2075" t="n">
         <v>-4.570260418067882</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.177670566850439</v>
+        <v>2.111721663102156</v>
       </c>
       <c r="F2075" t="n">
         <v>1.266499586835204</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.766030910492462</v>
+        <v>4.700082006744179</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.042310512467324</v>
       </c>
       <c r="D2076" t="n">
         <v>-4.558553700080876</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.284481511869508</v>
+        <v>2.218532608121226</v>
       </c>
       <c r="F2076" t="n">
         <v>1.278206304822211</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.875183199108933</v>
+        <v>4.809234295360651</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.045342851198729</v>
       </c>
       <c r="D2077" t="n">
         <v>-4.458890195997213</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.327379252234378</v>
+        <v>2.261430348486096</v>
       </c>
       <c r="F2077" t="n">
         <v>1.341393388025897</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.91612778776255</v>
+        <v>4.850178884014268</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452568</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.258247684476787</v>
       </c>
       <c r="D2078" t="n">
         <v>-4.469206294163565</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.536157646245895</v>
+        <v>2.470208742497613</v>
       </c>
       <c r="F2078" t="n">
         <v>1.341393388025897</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.129032621040608</v>
+        <v>5.063083717292326</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.257426351388877</v>
       </c>
       <c r="D2079" t="n">
         <v>-4.469112326146193</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.535373900364934</v>
+        <v>2.469424996616651</v>
       </c>
       <c r="F2079" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.128433204761088</v>
+        <v>5.062484301012806</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.251658337333231</v>
       </c>
       <c r="D2080" t="n">
         <v>-4.476331150346037</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.52671835662935</v>
+        <v>2.460769452881068</v>
       </c>
       <c r="F2080" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.122665190705442</v>
+        <v>5.05671628695716</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.251658337333231</v>
       </c>
       <c r="D2081" t="n">
         <v>-4.475382727227998</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.527097725876565</v>
+        <v>2.461148822128283</v>
       </c>
       <c r="F2081" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.122665190705442</v>
+        <v>5.05671628695716</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.264385945314323</v>
       </c>
       <c r="D2082" t="n">
         <v>-4.632451185483623</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.476997950555408</v>
+        <v>2.411049046807126</v>
       </c>
       <c r="F2082" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.135392798686534</v>
+        <v>5.069443894938252</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.26633194373871</v>
       </c>
       <c r="D2083" t="n">
         <v>-4.626458938694811</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.48134084769532</v>
+        <v>2.415391943947038</v>
       </c>
       <c r="F2083" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.137338797110922</v>
+        <v>5.07138989336264</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.259986079756479</v>
       </c>
       <c r="D2084" t="n">
         <v>-4.537900977564044</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.510418168165396</v>
+        <v>2.444469264417114</v>
       </c>
       <c r="F2084" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.130992933128691</v>
+        <v>5.065044029380409</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.259294757195475</v>
       </c>
       <c r="D2085" t="n">
         <v>-4.520141900060969</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.516830476605621</v>
+        <v>2.450881572857339</v>
       </c>
       <c r="F2085" t="n">
         <v>1.341763249373215</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.130301610567686</v>
+        <v>5.064352706819404</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.272076943104062</v>
       </c>
       <c r="D2086" t="n">
         <v>-4.420511749011902</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.569464722933835</v>
+        <v>2.503515819185553</v>
       </c>
       <c r="F2086" t="n">
         <v>1.441393400422283</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.202861887105714</v>
+        <v>5.136912983357432</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.461231208602788</v>
       </c>
       <c r="D2087" t="n">
         <v>-4.469911257700913</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.738859184956957</v>
+        <v>2.672910281208675</v>
       </c>
       <c r="F2087" t="n">
         <v>1.451652233854027</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.398171452663487</v>
+        <v>5.332222548915205</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.44841988170565</v>
       </c>
       <c r="D2088" t="n">
         <v>-4.263226784058537</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.808721647516769</v>
+        <v>2.742772743768487</v>
       </c>
       <c r="F2088" t="n">
         <v>1.658336707496403</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.509370809951775</v>
+        <v>5.443421906203493</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.450421395359755</v>
       </c>
       <c r="D2089" t="n">
         <v>-4.297383679056063</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.797060403171864</v>
+        <v>2.731111499423582</v>
       </c>
       <c r="F2089" t="n">
         <v>1.574752937955591</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.461222061881392</v>
+        <v>5.39527315813311</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.892802473902468</v>
+        <v>3.879864134253824</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.803918509349423</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.215459379353895</v>
+        <v>-4.216784726364907</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.183327237042398</v>
+        <v>3.116848194489712</v>
       </c>
       <c r="F2090" t="n">
         <v>1.574752937955591</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.814719175871059</v>
+        <v>5.748770272122777</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>168.8%</t>
+          <t>175.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.3%</t>
+          <t>-586.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-64.5%</t>
+          <t>-59.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>143.7%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.2%</t>
+          <t>-322.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-68.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.5%</t>
+          <t>132.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>134.3%</t>
         </is>
       </c>
     </row>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.168348744068675</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1357825831261859</v>
+        <v>-0.1388658451497196</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9973597802270264</v>
+        <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.533497470678817</v>
+        <v>2.528872577643516</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.222420243577034</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1545176266079569</v>
+        <v>-0.1576008886314906</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.051431279735386</v>
+        <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.503948127295373</v>
+        <v>2.499323234260073</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.225996029668782</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1504347439260139</v>
+        <v>-0.1535180059495476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.076960201651879</v>
+        <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.49414397126412</v>
+        <v>2.489519078228819</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.259648868177255</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1594133248449672</v>
+        <v>-0.1624965868685009</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.177373569568916</v>
+        <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.438378504998334</v>
+        <v>2.433753611963033</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.398734982796112</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1996760691990889</v>
+        <v>-0.2027593312226226</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.316459684187773</v>
+        <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.370298537720441</v>
+        <v>2.36567364468514</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.573859400182656</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2551706154061892</v>
+        <v>-0.2582538774297229</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.491584101574317</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.279779108036031</v>
+        <v>2.275154215000731</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.808311494197145</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3561706179135813</v>
+        <v>-0.359253879937115</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.491584101574317</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.272559943134435</v>
+        <v>2.267935050099135</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.912686225223592</v>
+        <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4045927010981361</v>
+        <v>-0.4076759631216698</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.595958832600762</v>
+        <v>-1.603666987659597</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.203262913744592</v>
+        <v>2.198638020709291</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.075199690922176</v>
+        <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4684822975390133</v>
+        <v>-0.471565559562547</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.693592263019449</v>
+        <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.145798645331936</v>
+        <v>2.141173752296635</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.201236484290465</v>
+        <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5162032862572143</v>
+        <v>-0.5192865482807481</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.668340640209707</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.163643347646896</v>
+        <v>2.159018454611595</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.144164712394534</v>
+        <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4893842418124414</v>
+        <v>-0.4924675038359752</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.668340640209707</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.167633683333297</v>
+        <v>2.163008790297996</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.285836554118655</v>
+        <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5475282054008312</v>
+        <v>-0.550611467424365</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.668340640209707</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.166158456434555</v>
+        <v>2.161533563399254</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.23624570969382</v>
+        <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.512638457466025</v>
+        <v>-0.5157217194895587</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.618749795784873</v>
+        <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.210966373254328</v>
+        <v>2.206341480219027</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.087327375221964</v>
+        <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4661222573239656</v>
+        <v>-0.4692055193474993</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.5875002050497</v>
+        <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.216664994048749</v>
+        <v>2.212040101013448</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.861482222502554</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3662051231999928</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.545573529462536</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.251400072437256</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.736903566164962</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3152345161088972</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.545573529462536</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.252539216993314</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.711866884596452</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3025860693193856</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.5202444419118</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.270370443685863</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.639733709308571</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2679990949655964</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.5202444419118</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.2761041479245</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.568367316698923</v>
+        <v>-8.576075471757756</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2491898003156026</v>
+        <v>-0.2522730623391358</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.448878049302152</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.309186721096423</v>
+        <v>2.304561828061122</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.474908282713699</v>
+        <v>-8.482616437772531</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2216896680344207</v>
+        <v>-0.2247729300579535</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.448878049302152</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.299303239783516</v>
+        <v>2.294678346748215</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.464255101160267</v>
+        <v>-8.4719632562191</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2192629559124217</v>
+        <v>-0.2223462179359545</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.448878049302152</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.297468679284142</v>
+        <v>2.292843786248842</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.366348062483777</v>
+        <v>-8.374056217542609</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.180400455415286</v>
+        <v>-0.1834837174388193</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.380892299441596</v>
+        <v>-1.388600454500431</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.337959814227015</v>
+        <v>2.333334921191714</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.342394521507819</v>
+        <v>-8.350102676566651</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1701505328794095</v>
+        <v>-0.1732337949029423</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.356938758465638</v>
+        <v>-1.364646913524473</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.353000444958083</v>
+        <v>2.348375551922782</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.078334583185022</v>
+        <v>-8.086042738243854</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.07778687371204285</v>
+        <v>-0.08087013573557567</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.092878820142842</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.498176091790009</v>
+        <v>2.493551198754708</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.371254959680184</v>
+        <v>-7.378963114739016</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2022579420295916</v>
+        <v>0.1991746800060588</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.092878820142842</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.495389058129708</v>
+        <v>2.490764165094407</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.331070661313993</v>
+        <v>-7.338778816372826</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2186752852639091</v>
+        <v>0.2155920232403763</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.052694521776651</v>
+        <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.519843261037264</v>
+        <v>2.515218368001963</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.167670790374631</v>
+        <v>-7.175378945433463</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.283402054860411</v>
+        <v>0.2803187928368782</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.889294650837289</v>
+        <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.617250004821638</v>
+        <v>2.612625111786337</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.009553410995855</v>
+        <v>-7.017261566054688</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3545734354497734</v>
+        <v>0.3514901734262406</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7311772714585135</v>
+        <v>-0.7388854265173482</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.720044861286756</v>
+        <v>2.715419968251455</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.85988701998834</v>
+        <v>-6.867595175047173</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4115477815398205</v>
+        <v>0.4084645195162873</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6382737802159776</v>
+        <v>-0.6459819352748123</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.772894745719318</v>
+        <v>2.768269852684018</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.727611546357454</v>
+        <v>-6.735319701416286</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3657187569993297</v>
+        <v>0.3626354949757968</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5059983065850909</v>
+        <v>-0.5137064616439256</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.753520815905005</v>
+        <v>2.748895922869704</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.555750330792551</v>
+        <v>-6.563458485851384</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4372783039129273</v>
+        <v>0.4341950418893945</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3341370910201881</v>
+        <v>-0.3418452460790228</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.859452605931583</v>
+        <v>2.854827712896283</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.470785664063232</v>
+        <v>-6.478493819122065</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4841705118283137</v>
+        <v>0.4810872498047809</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2491724242908685</v>
+        <v>-0.2568805793497032</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.923337747192834</v>
+        <v>2.918712854157533</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.576375653836337</v>
+        <v>-6.584083808895169</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3139585863198535</v>
+        <v>0.3108753242963203</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3547624140639729</v>
+        <v>-0.3624705691228076</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.732007823729753</v>
+        <v>2.727382930694452</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.508141069210909</v>
+        <v>-6.515849224269742</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3897967620471108</v>
+        <v>0.3867135000235775</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3363470911914369</v>
+        <v>-0.3440552462502716</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.791601359330361</v>
+        <v>2.78697646629506</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.36020102780331</v>
+        <v>-6.367909182862142</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3323519699717434</v>
+        <v>0.3292687079482102</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3160261752828793</v>
+        <v>-0.323734330341714</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.687173100237088</v>
+        <v>2.682548207201787</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.307231505549321</v>
+        <v>-6.314939660608154</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3448257926198606</v>
+        <v>0.3417425305963278</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2630566530288904</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.710240827336003</v>
+        <v>2.705615934300702</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.141443309589031</v>
+        <v>-6.149151464647863</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4041804589088835</v>
+        <v>0.4010971968853507</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2630566530288904</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.70328021524091</v>
+        <v>2.698655322205609</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.108080103110262</v>
+        <v>-6.115788258169094</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4319880958815343</v>
+        <v>0.4289048338580015</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2630566530288904</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.717742569622053</v>
+        <v>2.713117676586752</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.99982096598774</v>
+        <v>-6.007529121046573</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.469823871189738</v>
+        <v>0.4667406091662052</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2630566530288904</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.712274690081248</v>
+        <v>2.707649797045947</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.876529831170609</v>
+        <v>-5.884237986229442</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5166384191271671</v>
+        <v>0.5135551571036343</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1397655182117599</v>
+        <v>-0.1474736732705946</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.783747464982103</v>
+        <v>2.779122571946802</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.823832964039318</v>
+        <v>-5.831541119098151</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5454181442170092</v>
+        <v>0.5423348821934759</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.08706865108046874</v>
+        <v>-0.09477680613930345</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.823066563498203</v>
+        <v>2.818441670462903</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.580067522055874</v>
+        <v>-5.587775677114706</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6387050293574372</v>
+        <v>0.6356217673339044</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.08706865108046874</v>
+        <v>-0.09477680613930345</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.818847271845254</v>
+        <v>2.814222378809953</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.490291849679402</v>
+        <v>-5.498000004738234</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6767396122280425</v>
+        <v>0.6736563502045092</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.02546920616615872</v>
+        <v>-0.03317736122499343</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.857931252713856</v>
+        <v>2.853306359678555</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.240441455730327</v>
+        <v>-5.248149610789159</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7694218447913741</v>
+        <v>0.7663385827678413</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.02546920616615872</v>
+        <v>-0.03317736122499343</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.850673327697558</v>
+        <v>2.846048434662257</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.064549363262895</v>
+        <v>-5.072257518321727</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8433778052989958</v>
+        <v>0.8402945432754629</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.02546920616615872</v>
+        <v>-0.03317736122499343</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.854272451218207</v>
+        <v>2.849647558182906</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.893102900240431</v>
+        <v>-4.900811055299264</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.925283896562535</v>
+        <v>0.9222006345390019</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1459772568563044</v>
+        <v>0.1382691017974697</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.970467835086239</v>
+        <v>2.965842942050938</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.81308061313131</v>
+        <v>-4.820788768190143</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9563132890224804</v>
+        <v>0.9532300269989473</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2259995439654254</v>
+        <v>0.2182913889065907</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.017501684968008</v>
+        <v>3.012876791932707</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.749444870897376</v>
+        <v>-4.757153025956208</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9864623869703713</v>
+        <v>0.9833791249468384</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2896352861993599</v>
+        <v>0.2819271311405252</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.060377931362686</v>
+        <v>3.055753038327385</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.655747552680981</v>
+        <v>-4.663455707739813</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.005135573040725</v>
+        <v>1.002052311017192</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2896352861993599</v>
+        <v>0.2819271311405252</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.041572190146482</v>
+        <v>3.036947297111181</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.66625017574627</v>
+        <v>-4.673958330805102</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.002677600439487</v>
+        <v>0.9995943384159538</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.279132663134071</v>
+        <v>0.2714245080752363</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.037013692932186</v>
+        <v>3.032388799896885</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.553763915077395</v>
+        <v>-4.561472070136228</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.051601418541857</v>
+        <v>1.048518156518324</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.279132663134071</v>
+        <v>0.2714245080752363</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.040943006767006</v>
+        <v>3.036318113731705</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.53605022819953</v>
+        <v>-4.543758383258362</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.059365477210343</v>
+        <v>1.05628221518681</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2823139920309878</v>
+        <v>0.2746058369721531</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.043530388022496</v>
+        <v>3.038905494987195</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.412575956886512</v>
+        <v>-4.420284111945344</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.105753256955544</v>
+        <v>1.102669994932011</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2823139920309878</v>
+        <v>0.2746058369721531</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.040528459242489</v>
+        <v>3.035903566207188</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.192555158849501</v>
+        <v>-4.200263313908334</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.195340613180962</v>
+        <v>1.192257351157429</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4235338370989681</v>
+        <v>0.4158256820401334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.126839403293892</v>
+        <v>3.122214510258591</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.059687469786224</v>
+        <v>-4.067395624845056</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.264381871608097</v>
+        <v>1.261298609584564</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4235338370989681</v>
+        <v>0.4158256820401334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.142733586095715</v>
+        <v>3.138108693060414</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.939514386421725</v>
+        <v>-3.947222541480557</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.313596949394198</v>
+        <v>1.310513687370665</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.543706920463467</v>
+        <v>0.5359987654046323</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.215983280554716</v>
+        <v>3.211358387519415</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.804261025091748</v>
+        <v>-3.81196918015058</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.377786396487628</v>
+        <v>1.374703134464096</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6789602817934441</v>
+        <v>0.6712521267346094</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.307223399914142</v>
+        <v>3.302598506878842</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.86413585244944</v>
+        <v>-3.871844007508273</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.339873956945977</v>
+        <v>1.336790694922444</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.619085454435752</v>
+        <v>0.6113772993769173</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.257335994900953</v>
+        <v>3.252711101865652</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.744315621538603</v>
+        <v>-3.752023776597435</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.403091218544521</v>
+        <v>1.400007956520988</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.619085454435752</v>
+        <v>0.6113772993769173</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.272625164135162</v>
+        <v>3.268000271099861</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.746785328000409</v>
+        <v>-3.754493483059241</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.30974753528224</v>
+        <v>1.306664273258707</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6166157479739458</v>
+        <v>0.6089075929151111</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.178787539580519</v>
+        <v>3.174162646545219</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.815155514324418</v>
+        <v>-3.822863669383251</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.201661322237938</v>
+        <v>1.198578060214404</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6258914470101608</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.10361482048755</v>
+        <v>3.098989927452249</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.927027793950569</v>
+        <v>-3.934735949009402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.147349119019369</v>
+        <v>1.144265856995835</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6258914470101608</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.094051529119441</v>
+        <v>3.08942663608414</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.911053128464301</v>
+        <v>-3.918761283523134</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.120313510137903</v>
+        <v>1.11723024811437</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6258914470101608</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.060626054043468</v>
+        <v>3.056001161008167</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.735578868671832</v>
+        <v>-3.743287023730665</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.195070446046679</v>
+        <v>1.191987184023146</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6258914470101608</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.065193286035256</v>
+        <v>3.060568392999955</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.727654494086918</v>
+        <v>-3.73536264914575</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.173982224641851</v>
+        <v>1.170898962618318</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6258914470101608</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.040935314796463</v>
+        <v>3.036310421761162</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.721376291517069</v>
+        <v>-3.729084446575901</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.105031819071241</v>
+        <v>1.101948557047708</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6321696495800098</v>
+        <v>0.6244614945211751</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.973240549739822</v>
+        <v>2.968615656704522</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.661523672313346</v>
+        <v>-3.669231827372178</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.139145253184862</v>
+        <v>1.136061991161329</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6321696495800098</v>
+        <v>0.6244614945211751</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.983412936171955</v>
+        <v>2.978788043136654</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.575280209286968</v>
+        <v>-3.582988364345801</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.168588908969274</v>
+        <v>1.165505646945741</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6321696495800098</v>
+        <v>0.6244614945211751</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.978359206745815</v>
+        <v>2.973734313710514</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.620587028685948</v>
+        <v>-3.628295183744781</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.142241956654207</v>
+        <v>1.139158694630674</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.591359486570779</v>
+        <v>0.5836513315119443</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.945648884384802</v>
+        <v>2.941023991349501</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.64962013338825</v>
+        <v>-3.657328288447082</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.131180587806388</v>
+        <v>1.128097325782855</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.591359486570779</v>
+        <v>0.5836513315119443</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.946200757417904</v>
+        <v>2.941575864382603</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.556809651937391</v>
+        <v>-3.564517806996223</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.097577472278097</v>
+        <v>1.094494210254565</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6841699680216383</v>
+        <v>0.6764618129628036</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.931159738179785</v>
+        <v>2.926534845144484</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.601199121266818</v>
+        <v>-3.608907276325651</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.081695160470927</v>
+        <v>1.078611898447394</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6397804986922107</v>
+        <v>0.6320723436333759</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.906399532506729</v>
+        <v>2.901774639471428</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.580695427381321</v>
+        <v>-3.588403582440153</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.084972346536849</v>
+        <v>1.081889084513316</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.660284192577708</v>
+        <v>0.6525760375188733</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.913777457349751</v>
+        <v>2.90915256431445</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.620619521963893</v>
+        <v>-3.628327677022726</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.074494004534488</v>
+        <v>1.071410742510954</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.660284192577708</v>
+        <v>0.6525760375188733</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.919268753180418</v>
+        <v>2.914643860145117</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.648399919865246</v>
+        <v>-3.656108074924079</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.074879047142485</v>
+        <v>1.071795785118952</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.632503794676355</v>
+        <v>0.6247956396175203</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.914097716208145</v>
+        <v>2.909472823172844</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.766780592595385</v>
+        <v>-3.774488747654217</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8658824980510833</v>
+        <v>0.8627992360275503</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5652859425253788</v>
+        <v>0.5575777874665441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.712122724918212</v>
+        <v>2.707497831882912</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.875394671038716</v>
+        <v>-3.883102826097548</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9425865273929563</v>
+        <v>0.9395032653694235</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5652859425253788</v>
+        <v>0.5575777874665441</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.832272385637418</v>
+        <v>2.827647492602118</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.839985632790573</v>
+        <v>-3.847693787849405</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9712631687945366</v>
+        <v>0.9681799067710035</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5652859425253788</v>
+        <v>0.5575777874665441</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.846785411739741</v>
+        <v>2.842160518704441</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.848446801446034</v>
+        <v>-3.856154956504867</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9652981426747207</v>
+        <v>0.9622148806511879</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5568247738699177</v>
+        <v>0.549116618811083</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.839128151888833</v>
+        <v>2.834503258853533</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.671330471410868</v>
+        <v>-3.6790386264697</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.03287370353409</v>
+        <v>1.029790441510557</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5568247738699177</v>
+        <v>0.549116618811083</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.835857180734136</v>
+        <v>2.831232287698835</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.716422716244414</v>
+        <v>-3.724130871303246</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.015520197362584</v>
+        <v>1.012436935339051</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4949287307005279</v>
+        <v>0.4872205756416932</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.799402946594415</v>
+        <v>2.794778053559114</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.537047295005646</v>
+        <v>-3.544755450064478</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.081057341164506</v>
+        <v>1.077974079140973</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6517054888712466</v>
+        <v>0.6439973338124119</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88725597680326</v>
+        <v>2.88263108376796</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.582061508526252</v>
+        <v>-3.589769663585085</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.043859111087853</v>
+        <v>1.04077584906432</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.621356593556642</v>
+        <v>0.6136484384978073</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.849854094946088</v>
+        <v>2.845229201910787</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.849066018798688</v>
+        <v>-3.85677417385752</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9427488693178248</v>
+        <v>0.9396656072942917</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4269935555136934</v>
+        <v>0.4192854004548587</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.738927834459264</v>
+        <v>2.734302941423963</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.95026380023586</v>
+        <v>-3.957971955294693</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.901473678639457</v>
+        <v>0.898390416615924</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3585847419683742</v>
+        <v>0.3508765869095395</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.697086468228574</v>
+        <v>2.692461575193273</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.943752833621548</v>
+        <v>-3.95146098868038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9016780268394988</v>
+        <v>0.8985947648159658</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3585847419683742</v>
+        <v>0.3508765869095395</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.694686429782891</v>
+        <v>2.69006153674759</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.92471470591425</v>
+        <v>-3.932422860973083</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9058179971306626</v>
+        <v>0.9027347351071295</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3004011306371797</v>
+        <v>0.2926929755783449</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.656300982192419</v>
+        <v>2.651676089157118</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.97723050818907</v>
+        <v>-3.984938663247903</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.004106077854925</v>
+        <v>1.001022815831392</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3004011306371797</v>
+        <v>0.2926929755783449</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.775595383826609</v>
+        <v>2.770970490791308</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.98063881962365</v>
+        <v>-3.988346974682483</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.003576082267227</v>
+        <v>1.000492820243694</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.332917699646557</v>
+        <v>0.3252095445877223</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.795938654218369</v>
+        <v>2.791313761183068</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.961282683729803</v>
+        <v>-3.968990838788636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.017327067021691</v>
+        <v>1.014243804998158</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.332917699646557</v>
+        <v>0.3252095445877223</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.801947184615295</v>
+        <v>2.797322291579994</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.813539713494801</v>
+        <v>-3.821247868553634</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9743744763928917</v>
+        <v>0.9712912143693586</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5007250568814402</v>
+        <v>0.4930169018226055</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.800581820233425</v>
+        <v>2.795956927198123</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.897360934769499</v>
+        <v>-3.905069089828332</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9436396094144934</v>
+        <v>0.9405563473909604</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5007250568814402</v>
+        <v>0.4930169018226055</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.803375441764905</v>
+        <v>2.798750548729604</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.891208228716715</v>
+        <v>-3.898916383775547</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9467630402272655</v>
+        <v>0.9436797782037325</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5068777629342245</v>
+        <v>0.4991696078753898</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.807729413788234</v>
+        <v>2.803104520752933</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.436734329019526</v>
+        <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.908017526867216</v>
+        <v>-3.915725681926049</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8731708939588914</v>
+        <v>0.9360365356836422</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4900684647837228</v>
+        <v>0.4823603097248881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.73077540788976</v>
+        <v>2.792099418602743</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.503069882816347</v>
+        <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.845719528091094</v>
+        <v>-3.853427683149927</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.964425647266161</v>
+        <v>1.027291288990912</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5353627290581648</v>
+        <v>0.5276545739993301</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.824287520251246</v>
+        <v>2.885611530964229</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.305361884530474</v>
+        <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.643929330425936</v>
+        <v>-3.651637485484769</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8474337280463513</v>
+        <v>0.9102993697711022</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7333809212273192</v>
+        <v>0.7256727661684845</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.745390437266865</v>
+        <v>2.806714447979849</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.375652116852649</v>
+        <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.694816043112131</v>
+        <v>-3.702524198170964</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8973692752940485</v>
+        <v>0.9602349170187994</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6824942085411247</v>
+        <v>0.67478605348229</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.785148641977324</v>
+        <v>2.846472652690307</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.390279852968693</v>
+        <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.608205300462324</v>
+        <v>-3.615913455521156</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9466413084700152</v>
+        <v>1.009506950194766</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.761119939746283</v>
+        <v>0.7534117846874483</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.846951816816463</v>
+        <v>2.908275827529446</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.388815833793364</v>
+        <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.668414598467608</v>
+        <v>-3.676122753526441</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9210935700925731</v>
+        <v>0.9839592118173239</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7009106417409985</v>
+        <v>0.6932024866821638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.809362218837963</v>
+        <v>2.870686229550947</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.387307451833293</v>
+        <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.619227949783257</v>
+        <v>-3.626936104842089</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9392598476062421</v>
+        <v>1.002125489330993</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7009106417409985</v>
+        <v>0.6932024866821638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.807853836877892</v>
+        <v>2.869177847590875</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.387170319268729</v>
+        <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.574854818144688</v>
+        <v>-3.582562973203521</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9568719676971058</v>
+        <v>1.019737609421857</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7452837733795671</v>
+        <v>0.7375756183207324</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.834340583296469</v>
+        <v>2.895664594009453</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.38156411340732</v>
+        <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.597335169003573</v>
+        <v>-3.605043324062406</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9422736214921423</v>
+        <v>1.005139263216893</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7452837733795671</v>
+        <v>0.7375756183207324</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.82873437743506</v>
+        <v>2.890058388148043</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.387945870435124</v>
+        <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.549679438442517</v>
+        <v>-3.55738759350135</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9677176707443693</v>
+        <v>1.03058331246912</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7929395039406227</v>
+        <v>0.785231348881788</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.863709572799498</v>
+        <v>2.925033583512481</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.392838243809849</v>
+        <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.449161279943763</v>
+        <v>-3.456869435002595</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.012817307518596</v>
+        <v>1.075682949243347</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8934576624393773</v>
+        <v>0.8857495073805426</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.928912841273476</v>
+        <v>2.990236851986459</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.379592916285721</v>
+        <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.43325595051141</v>
+        <v>-3.440964105570242</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.005934111767409</v>
+        <v>1.06879975349216</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8143450017301384</v>
+        <v>0.8066368466713036</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.868199917323805</v>
+        <v>2.929523928036788</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.38369061889635</v>
+        <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.388417548903012</v>
+        <v>-3.396125703961844</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.027967175021397</v>
+        <v>1.090832816746148</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8188884346750078</v>
+        <v>0.8111802796161731</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.875023679701355</v>
+        <v>2.936347690414338</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.387851558527428</v>
+        <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.40791600514502</v>
+        <v>-3.415624160203853</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.024328732155672</v>
+        <v>1.087194373880423</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7708037933951035</v>
+        <v>0.7630956383362688</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.85033383456449</v>
+        <v>2.911657845277473</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.393731161055265</v>
+        <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.36371316805912</v>
+        <v>-3.371421323117952</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.047889469517869</v>
+        <v>1.11075511124262</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.815006630481004</v>
+        <v>0.8072984754221693</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.882735139343867</v>
+        <v>2.944059150056851</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.392141161524513</v>
+        <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.371272833896167</v>
+        <v>-3.378980988954999</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.043275603652298</v>
+        <v>1.106141245377049</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8698100344908233</v>
+        <v>0.8621018794319886</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.914027182219007</v>
+        <v>2.97535119293199</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.443388926707552</v>
+        <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.212981416356894</v>
+        <v>-3.220689571415727</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.157839935851046</v>
+        <v>1.220705577575797</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8698100344908233</v>
+        <v>0.8621018794319886</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.965274947402047</v>
+        <v>3.026598958115029</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.441829631301805</v>
+        <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.005339412722418</v>
+        <v>-3.013047567781251</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.23933744189909</v>
+        <v>1.302203083623841</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.077452038125299</v>
+        <v>1.069743883066465</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.088300854176985</v>
+        <v>3.149624864889968</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.436777859540075</v>
+        <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.95430731999989</v>
+        <v>-2.962015475058723</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.254698507226371</v>
+        <v>1.317564148951122</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.128484130847828</v>
+        <v>1.120775975788993</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.113868338048772</v>
+        <v>3.175192348761755</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.45396526363278</v>
+        <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.889083138872684</v>
+        <v>-2.896791293931517</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.297975583769958</v>
+        <v>1.36084122549471</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.193708311975033</v>
+        <v>1.186000156916198</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.1701902508178</v>
+        <v>3.231514261530783</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.449926235932061</v>
+        <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.851656118801551</v>
+        <v>-2.859364273860383</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.308907364097692</v>
+        <v>1.371773005822443</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.198959850004215</v>
+        <v>1.19125169494538</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.16930214593459</v>
+        <v>3.230626156647573</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.451183028263301</v>
+        <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.850298133828005</v>
+        <v>-2.858006288886838</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.310707350418351</v>
+        <v>1.373572992143102</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.273297975542033</v>
+        <v>1.265589820483199</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.215161813588521</v>
+        <v>3.276485824301504</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.611740799284512</v>
+        <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.821884870728121</v>
+        <v>-2.829593025786954</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.482630426679515</v>
+        <v>1.545496068404266</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.214322412795605</v>
+        <v>1.20661425773677</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.340334246961875</v>
+        <v>3.401658257674858</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.731853708502329</v>
+        <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.747102609703109</v>
+        <v>-2.754810764761941</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.632656240307337</v>
+        <v>1.695521882032088</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.289104673820617</v>
+        <v>1.281396518761783</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.5053165127947</v>
+        <v>3.566640523507683</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.723561684516188</v>
+        <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.721018525439301</v>
+        <v>-2.728726680498133</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.63479785002672</v>
+        <v>1.69766349175147</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.289104673820617</v>
+        <v>1.281396518761783</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.497024488808559</v>
+        <v>3.558348499521542</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.721754880099967</v>
+        <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.63314061233018</v>
+        <v>-2.640848767389013</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.668142210854147</v>
+        <v>1.731007852578898</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.405030316243968</v>
+        <v>1.397322161185134</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.564773069846348</v>
+        <v>3.626097080559332</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.739309285826759</v>
+        <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.624248150936897</v>
+        <v>-2.63195630599573</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.689253601138252</v>
+        <v>1.752119242863003</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.405030316243968</v>
+        <v>1.397322161185134</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.58232747557314</v>
+        <v>3.643651486286123</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.731164333231343</v>
+        <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.792724267906775</v>
+        <v>-2.800432422965608</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.613718201754885</v>
+        <v>1.676583843479636</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.377082480527388</v>
+        <v>1.369374325468553</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.557413821547776</v>
+        <v>3.618737832260758</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.712434030419205</v>
+        <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.346468075277335</v>
+        <v>-2.354176230336168</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.773490375994522</v>
+        <v>1.836356017719273</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.282363810857755</v>
+        <v>1.27465565579892</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.481852316933858</v>
+        <v>3.543176327646841</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.703098052916109</v>
+        <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.323746971594183</v>
+        <v>-2.331455126653015</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.773242839964688</v>
+        <v>1.836108481689439</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.282363810857755</v>
+        <v>1.27465565579892</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.472516339430762</v>
+        <v>3.533840350143745</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.862004178767278</v>
+        <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.452948784888225</v>
+        <v>-2.460656939947058</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.88046824049824</v>
+        <v>1.943333882222991</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.153161997563713</v>
+        <v>1.145453842504878</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.553901377305506</v>
+        <v>3.615225388018489</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.899082001260925</v>
+        <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.478823183362251</v>
+        <v>-2.486531338421083</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.907196303602276</v>
+        <v>1.970061945327027</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.198073606275454</v>
+        <v>1.190365451216619</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.617926165026197</v>
+        <v>3.67925017573918</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.89575735725047</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.471768493147077</v>
+        <v>-2.47947664820591</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.906693535677891</v>
+        <v>1.969559177402642</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.205128296490628</v>
+        <v>1.197420141431793</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.618834335144847</v>
+        <v>3.68015834585783</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.905763510895211</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.444817268820589</v>
+        <v>-2.452525423879422</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.927480179053227</v>
+        <v>1.990345820777979</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.220008642518347</v>
+        <v>1.212300487459512</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.63776869640622</v>
+        <v>3.699092707119203</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.089866643040171</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.466361496651376</v>
+        <v>-2.474069651710209</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.102965620065873</v>
+        <v>2.165831261790624</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.220008642518347</v>
+        <v>1.212300487459512</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.821871828551179</v>
+        <v>3.883195839264162</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.081983337943164</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.488769614456249</v>
+        <v>-2.496477769515081</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.086119067846917</v>
+        <v>2.148984709571668</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.220008642518347</v>
+        <v>1.212300487459512</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.813988523454173</v>
+        <v>3.875312534167155</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.084037337492802</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.516993850033849</v>
+        <v>-2.524702005092681</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.076883373165514</v>
+        <v>2.139749014890265</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.237985394969655</v>
+        <v>1.230277239910821</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.826828574474595</v>
+        <v>3.888152585187578</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.140291055214649</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.526434775922379</v>
+        <v>-2.534142930981211</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.129360720531949</v>
+        <v>2.1922263622567</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.360412512513047</v>
+        <v>1.352704357454212</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.956538562722477</v>
+        <v>4.01786257343546</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.14318214975995</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.615311407090853</v>
+        <v>-2.623019562149685</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.096701162609861</v>
+        <v>2.159566804334611</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.271535881344573</v>
+        <v>1.263827726285738</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.906103678566694</v>
+        <v>3.967427689279677</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.141293962653725</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.691641384691759</v>
+        <v>-2.699349539750591</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.064280984463274</v>
+        <v>2.127146626188024</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.271535881344573</v>
+        <v>1.263827726285738</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.904215491460469</v>
+        <v>3.965539502173452</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.136114192256587</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.7853053293693</v>
+        <v>-2.793013484428132</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.02163563619512</v>
+        <v>2.08450127791987</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.177871936667032</v>
+        <v>1.170163781608197</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.842837354256806</v>
+        <v>3.904161364969789</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.134548202466739</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.946873754896555</v>
+        <v>-2.954581909955388</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.955442276194369</v>
+        <v>2.01830791791912</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.051089012869152</v>
+        <v>1.043380857810317</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.765201610188231</v>
+        <v>3.826525620901214</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.147621609332658</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.055174416766675</v>
+        <v>-3.062882571825507</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.92519541831224</v>
+        <v>1.988061060036991</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.051089012869152</v>
+        <v>1.043380857810317</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.778275017054149</v>
+        <v>3.839599027767133</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.139626806115598</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.072978388487419</v>
+        <v>-3.080686543546251</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.910079026406883</v>
+        <v>1.972944668131634</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9805543899639511</v>
+        <v>0.9728462349051163</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.727959440093969</v>
+        <v>3.789283450806952</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.1381508472426</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.100879175596892</v>
+        <v>-3.108587330655724</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.897442752690095</v>
+        <v>1.960308394414846</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9459574658210163</v>
+        <v>0.9382493107621815</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.70572532673521</v>
+        <v>3.767049337448193</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.134915291219799</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.223405278299786</v>
+        <v>-3.231113433358618</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.845196755586137</v>
+        <v>1.908062397310887</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8234313631181224</v>
+        <v>0.8157232080592877</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.628974109090672</v>
+        <v>3.690298119803656</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.201621250810303</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.453919774485374</v>
+        <v>-3.461627929544207</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.819696916702405</v>
+        <v>1.882562558427156</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5929168669325336</v>
+        <v>0.5852087118736989</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.557371370969823</v>
+        <v>3.618695381682806</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.34193296981215</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.802664859709818</v>
+        <v>-3.810373014768651</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.820510601614474</v>
+        <v>1.883376243339225</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4841689130136358</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.632434317620331</v>
+        <v>3.693758328333314</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.410913238957789</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.956651277485959</v>
+        <v>-3.964359432544791</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.827896303649658</v>
+        <v>1.890761945374409</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4841689130136358</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.701414586765971</v>
+        <v>3.762738597478954</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.39696444107791</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.161250712348967</v>
+        <v>-4.1689588674078</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.732107731824575</v>
+        <v>1.794973373549326</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4841689130136358</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.687465788886092</v>
+        <v>3.748789799599075</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.408834930133324</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.413725866356692</v>
+        <v>-4.421434021415524</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.6429881592769</v>
+        <v>1.705853801001651</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4841689130136358</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.699336277941506</v>
+        <v>3.760660288654489</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.410045464652268</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.706621622836104</v>
+        <v>-4.714329777894936</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.527040391204078</v>
+        <v>1.589906032928829</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4841689130136358</v>
+        <v>0.4764607579548011</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.70054681246045</v>
+        <v>3.761870823173433</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.414167206879589</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.893285750970912</v>
+        <v>-4.900993906029744</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.456496482177477</v>
+        <v>1.519362123902228</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.457429942189076</v>
+        <v>0.4497217871302412</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.688625172193035</v>
+        <v>3.749949182906018</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.409245059615779</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.039306437884874</v>
+        <v>-5.047014592943706</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.393166060148081</v>
+        <v>1.456031701872832</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.448346850395219</v>
+        <v>0.4406386953363843</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.678253169852911</v>
+        <v>3.739577180565893</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.571449116314823</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.131020446994459</v>
+        <v>-5.138728602053291</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.518684513203291</v>
+        <v>1.581550154928042</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.448346850395219</v>
+        <v>0.4406386953363843</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.840457226551955</v>
+        <v>3.901781237264938</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.566295754278637</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.162672106054428</v>
+        <v>-5.201709736627575</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.500870487543118</v>
+        <v>1.551204339062143</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4431783931507788</v>
+        <v>0.4235765143511808</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.832202790169104</v>
+        <v>3.88639056663763</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.576525171847128</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.244606924323311</v>
+        <v>-5.283644554896458</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.478325977804056</v>
+        <v>1.528659829323081</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4332436475636986</v>
+        <v>0.4136417687641006</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.836471360385348</v>
+        <v>3.890659136853873</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.585450810303031</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.346583046571719</v>
+        <v>-5.385620677144866</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.446461167360595</v>
+        <v>1.49679501887962</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.331267525315291</v>
+        <v>0.311665646515693</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.784211325492206</v>
+        <v>3.83839910196073</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.577603697547206</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.236576763094497</v>
+        <v>-5.275614393667644</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.482616567995659</v>
+        <v>1.532950419514684</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3544720972325662</v>
+        <v>0.3348702184329682</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.790286955886746</v>
+        <v>3.844474732355271</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.58185370826918</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.093517187353571</v>
+        <v>-5.132554817926719</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.544090409014004</v>
+        <v>1.594424260533029</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3624855238225455</v>
+        <v>0.3428836450229475</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.799345022562708</v>
+        <v>3.853532799031233</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.589114591151716</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.792070461881734</v>
+        <v>-4.831108092454881</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.671929982085275</v>
+        <v>1.7222638336043</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6639322492943828</v>
+        <v>0.6443303704947847</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.987473940728346</v>
+        <v>4.041661717196871</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.590085768904427</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.816660706116918</v>
+        <v>-4.855698336690065</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.663065062143912</v>
+        <v>1.713398913662937</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6639322492943828</v>
+        <v>0.6443303704947847</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.988445118481057</v>
+        <v>4.042632894949582</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.590928673284183</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.765622330110397</v>
+        <v>-4.804659960683545</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.684323316926276</v>
+        <v>1.7346571684453</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6639322492943828</v>
+        <v>0.6443303704947847</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.989288022860812</v>
+        <v>4.043475799329338</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.609966772158328</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.724483035243766</v>
+        <v>-4.763520665816914</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.719817133747073</v>
+        <v>1.770150985266098</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7050715441610136</v>
+        <v>0.6854696653614155</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.033009698654936</v>
+        <v>4.087197475123461</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.426150768282263</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.627848123225126</v>
+        <v>-4.666885753798274</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.574655094678464</v>
+        <v>1.624988946197489</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8017064561796535</v>
+        <v>0.7821045773800555</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.907174641990055</v>
+        <v>3.96136241845858</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.429652812356227</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.558810112276658</v>
+        <v>-4.597847742849806</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.605772343131815</v>
+        <v>1.65610619465084</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8707444671281216</v>
+        <v>0.8511425883285235</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.9520994926331</v>
+        <v>4.006287269101625</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.414079631432309</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.394313778085697</v>
+        <v>-4.433351408658845</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.655997695884283</v>
+        <v>1.706331547403307</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.035240801319083</v>
+        <v>1.015638922519485</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.03522411222376</v>
+        <v>4.089411888692284</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.413267341868739</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.317215176543824</v>
+        <v>-4.356252807116972</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.686024846937461</v>
+        <v>1.736358698456486</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.035240801319083</v>
+        <v>1.015638922519485</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.034411822660189</v>
+        <v>4.088599599128714</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.423136120993811</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.327600371433713</v>
+        <v>-4.366638002006861</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.691739548106578</v>
+        <v>1.742073399625603</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.024855606429194</v>
+        <v>1.005253727629596</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.038049484851328</v>
+        <v>4.092237261319853</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.493973126770237</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.346188530155938</v>
+        <v>-4.385226160729086</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.755141290394113</v>
+        <v>1.805475141913138</v>
       </c>
       <c r="F2038" t="n">
-        <v>1.006267447706969</v>
+        <v>0.9866655689073704</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.097733595394418</v>
+        <v>4.151921371862943</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.490842137588535</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.346487076851974</v>
+        <v>-4.385524707425122</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.751890882533997</v>
+        <v>1.802224734053022</v>
       </c>
       <c r="F2039" t="n">
-        <v>1.005968901010933</v>
+        <v>0.9863670222113345</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.094423478195095</v>
+        <v>4.14861125466362</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.495373032527926</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.245663943161547</v>
+        <v>-4.284701573734695</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.79675103094956</v>
+        <v>1.847084882468585</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.018433116495287</v>
+        <v>0.9988312376956885</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.106432902425099</v>
+        <v>4.160620678893624</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.49550228600647</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.054882582409139</v>
+        <v>-4.093920212982287</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.873192828729066</v>
+        <v>1.923526680248091</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.209214477247694</v>
+        <v>1.189612598448096</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.221030972355086</v>
+        <v>4.275218748823612</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.475339131744066</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.947919224559717</v>
+        <v>-3.986956855132865</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.895815017606431</v>
+        <v>1.946148869125456</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.267679085207496</v>
+        <v>1.248077206407897</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.235946582868564</v>
+        <v>4.290134359337089</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.510306068356125</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.892588636657955</v>
+        <v>-3.931626267231103</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.952914189379195</v>
+        <v>2.003248040898219</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.323009673109258</v>
+        <v>1.303407794309659</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.30411187222168</v>
+        <v>4.358299648690204</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.503992636257562</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.880534509744992</v>
+        <v>-3.91957214031814</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.951422408045818</v>
+        <v>2.001756259564842</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.33506380002222</v>
+        <v>1.315461921222622</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.305030916270895</v>
+        <v>4.35921869273942</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.505873266441698</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.921689629313213</v>
+        <v>-3.960727259886361</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.936840990402665</v>
+        <v>1.98717484192169</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.293908680453999</v>
+        <v>1.274306801654401</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.282218474714099</v>
+        <v>4.336406251182623</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.518724292319581</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.853641066621683</v>
+        <v>-3.892678697194831</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.976911441357159</v>
+        <v>2.027245292876184</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.361957243145529</v>
+        <v>1.342355364345931</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.335898638206898</v>
+        <v>4.390086414675424</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.538926962493175</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.085241459791185</v>
+        <v>-4.124279090364332</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.904473954262953</v>
+        <v>1.954807805781978</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.361957243145529</v>
+        <v>1.342355364345931</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.356101308380492</v>
+        <v>4.410289084849018</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.522533198560057</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.135293005320404</v>
+        <v>-4.174330635893552</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.868059572118147</v>
+        <v>1.918393423637172</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.361957243145529</v>
+        <v>1.342355364345931</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.339707544447375</v>
+        <v>4.3938953209159</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.482785112153524</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.310399837896849</v>
+        <v>-4.349437468469997</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.758268752681036</v>
+        <v>1.808602604200061</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.361957243145529</v>
+        <v>1.342355364345931</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.299959458040841</v>
+        <v>4.354147234509367</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.489807731150464</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.114299684466326</v>
+        <v>-4.153337315039474</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.843731433050185</v>
+        <v>1.89406528456921</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.558057396576052</v>
+        <v>1.538455517776454</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.424642169096095</v>
+        <v>4.47882994556462</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.588978730723368</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.961274292353042</v>
+        <v>-4.000311922926191</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.004112589468403</v>
+        <v>2.054446440987428</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.711082788689336</v>
+        <v>1.691480909889738</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.61562840393697</v>
+        <v>4.669816180405495</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.776444955631661</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.989581606226312</v>
+        <v>-4.028619236799461</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.180255888827388</v>
+        <v>2.230589740346413</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.711082788689336</v>
+        <v>1.691480909889738</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.803094628845263</v>
+        <v>4.857282405313788</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.745847906985743</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.156174831339834</v>
+        <v>-4.195212461912983</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.083021550136062</v>
+        <v>2.133355401655086</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.544489563575814</v>
+        <v>1.524887684776216</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.672541645131232</v>
+        <v>4.726729421599757</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.749524309647461</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.133139037978268</v>
+        <v>-4.172176668551417</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.095912270142406</v>
+        <v>2.14624612166143</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.544489563575814</v>
+        <v>1.524887684776216</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.67621804779295</v>
+        <v>4.730405824261474</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.747142364770956</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.103893057522572</v>
+        <v>-4.142930688095721</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.105228717448179</v>
+        <v>2.155562568967204</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.544489563575814</v>
+        <v>1.524887684776216</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.673836102916445</v>
+        <v>4.72802387938497</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.744435603928591</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.210818605400423</v>
+        <v>-4.249856235973572</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.059751737454674</v>
+        <v>2.110085588973699</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.437564015697963</v>
+        <v>1.417962136898364</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.606974013347369</v>
+        <v>4.661161789815894</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700997</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.745864406071826</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.355837163907672</v>
+        <v>-4.39487479448082</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.003173116195009</v>
+        <v>2.053506967714034</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.292545457190714</v>
+        <v>1.272943578391116</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.521391680386254</v>
+        <v>4.575579456854779</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.845795645329579</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.474178929692389</v>
+        <v>-4.513216560265538</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.055767649138875</v>
+        <v>2.1061015006579</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.303231495753604</v>
+        <v>1.283629616954006</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.627734542781742</v>
+        <v>4.681922319250266</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.843581342455518</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.525589352013097</v>
+        <v>-4.564626982586246</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.032989177336531</v>
+        <v>2.083323028855555</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.303231495753604</v>
+        <v>1.283629616954006</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.62552023990768</v>
+        <v>4.679708016376205</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.843484470529807</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.605008803220849</v>
+        <v>-4.644046433793998</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.001124524927719</v>
+        <v>2.051458376446744</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.303231495753604</v>
+        <v>1.283629616954006</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.62542336798197</v>
+        <v>4.679611144450495</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.84347836408785</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.700471801138066</v>
+        <v>-4.739509431711215</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.962933219318876</v>
+        <v>2.0132670708379</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.303231495753604</v>
+        <v>1.283629616954006</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.625417261540012</v>
+        <v>4.679605038008537</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217997</v>
+        <v>3.715372960217999</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.84157476065046</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.636095890287351</v>
+        <v>-4.6751335208605</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.986779980221772</v>
+        <v>2.037113831740797</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.367607406604319</v>
+        <v>1.348005527804721</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.662139204613053</v>
+        <v>4.716326981081577</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353534</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.847308578398187</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.691465052419545</v>
+        <v>-4.730502682992694</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.970366133116621</v>
+        <v>2.020699984635645</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.367607406604319</v>
+        <v>1.348005527804721</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.667873022360779</v>
+        <v>4.722060798829304</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.84684694174112</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.736902832250372</v>
+        <v>-4.775940462823521</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.951729384527223</v>
+        <v>2.002063236046247</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.32476241592616</v>
+        <v>1.305160537126562</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.641704391296815</v>
+        <v>4.695892167765341</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113686</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.866721334591438</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.648695998102794</v>
+        <v>-4.687733628675943</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.006886511036573</v>
+        <v>2.057220362555597</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.32476241592616</v>
+        <v>1.305160537126562</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.661578784147134</v>
+        <v>4.715766560615659</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.850422035116166</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.542661002897485</v>
+        <v>-4.581698633470634</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.033001209643424</v>
+        <v>2.083335061162449</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.32476241592616</v>
+        <v>1.305160537126562</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.645279484671862</v>
+        <v>4.699467261140387</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.852852984580212</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.35944933976439</v>
+        <v>-4.398486970337538</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.108716824360708</v>
+        <v>2.159050675879732</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.32476241592616</v>
+        <v>1.305160537126562</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.647710434135908</v>
+        <v>4.701898210604432</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.818644170428102</v>
+        <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.287727892750539</v>
+        <v>-4.326765523323687</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.103196589014138</v>
+        <v>2.153530440533163</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.39648386294001</v>
+        <v>1.376881984140412</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.656534488192109</v>
+        <v>4.710722264660633</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.765559916349273</v>
+        <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.265354867142833</v>
+        <v>-4.304392497715981</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.059061545178392</v>
+        <v>2.109395396697417</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.407739614052912</v>
+        <v>1.388137735253314</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.610203684781021</v>
+        <v>4.664391461249545</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.950758121234629</v>
+        <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.298371163053577</v>
+        <v>-4.337408793626726</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.23105323169945</v>
+        <v>2.281387083218474</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.33830223738616</v>
+        <v>1.318700358586562</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.753739463666325</v>
+        <v>4.807927240134849</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.942679347062878</v>
+        <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.286843527403969</v>
+        <v>-4.325881157977117</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.227585511787542</v>
+        <v>2.277919363306566</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.397302895587523</v>
+        <v>1.377701016787925</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.781061084415392</v>
+        <v>4.835248860883916</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.946347459584667</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.384185028746337</v>
+        <v>-4.423222659319486</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.192317023772384</v>
+        <v>2.242650875291408</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.352882713422034</v>
+        <v>1.333280834622436</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.758077087637887</v>
+        <v>4.812264864106412</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.947598541777505</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.470041058086304</v>
+        <v>-4.509078688659453</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.159225694229235</v>
+        <v>2.209559545748259</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.310506644195899</v>
+        <v>1.290904765396301</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.733902528295045</v>
+        <v>4.788090304763569</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.930017743598007</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.478877855502423</v>
+        <v>-4.517915486075572</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.13811017708329</v>
+        <v>2.188444028602313</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.303064471554549</v>
+        <v>1.283462592754951</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.711856426530736</v>
+        <v>4.76604420299926</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.940182254643056</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.570260418067882</v>
+        <v>-4.609298048641031</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.111721663102156</v>
+        <v>2.162055514621179</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.266499586835204</v>
+        <v>1.246897708035606</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.700082006744179</v>
+        <v>4.754269783212703</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.042310512467324</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.558553700080876</v>
+        <v>-4.597591330654025</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.218532608121226</v>
+        <v>2.268866459640249</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.278206304822211</v>
+        <v>1.258604426022612</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.809234295360651</v>
+        <v>4.863422071829174</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.045342851198729</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.458890195997213</v>
+        <v>-4.497927826570362</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.261430348486096</v>
+        <v>2.311764200005118</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.341393388025897</v>
+        <v>1.321791509226299</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.850178884014268</v>
+        <v>4.904366660482791</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452568</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.258247684476787</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.469206294163565</v>
+        <v>-4.508243924736714</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.470208742497613</v>
+        <v>2.520542594016636</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.341393388025897</v>
+        <v>1.321791509226299</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.063083717292326</v>
+        <v>5.117271493760849</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.257426351388877</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.469112326146193</v>
+        <v>-4.508149956719341</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.469424996616651</v>
+        <v>2.519758848135675</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.062484301012806</v>
+        <v>5.116672077481329</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.251658337333231</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.476331150346037</v>
+        <v>-4.515368780919186</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.460769452881068</v>
+        <v>2.511103304400091</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.05671628695716</v>
+        <v>5.110904063425683</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.251658337333231</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.475382727227998</v>
+        <v>-4.514420357801147</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.461148822128283</v>
+        <v>2.511482673647306</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.05671628695716</v>
+        <v>5.110904063425683</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.264385945314323</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.632451185483623</v>
+        <v>-4.671488816056772</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.411049046807126</v>
+        <v>2.461382898326149</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.069443894938252</v>
+        <v>5.123631671406775</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.26633194373871</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.626458938694811</v>
+        <v>-4.66549656926796</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.415391943947038</v>
+        <v>2.465725795466061</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.07138989336264</v>
+        <v>5.125577669831163</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.259986079756479</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.537900977564044</v>
+        <v>-4.576938608137192</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.444469264417114</v>
+        <v>2.494803115936137</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.065044029380409</v>
+        <v>5.119231805848932</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.259294757195475</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.520141900060969</v>
+        <v>-4.559179530634118</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.450881572857339</v>
+        <v>2.501215424376362</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.341763249373215</v>
+        <v>1.322161370573617</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.064352706819404</v>
+        <v>5.118540483287927</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.272076943104062</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.420511749011902</v>
+        <v>-4.45954937958505</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.503515819185553</v>
+        <v>2.553849670704576</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.441393400422283</v>
+        <v>1.421791521622684</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.136912983357432</v>
+        <v>5.191100759825955</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.461231208602788</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.469911257700913</v>
+        <v>-4.508948888274062</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.672910281208675</v>
+        <v>2.723244132727698</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.451652233854027</v>
+        <v>1.432050355054429</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.332222548915205</v>
+        <v>5.386410325383728</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.44841988170565</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.263226784058537</v>
+        <v>-4.302264414631686</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.742772743768487</v>
+        <v>2.793106595287511</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.658336707496403</v>
+        <v>1.638734828696805</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.443421906203493</v>
+        <v>5.497609682672016</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.450421395359755</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.297383679056063</v>
+        <v>-4.336421309629212</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.731111499423582</v>
+        <v>2.781445350942605</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.574752937955591</v>
+        <v>1.555151059155992</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.39527315813311</v>
+        <v>5.449460934601633</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.879864134253824</v>
+        <v>3.754314530395749</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.803918509349423</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.216784726364907</v>
+        <v>-4.243831830567755</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.116848194489712</v>
+        <v>3.171978256556855</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.574752937955591</v>
+        <v>1.555151059155992</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.748770272122777</v>
+        <v>5.8029580485913</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.4%</t>
+          <t>177.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>134.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2090"/>
+  <dimension ref="A1:G2091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013425</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217999</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353534</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113686</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236293</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.754314530395749</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49631,6 +49631,29 @@
       </c>
       <c r="G2090" t="n">
         <v>5.8029580485913</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="2" t="n">
+        <v>45553</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>3.755455012694191</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>4.890690638286161</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>-4.243831830567755</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>3.171978256556855</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>1.555151059155992</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>4.883754435272529</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>177.4%</t>
+          <t>176.9%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.0%</t>
+          <t>-585.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-67.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,21 +1433,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>41.8%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.626936104842089</v>
+        <v>-3.64431436001982</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002125489330993</v>
+        <v>0.9951741872599009</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6932024866821638</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.582562973203521</v>
+        <v>-3.599941228381251</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019737609421857</v>
+        <v>1.012786307350765</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7375756183207324</v>
@@ -47022,10 +47022,10 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.605043324062406</v>
+        <v>-3.622421579240136</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005139263216893</v>
+        <v>0.9981879611458011</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7375756183207324</v>
@@ -47045,10 +47045,10 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.55738759350135</v>
+        <v>-3.57476584867908</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03058331246912</v>
+        <v>1.023632010398028</v>
       </c>
       <c r="F1978" t="n">
         <v>0.785231348881788</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.456869435002595</v>
+        <v>-3.474247690180325</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075682949243347</v>
+        <v>1.068731647172255</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8857495073805426</v>
@@ -47091,10 +47091,10 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.440964105570242</v>
+        <v>-3.458342360747973</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.06879975349216</v>
+        <v>1.061848451421068</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8066368466713036</v>
@@ -47114,10 +47114,10 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.396125703961844</v>
+        <v>-3.413503959139575</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090832816746148</v>
+        <v>1.083881514675056</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8111802796161731</v>
@@ -47137,10 +47137,10 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.415624160203853</v>
+        <v>-3.433002415381583</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087194373880423</v>
+        <v>1.080243071809331</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7630956383362688</v>
@@ -47160,10 +47160,10 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.371421323117952</v>
+        <v>-3.388799578295683</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.11075511124262</v>
+        <v>1.103803809171528</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8072984754221693</v>
@@ -47183,10 +47183,10 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.378980988954999</v>
+        <v>-3.396359244132729</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106141245377049</v>
+        <v>1.099189943305957</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8621018794319886</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.220689571415727</v>
+        <v>-3.238067826593457</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220705577575797</v>
+        <v>1.213754275504705</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8621018794319886</v>
@@ -47229,10 +47229,10 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.013047567781251</v>
+        <v>-3.030425822958981</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.302203083623841</v>
+        <v>1.295251781552749</v>
       </c>
       <c r="F1986" t="n">
         <v>1.069743883066465</v>
@@ -47252,10 +47252,10 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.962015475058723</v>
+        <v>-2.979393730236453</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317564148951122</v>
+        <v>1.31061284688003</v>
       </c>
       <c r="F1987" t="n">
         <v>1.120775975788993</v>
@@ -47275,10 +47275,10 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.896791293931517</v>
+        <v>-2.914169549109247</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.36084122549471</v>
+        <v>1.353889923423617</v>
       </c>
       <c r="F1988" t="n">
         <v>1.186000156916198</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.859364273860383</v>
+        <v>-2.876742529038113</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371773005822443</v>
+        <v>1.364821703751351</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19125169494538</v>
@@ -47321,10 +47321,10 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.858006288886838</v>
+        <v>-2.875384544064568</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.373572992143102</v>
+        <v>1.36662169007201</v>
       </c>
       <c r="F1990" t="n">
         <v>1.265589820483199</v>
@@ -47344,10 +47344,10 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.829593025786954</v>
+        <v>-2.846971280964684</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.545496068404266</v>
+        <v>1.538544766333174</v>
       </c>
       <c r="F1991" t="n">
         <v>1.20661425773677</v>
@@ -47367,10 +47367,10 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.754810764761941</v>
+        <v>-2.772189019939672</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.695521882032088</v>
+        <v>1.688570579960996</v>
       </c>
       <c r="F1992" t="n">
         <v>1.281396518761783</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.728726680498133</v>
+        <v>-2.746104935675864</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.69766349175147</v>
+        <v>1.690712189680378</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.640848767389013</v>
+        <v>-2.658227022566743</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.731007852578898</v>
+        <v>1.724056550507806</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.63195630599573</v>
+        <v>-2.64933456117346</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.752119242863003</v>
+        <v>1.745167940791911</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.800432422965608</v>
+        <v>-2.817810678143338</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.676583843479636</v>
+        <v>1.669632541408543</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
@@ -47482,10 +47482,10 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.354176230336168</v>
+        <v>-2.371554485513898</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.836356017719273</v>
+        <v>1.829404715648181</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
@@ -47505,10 +47505,10 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.331455126653015</v>
+        <v>-2.348833381830746</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.836108481689439</v>
+        <v>1.829157179618347</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.460656939947058</v>
+        <v>-2.478035195124788</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.943333882222991</v>
+        <v>1.936382580151899</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
@@ -47551,10 +47551,10 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.486531338421083</v>
+        <v>-2.503909593598814</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.970061945327027</v>
+        <v>1.963110643255935</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.47947664820591</v>
+        <v>-2.49685490338364</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.969559177402642</v>
+        <v>1.96260787533155</v>
       </c>
       <c r="F2001" t="n">
         <v>1.197420141431793</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.452525423879422</v>
+        <v>-2.469903679057152</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.990345820777979</v>
+        <v>1.983394518706886</v>
       </c>
       <c r="F2002" t="n">
         <v>1.212300487459512</v>
@@ -47620,10 +47620,10 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.474069651710209</v>
+        <v>-2.491447906887939</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.165831261790624</v>
+        <v>2.158879959719531</v>
       </c>
       <c r="F2003" t="n">
         <v>1.212300487459512</v>
@@ -47643,10 +47643,10 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.496477769515081</v>
+        <v>-2.513856024692811</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.148984709571668</v>
+        <v>2.142033407500576</v>
       </c>
       <c r="F2004" t="n">
         <v>1.212300487459512</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.524702005092681</v>
+        <v>-2.542080260270412</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.139749014890265</v>
+        <v>2.132797712819173</v>
       </c>
       <c r="F2005" t="n">
         <v>1.230277239910821</v>
@@ -47689,10 +47689,10 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.534142930981211</v>
+        <v>-2.551521186158942</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.1922263622567</v>
+        <v>2.185275060185608</v>
       </c>
       <c r="F2006" t="n">
         <v>1.352704357454212</v>
@@ -47712,10 +47712,10 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.623019562149685</v>
+        <v>-2.640397817327416</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.159566804334611</v>
+        <v>2.15261550226352</v>
       </c>
       <c r="F2007" t="n">
         <v>1.263827726285738</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.699349539750591</v>
+        <v>-2.716727794928322</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.127146626188024</v>
+        <v>2.120195324116932</v>
       </c>
       <c r="F2008" t="n">
         <v>1.263827726285738</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.793013484428132</v>
+        <v>-2.810391739605863</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.08450127791987</v>
+        <v>2.077549975848778</v>
       </c>
       <c r="F2009" t="n">
         <v>1.170163781608197</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.954581909955388</v>
+        <v>-2.971960165133118</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.01830791791912</v>
+        <v>2.011356615848028</v>
       </c>
       <c r="F2010" t="n">
         <v>1.043380857810317</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.062882571825507</v>
+        <v>-3.080260827003237</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.988061060036991</v>
+        <v>1.981109757965899</v>
       </c>
       <c r="F2011" t="n">
         <v>1.043380857810317</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.080686543546251</v>
+        <v>-3.098064798723982</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.972944668131634</v>
+        <v>1.965993366060541</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9728462349051163</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.108587330655724</v>
+        <v>-3.125965585833455</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.960308394414846</v>
+        <v>1.953357092343754</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9382493107621815</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.231113433358618</v>
+        <v>-3.248491688536348</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.908062397310887</v>
+        <v>1.901111095239795</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8157232080592877</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.461627929544207</v>
+        <v>-3.479006184721937</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.882562558427156</v>
+        <v>1.875611256356064</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5852087118736989</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.810373014768651</v>
+        <v>-3.827751269946381</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.883376243339225</v>
+        <v>1.876424941268133</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4764607579548011</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.964359432544791</v>
+        <v>-3.981737687722521</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.890761945374409</v>
+        <v>1.883810643303317</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4764607579548011</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.1689588674078</v>
+        <v>-4.18633712258553</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.794973373549326</v>
+        <v>1.788022071478234</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4764607579548011</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.421434021415524</v>
+        <v>-4.438812276593255</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.705853801001651</v>
+        <v>1.698902498930558</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4764607579548011</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.714329777894936</v>
+        <v>-4.731708033072667</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.589906032928829</v>
+        <v>1.582954730857737</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4764607579548011</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.900993906029744</v>
+        <v>-4.918372161207475</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.519362123902228</v>
+        <v>1.512410821831135</v>
       </c>
       <c r="F2021" t="n">
         <v>0.4497217871302412</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.047014592943706</v>
+        <v>-5.064392848121437</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.456031701872832</v>
+        <v>1.44908039980174</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4406386953363843</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.138728602053291</v>
+        <v>-5.156106857231022</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.581550154928042</v>
+        <v>1.57459885285695</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4406386953363843</v>
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.201709736627575</v>
+        <v>-5.187758516290991</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.551204339062143</v>
+        <v>1.556784827196777</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4235765143511808</v>
+        <v>0.4354702380919441</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.88639056663763</v>
+        <v>3.893526800882088</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.283644554896458</v>
+        <v>-5.269693334559874</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.528659829323081</v>
+        <v>1.534240317457714</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4136417687641006</v>
+        <v>0.4255354925048639</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.890659136853873</v>
+        <v>3.897795371098331</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.385620677144866</v>
+        <v>-5.371669456808282</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.49679501887962</v>
+        <v>1.502375507014254</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.311665646515693</v>
+        <v>0.3235593702564563</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.83839910196073</v>
+        <v>3.845535336205189</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.275614393667644</v>
+        <v>-5.26166317333106</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.532950419514684</v>
+        <v>1.538530907649318</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3348702184329682</v>
+        <v>0.3467639421737315</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.844474732355271</v>
+        <v>3.851610966599729</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.132554817926719</v>
+        <v>-5.118603597590134</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.594424260533029</v>
+        <v>1.600004748667663</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3428836450229475</v>
+        <v>0.3547773687637108</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.853532799031233</v>
+        <v>3.860669033275691</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.831108092454881</v>
+        <v>-4.817156872118296</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.7222638336043</v>
+        <v>1.727844321738934</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6443303704947847</v>
+        <v>0.6562240942355481</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.041661717196871</v>
+        <v>4.04879795144133</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.855698336690065</v>
+        <v>-4.84174711635348</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.713398913662937</v>
+        <v>1.718979401797571</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6443303704947847</v>
+        <v>0.6562240942355481</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.042632894949582</v>
+        <v>4.04976912919404</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.804659960683545</v>
+        <v>-4.79070874034696</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.7346571684453</v>
+        <v>1.740237656579934</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6443303704947847</v>
+        <v>0.6562240942355481</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.043475799329338</v>
+        <v>4.050612033573795</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.763520665816914</v>
+        <v>-4.749569445480329</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.770150985266098</v>
+        <v>1.775731473400732</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6854696653614155</v>
+        <v>0.6973633891021789</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.087197475123461</v>
+        <v>4.09433370936792</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.666885753798274</v>
+        <v>-4.652934533461689</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.624988946197489</v>
+        <v>1.630569434332123</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7821045773800555</v>
+        <v>0.7939983011208188</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.96136241845858</v>
+        <v>3.968498652703038</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.597847742849806</v>
+        <v>-4.583896522513221</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65610619465084</v>
+        <v>1.661686682785474</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8511425883285235</v>
+        <v>0.8630363120692869</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.006287269101625</v>
+        <v>4.013423503346083</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.433351408658845</v>
+        <v>-4.41940018832226</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.706331547403307</v>
+        <v>1.711912035537941</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.015638922519485</v>
+        <v>1.027532646260249</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.089411888692284</v>
+        <v>4.096548122936743</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.356252807116972</v>
+        <v>-4.342301586780387</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.736358698456486</v>
+        <v>1.74193918659112</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.015638922519485</v>
+        <v>1.027532646260249</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.088599599128714</v>
+        <v>4.095735833373173</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.366638002006861</v>
+        <v>-4.352686781670276</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.742073399625603</v>
+        <v>1.747653887760237</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.005253727629596</v>
+        <v>1.017147451370359</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.092237261319853</v>
+        <v>4.099373495564311</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.385226160729086</v>
+        <v>-4.371274940392501</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.805475141913138</v>
+        <v>1.811055630047772</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9866655689073704</v>
+        <v>0.9985592926481339</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.151921371862943</v>
+        <v>4.159057606107401</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.385524707425122</v>
+        <v>-4.371573487088537</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.802224734053022</v>
+        <v>1.807805222187656</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9863670222113345</v>
+        <v>0.998260745952098</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.14861125466362</v>
+        <v>4.155747488908078</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.284701573734695</v>
+        <v>-4.270750353398109</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.847084882468585</v>
+        <v>1.852665370603219</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9988312376956885</v>
+        <v>1.010724961436452</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.160620678893624</v>
+        <v>4.167756913138081</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.093920212982287</v>
+        <v>-4.079968992645702</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.923526680248091</v>
+        <v>1.929107168382725</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.189612598448096</v>
+        <v>1.201506322188859</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.275218748823612</v>
+        <v>4.282354983068069</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.986956855132865</v>
+        <v>-3.97300563479628</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.946148869125456</v>
+        <v>1.95172935726009</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.248077206407897</v>
+        <v>1.259970930148661</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.290134359337089</v>
+        <v>4.297270593581547</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.931626267231103</v>
+        <v>-3.917675046894518</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.003248040898219</v>
+        <v>2.008828529032853</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.303407794309659</v>
+        <v>1.315301518050423</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.358299648690204</v>
+        <v>4.365435882934663</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.91957214031814</v>
+        <v>-3.905620919981555</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.001756259564842</v>
+        <v>2.007336747699476</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.315461921222622</v>
+        <v>1.327355644963386</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.35921869273942</v>
+        <v>4.366354926983878</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.960727259886361</v>
+        <v>-3.946776039549776</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.98717484192169</v>
+        <v>1.992755330056323</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.274306801654401</v>
+        <v>1.286200525395165</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.336406251182623</v>
+        <v>4.343542485427081</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.892678697194831</v>
+        <v>-3.878727476858246</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.027245292876184</v>
+        <v>2.032825781010818</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.342355364345931</v>
+        <v>1.354249088086695</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.390086414675424</v>
+        <v>4.397222648919882</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.124279090364332</v>
+        <v>-4.110327870027747</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.954807805781978</v>
+        <v>1.960388293916612</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.342355364345931</v>
+        <v>1.354249088086695</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.410289084849018</v>
+        <v>4.417425319093476</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.174330635893552</v>
+        <v>-4.160379415556967</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.918393423637172</v>
+        <v>1.923973911771806</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.342355364345931</v>
+        <v>1.354249088086695</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.3938953209159</v>
+        <v>4.401031555160358</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.349437468469997</v>
+        <v>-4.335486248133412</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.808602604200061</v>
+        <v>1.814183092334695</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.342355364345931</v>
+        <v>1.354249088086695</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.354147234509367</v>
+        <v>4.361283468753824</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.153337315039474</v>
+        <v>-4.139386094702889</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.89406528456921</v>
+        <v>1.899645772703844</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.538455517776454</v>
+        <v>1.550349241517218</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.47882994556462</v>
+        <v>4.485966179809078</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.000311922926191</v>
+        <v>-3.986360702589605</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.054446440987428</v>
+        <v>2.060026929122062</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.691480909889738</v>
+        <v>1.703374633630502</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.669816180405495</v>
+        <v>4.676952414649953</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.028619236799461</v>
+        <v>-4.014668016462875</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.230589740346413</v>
+        <v>2.236170228481047</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.691480909889738</v>
+        <v>1.703374633630502</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.857282405313788</v>
+        <v>4.864418639558245</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.195212461912983</v>
+        <v>-4.181261241576397</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.133355401655086</v>
+        <v>2.13893588978972</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.524887684776216</v>
+        <v>1.536781408516979</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.726729421599757</v>
+        <v>4.733865655844215</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.172176668551417</v>
+        <v>-4.158225448214831</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.14624612166143</v>
+        <v>2.151826609796065</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.524887684776216</v>
+        <v>1.536781408516979</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.730405824261474</v>
+        <v>4.737542058505933</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.142930688095721</v>
+        <v>-4.128979467759135</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.155562568967204</v>
+        <v>2.161143057101838</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.524887684776216</v>
+        <v>1.536781408516979</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.72802387938497</v>
+        <v>4.735160113629428</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.249856235973572</v>
+        <v>-4.235905015636986</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.110085588973699</v>
+        <v>2.115666077108333</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.417962136898364</v>
+        <v>1.429855860639128</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.661161789815894</v>
+        <v>4.668298024060352</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.39487479448082</v>
+        <v>-4.380923574144235</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.053506967714034</v>
+        <v>2.059087455848668</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.272943578391116</v>
+        <v>1.284837302131879</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.575579456854779</v>
+        <v>4.582715691099237</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687011</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.513216560265538</v>
+        <v>-4.499265339928952</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.1061015006579</v>
+        <v>2.111681988792534</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.283629616954006</v>
+        <v>1.295523340694769</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.681922319250266</v>
+        <v>4.689058553494724</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.564626982586246</v>
+        <v>-4.523883824955894</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.083323028855555</v>
+        <v>2.099620291907696</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.283629616954006</v>
+        <v>1.295523340694769</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.679708016376205</v>
+        <v>4.686844250620664</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.644046433793998</v>
+        <v>-4.603303276163646</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.051458376446744</v>
+        <v>2.067755639498884</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.283629616954006</v>
+        <v>1.295523340694769</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.679611144450495</v>
+        <v>4.686747378694952</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.739509431711215</v>
+        <v>-4.698766274080864</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.0132670708379</v>
+        <v>2.02956433389004</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.283629616954006</v>
+        <v>1.295523340694769</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.679605038008537</v>
+        <v>4.686741272252996</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.6751335208605</v>
+        <v>-4.634390363230149</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.037113831740797</v>
+        <v>2.053411094792937</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.348005527804721</v>
+        <v>1.359899251545485</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.716326981081577</v>
+        <v>4.723463215326035</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.730502682992694</v>
+        <v>-4.689759525362343</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.020699984635645</v>
+        <v>2.036997247687786</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.348005527804721</v>
+        <v>1.359899251545485</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.722060798829304</v>
+        <v>4.729197033073762</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.775940462823521</v>
+        <v>-4.73519730519317</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.002063236046247</v>
+        <v>2.018360499098387</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.305160537126562</v>
+        <v>1.317054260867325</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.695892167765341</v>
+        <v>4.703028402009799</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.687733628675943</v>
+        <v>-4.646990471045592</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.057220362555597</v>
+        <v>2.073517625607737</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.305160537126562</v>
+        <v>1.317054260867325</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.715766560615659</v>
+        <v>4.722902794860118</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.581698633470634</v>
+        <v>-4.540955475840282</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.083335061162449</v>
+        <v>2.099632324214589</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.305160537126562</v>
+        <v>1.317054260867325</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.699467261140387</v>
+        <v>4.706603495384845</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.398486970337538</v>
+        <v>-4.357743812707187</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.159050675879732</v>
+        <v>2.175347938931873</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.305160537126562</v>
+        <v>1.317054260867325</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.701898210604432</v>
+        <v>4.709034444848891</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.326765523323687</v>
+        <v>-4.286022365693336</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.153530440533163</v>
+        <v>2.169827703585303</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.376881984140412</v>
+        <v>1.388775707881176</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.710722264660633</v>
+        <v>4.717858498905091</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.304392497715981</v>
+        <v>-4.26364934008563</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.109395396697417</v>
+        <v>2.125692659749557</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.388137735253314</v>
+        <v>1.400031458994077</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.664391461249545</v>
+        <v>4.671527695494003</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.337408793626726</v>
+        <v>-4.296665635996375</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.281387083218474</v>
+        <v>2.297684346270614</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.318700358586562</v>
+        <v>1.330594082327326</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.807927240134849</v>
+        <v>4.815063474379308</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.325881157977117</v>
+        <v>-4.285138000346766</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.277919363306566</v>
+        <v>2.294216626358707</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.377701016787925</v>
+        <v>1.389594740528688</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.835248860883916</v>
+        <v>4.842385095128374</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236293</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.423222659319486</v>
+        <v>-4.382479501689135</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.242650875291408</v>
+        <v>2.258948138343547</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.333280834622436</v>
+        <v>1.3451745583632</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.812264864106412</v>
+        <v>4.81940109835087</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.509078688659453</v>
+        <v>-4.468335531029101</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.209559545748259</v>
+        <v>2.225856808800399</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.290904765396301</v>
+        <v>1.302798489137065</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.788090304763569</v>
+        <v>4.795226539008027</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.517915486075572</v>
+        <v>-4.477172328445221</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.188444028602313</v>
+        <v>2.204741291654453</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.283462592754951</v>
+        <v>1.295356316495714</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.76604420299926</v>
+        <v>4.773180437243719</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.609298048641031</v>
+        <v>-4.568554891010679</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.162055514621179</v>
+        <v>2.178352777673319</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.246897708035606</v>
+        <v>1.258791431776369</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.754269783212703</v>
+        <v>4.761406017457161</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.597591330654025</v>
+        <v>-4.556848173023673</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.268866459640249</v>
+        <v>2.285163722692389</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.258604426022612</v>
+        <v>1.270498149763376</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.863422071829174</v>
+        <v>4.870558306073632</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.497927826570362</v>
+        <v>-4.457184668940011</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.311764200005118</v>
+        <v>2.328061463057259</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.321791509226299</v>
+        <v>1.333685232967062</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.904366660482791</v>
+        <v>4.911502894727249</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.508243924736714</v>
+        <v>-4.467500767106363</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.520542594016636</v>
+        <v>2.536839857068776</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.321791509226299</v>
+        <v>1.333685232967062</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.117271493760849</v>
+        <v>5.124407728005307</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.508149956719341</v>
+        <v>-4.46740679908899</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.519758848135675</v>
+        <v>2.536056111187815</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.116672077481329</v>
+        <v>5.123808311725787</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.515368780919186</v>
+        <v>-4.474625623288834</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.511103304400091</v>
+        <v>2.527400567452231</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.110904063425683</v>
+        <v>5.118040297670142</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.514420357801147</v>
+        <v>-4.473677200170796</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.511482673647306</v>
+        <v>2.527779936699447</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.110904063425683</v>
+        <v>5.118040297670142</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.671488816056772</v>
+        <v>-4.63074565842642</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.461382898326149</v>
+        <v>2.477680161378289</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.123631671406775</v>
+        <v>5.130767905651233</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.66549656926796</v>
+        <v>-4.624753411637609</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.465725795466061</v>
+        <v>2.482023058518201</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.125577669831163</v>
+        <v>5.13271390407562</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.576938608137192</v>
+        <v>-4.536195450506841</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.494803115936137</v>
+        <v>2.511100378988277</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.119231805848932</v>
+        <v>5.126368040093389</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.559179530634118</v>
+        <v>-4.518436373003767</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.501215424376362</v>
+        <v>2.517512687428503</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.322161370573617</v>
+        <v>1.33405509431438</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.118540483287927</v>
+        <v>5.125676717532386</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.45954937958505</v>
+        <v>-4.418806221954699</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.553849670704576</v>
+        <v>2.570146933756716</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.421791521622684</v>
+        <v>1.433685245363448</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.191100759825955</v>
+        <v>5.198236994070413</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.508948888274062</v>
+        <v>-4.46820573064371</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.723244132727698</v>
+        <v>2.739541395779838</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.432050355054429</v>
+        <v>1.443944078795193</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.386410325383728</v>
+        <v>5.393546559628186</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.302264414631686</v>
+        <v>-4.261521257001334</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.793106595287511</v>
+        <v>2.809403858339651</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.638734828696805</v>
+        <v>1.650628552437568</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.497609682672016</v>
+        <v>5.504745916916473</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.336421309629212</v>
+        <v>-4.29567815199886</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.781445350942605</v>
+        <v>2.797742613994745</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.555151059155992</v>
+        <v>1.567044782896756</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.449460934601633</v>
+        <v>5.456597168846091</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652383</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.243831830567755</v>
+        <v>-4.243603441986565</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.171978256556855</v>
+        <v>3.172069611989331</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.555151059155992</v>
+        <v>1.567044782896756</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.8029580485913</v>
+        <v>5.810094282835759</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.755455012694191</v>
+        <v>3.758104326857142</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.890690638286161</v>
+        <v>4.885557212133674</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.243831830567755</v>
+        <v>-4.243603441986565</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.171978256556855</v>
+        <v>3.172069611989331</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.555151059155992</v>
+        <v>1.567044782896756</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.883754435272529</v>
+        <v>4.878621009120041</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.9%</t>
+          <t>-585.1%</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-59.0%</t>
+          <t>-58.7%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.64431436001982</v>
+        <v>-3.649643735309048</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9951741872599009</v>
+        <v>0.9930424371442095</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6932024866821638</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.599941228381251</v>
+        <v>-3.605270603670479</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.012786307350765</v>
+        <v>1.010654557235073</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7375756183207324</v>
@@ -47022,10 +47022,10 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.622421579240136</v>
+        <v>-3.627750954529364</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9981879611458011</v>
+        <v>0.9960562110301097</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7375756183207324</v>
@@ -47045,10 +47045,10 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.57476584867908</v>
+        <v>-3.580095223968309</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.023632010398028</v>
+        <v>1.021500260282337</v>
       </c>
       <c r="F1978" t="n">
         <v>0.785231348881788</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.474247690180325</v>
+        <v>-3.479577065469554</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.068731647172255</v>
+        <v>1.066599897056563</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8857495073805426</v>
@@ -47091,10 +47091,10 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.458342360747973</v>
+        <v>-3.463671736037202</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.061848451421068</v>
+        <v>1.059716701305377</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8066368466713036</v>
@@ -47114,10 +47114,10 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.413503959139575</v>
+        <v>-3.418833334428804</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.083881514675056</v>
+        <v>1.081749764559364</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8111802796161731</v>
@@ -47137,10 +47137,10 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.433002415381583</v>
+        <v>-3.438331790670812</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.080243071809331</v>
+        <v>1.078111321693639</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7630956383362688</v>
@@ -47160,10 +47160,10 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.388799578295683</v>
+        <v>-3.394128953584911</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.103803809171528</v>
+        <v>1.101672059055836</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8072984754221693</v>
@@ -47183,10 +47183,10 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.396359244132729</v>
+        <v>-3.401688619421958</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.099189943305957</v>
+        <v>1.097058193190265</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8621018794319886</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.238067826593457</v>
+        <v>-3.243397201882686</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.213754275504705</v>
+        <v>1.211622525389014</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8621018794319886</v>
@@ -47229,10 +47229,10 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.030425822958981</v>
+        <v>-3.03575519824821</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.295251781552749</v>
+        <v>1.293120031437057</v>
       </c>
       <c r="F1986" t="n">
         <v>1.069743883066465</v>
@@ -47252,10 +47252,10 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.979393730236453</v>
+        <v>-2.984723105525682</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.31061284688003</v>
+        <v>1.308481096764339</v>
       </c>
       <c r="F1987" t="n">
         <v>1.120775975788993</v>
@@ -47275,10 +47275,10 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.914169549109247</v>
+        <v>-2.919498924398476</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.353889923423617</v>
+        <v>1.351758173307926</v>
       </c>
       <c r="F1988" t="n">
         <v>1.186000156916198</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.876742529038113</v>
+        <v>-2.882071904327342</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.364821703751351</v>
+        <v>1.36268995363566</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19125169494538</v>
@@ -47321,10 +47321,10 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.875384544064568</v>
+        <v>-2.880713919353797</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36662169007201</v>
+        <v>1.364489939956318</v>
       </c>
       <c r="F1990" t="n">
         <v>1.265589820483199</v>
@@ -47344,10 +47344,10 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.846971280964684</v>
+        <v>-2.852300656253913</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.538544766333174</v>
+        <v>1.536413016217482</v>
       </c>
       <c r="F1991" t="n">
         <v>1.20661425773677</v>
@@ -47367,10 +47367,10 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.772189019939672</v>
+        <v>-2.7775183952289</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.688570579960996</v>
+        <v>1.686438829845305</v>
       </c>
       <c r="F1992" t="n">
         <v>1.281396518761783</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.746104935675864</v>
+        <v>-2.751434310965093</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.690712189680378</v>
+        <v>1.688580439564687</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.658227022566743</v>
+        <v>-2.663556397855972</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.724056550507806</v>
+        <v>1.721924800392115</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.64933456117346</v>
+        <v>-2.654663936462689</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.745167940791911</v>
+        <v>1.743036190676219</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.817810678143338</v>
+        <v>-2.823140053432567</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.669632541408543</v>
+        <v>1.667500791292852</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
@@ -47482,10 +47482,10 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.371554485513898</v>
+        <v>-2.376883860803127</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.829404715648181</v>
+        <v>1.82727296553249</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
@@ -47505,10 +47505,10 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.348833381830746</v>
+        <v>-2.354162757119974</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.829157179618347</v>
+        <v>1.827025429502655</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.478035195124788</v>
+        <v>-2.483364570414017</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.936382580151899</v>
+        <v>1.934250830036207</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
@@ -47551,10 +47551,10 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.503909593598814</v>
+        <v>-2.509238968888043</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.963110643255935</v>
+        <v>1.960978893140243</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
@@ -47574,10 +47574,10 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.49685490338364</v>
+        <v>-2.502184278672869</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96260787533155</v>
+        <v>1.960476125215858</v>
       </c>
       <c r="F2001" t="n">
         <v>1.197420141431793</v>
@@ -47597,10 +47597,10 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.469903679057152</v>
+        <v>-2.475233054346381</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.983394518706886</v>
+        <v>1.981262768591195</v>
       </c>
       <c r="F2002" t="n">
         <v>1.212300487459512</v>
@@ -47620,10 +47620,10 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.491447906887939</v>
+        <v>-2.496777282177168</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.158879959719531</v>
+        <v>2.15674820960384</v>
       </c>
       <c r="F2003" t="n">
         <v>1.212300487459512</v>
@@ -47643,10 +47643,10 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.513856024692811</v>
+        <v>-2.51918539998204</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.142033407500576</v>
+        <v>2.139901657384884</v>
       </c>
       <c r="F2004" t="n">
         <v>1.212300487459512</v>
@@ -47666,10 +47666,10 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.542080260270412</v>
+        <v>-2.547409635559641</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.132797712819173</v>
+        <v>2.130665962703481</v>
       </c>
       <c r="F2005" t="n">
         <v>1.230277239910821</v>
@@ -47689,10 +47689,10 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.551521186158942</v>
+        <v>-2.55685056144817</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.185275060185608</v>
+        <v>2.183143310069917</v>
       </c>
       <c r="F2006" t="n">
         <v>1.352704357454212</v>
@@ -47712,10 +47712,10 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.640397817327416</v>
+        <v>-2.645727192616644</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.15261550226352</v>
+        <v>2.150483752147828</v>
       </c>
       <c r="F2007" t="n">
         <v>1.263827726285738</v>
@@ -47735,10 +47735,10 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.716727794928322</v>
+        <v>-2.72205717021755</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.120195324116932</v>
+        <v>2.118063574001241</v>
       </c>
       <c r="F2008" t="n">
         <v>1.263827726285738</v>
@@ -47758,10 +47758,10 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.810391739605863</v>
+        <v>-2.815721114895092</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.077549975848778</v>
+        <v>2.075418225733086</v>
       </c>
       <c r="F2009" t="n">
         <v>1.170163781608197</v>
@@ -47781,10 +47781,10 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.971960165133118</v>
+        <v>-2.977289540422347</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.011356615848028</v>
+        <v>2.009224865732337</v>
       </c>
       <c r="F2010" t="n">
         <v>1.043380857810317</v>
@@ -47804,10 +47804,10 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.080260827003237</v>
+        <v>-3.085590202292466</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.981109757965899</v>
+        <v>1.978978007850207</v>
       </c>
       <c r="F2011" t="n">
         <v>1.043380857810317</v>
@@ -47827,10 +47827,10 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.098064798723982</v>
+        <v>-3.10339417401321</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.965993366060541</v>
+        <v>1.96386161594485</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9728462349051163</v>
@@ -47850,10 +47850,10 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.125965585833455</v>
+        <v>-3.131294961122683</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.953357092343754</v>
+        <v>1.951225342228063</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9382493107621815</v>
@@ -47873,10 +47873,10 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.248491688536348</v>
+        <v>-3.253821063825577</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.901111095239795</v>
+        <v>1.898979345124104</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8157232080592877</v>
@@ -47896,10 +47896,10 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.479006184721937</v>
+        <v>-3.484335560011166</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.875611256356064</v>
+        <v>1.873479506240372</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5852087118736989</v>
@@ -47919,10 +47919,10 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.827751269946381</v>
+        <v>-3.83308064523561</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.876424941268133</v>
+        <v>1.874293191152442</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4764607579548011</v>
@@ -47942,10 +47942,10 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.981737687722521</v>
+        <v>-3.98706706301175</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.883810643303317</v>
+        <v>1.881678893187625</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4764607579548011</v>
@@ -47965,10 +47965,10 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.18633712258553</v>
+        <v>-4.191666497874759</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.788022071478234</v>
+        <v>1.785890321362543</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4764607579548011</v>
@@ -47988,10 +47988,10 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.438812276593255</v>
+        <v>-4.444141651882483</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.698902498930558</v>
+        <v>1.696770748814867</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4764607579548011</v>
@@ -48011,10 +48011,10 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.731708033072667</v>
+        <v>-4.737037408361895</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.582954730857737</v>
+        <v>1.580822980742046</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4764607579548011</v>
@@ -48034,10 +48034,10 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.918372161207475</v>
+        <v>-4.923701536496703</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.512410821831135</v>
+        <v>1.510279071715444</v>
       </c>
       <c r="F2021" t="n">
         <v>0.4497217871302412</v>
@@ -48057,10 +48057,10 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.064392848121437</v>
+        <v>-5.069722223410666</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.44908039980174</v>
+        <v>1.446948649686048</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4406386953363843</v>
@@ -48080,10 +48080,10 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.156106857231022</v>
+        <v>-5.16143623252025</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.57459885285695</v>
+        <v>1.572467102741259</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4406386953363843</v>
@@ -48103,10 +48103,10 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.187758516290991</v>
+        <v>-5.19308789158022</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.556784827196777</v>
+        <v>1.554653077081085</v>
       </c>
       <c r="F2024" t="n">
         <v>0.4354702380919441</v>
@@ -48126,10 +48126,10 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.269693334559874</v>
+        <v>-5.275022709849103</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.534240317457714</v>
+        <v>1.532108567342023</v>
       </c>
       <c r="F2025" t="n">
         <v>0.4255354925048639</v>
@@ -48149,10 +48149,10 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.371669456808282</v>
+        <v>-5.37699883209751</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.502375507014254</v>
+        <v>1.500243756898562</v>
       </c>
       <c r="F2026" t="n">
         <v>0.3235593702564563</v>
@@ -48172,10 +48172,10 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.26166317333106</v>
+        <v>-5.266992548620289</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.538530907649318</v>
+        <v>1.536399157533626</v>
       </c>
       <c r="F2027" t="n">
         <v>0.3467639421737315</v>
@@ -48195,10 +48195,10 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.118603597590134</v>
+        <v>-5.123932972879363</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.600004748667663</v>
+        <v>1.597872998551971</v>
       </c>
       <c r="F2028" t="n">
         <v>0.3547773687637108</v>
@@ -48218,10 +48218,10 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.817156872118296</v>
+        <v>-4.822486247407525</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.727844321738934</v>
+        <v>1.725712571623242</v>
       </c>
       <c r="F2029" t="n">
         <v>0.6562240942355481</v>
@@ -48241,10 +48241,10 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.84174711635348</v>
+        <v>-4.847076491642709</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.718979401797571</v>
+        <v>1.716847651681879</v>
       </c>
       <c r="F2030" t="n">
         <v>0.6562240942355481</v>
@@ -48264,10 +48264,10 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.79070874034696</v>
+        <v>-4.796038115636189</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.740237656579934</v>
+        <v>1.738105906464243</v>
       </c>
       <c r="F2031" t="n">
         <v>0.6562240942355481</v>
@@ -48287,10 +48287,10 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.749569445480329</v>
+        <v>-4.754898820769558</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.775731473400732</v>
+        <v>1.773599723285041</v>
       </c>
       <c r="F2032" t="n">
         <v>0.6973633891021789</v>
@@ -48310,10 +48310,10 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.652934533461689</v>
+        <v>-4.658263908750918</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.630569434332123</v>
+        <v>1.628437684216431</v>
       </c>
       <c r="F2033" t="n">
         <v>0.7939983011208188</v>
@@ -48333,10 +48333,10 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.583896522513221</v>
+        <v>-4.58922589780245</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.661686682785474</v>
+        <v>1.659554932669782</v>
       </c>
       <c r="F2034" t="n">
         <v>0.8630363120692869</v>
@@ -48356,10 +48356,10 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.41940018832226</v>
+        <v>-4.424729563611488</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.711912035537941</v>
+        <v>1.70978028542225</v>
       </c>
       <c r="F2035" t="n">
         <v>1.027532646260249</v>
@@ -48379,10 +48379,10 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.342301586780387</v>
+        <v>-4.347630962069616</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.74193918659112</v>
+        <v>1.739807436475429</v>
       </c>
       <c r="F2036" t="n">
         <v>1.027532646260249</v>
@@ -48402,10 +48402,10 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.352686781670276</v>
+        <v>-4.358016156959505</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.747653887760237</v>
+        <v>1.745522137644545</v>
       </c>
       <c r="F2037" t="n">
         <v>1.017147451370359</v>
@@ -48425,10 +48425,10 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.371274940392501</v>
+        <v>-4.37660431568173</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.811055630047772</v>
+        <v>1.80892387993208</v>
       </c>
       <c r="F2038" t="n">
         <v>0.9985592926481339</v>
@@ -48448,10 +48448,10 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.371573487088537</v>
+        <v>-4.376902862377766</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.807805222187656</v>
+        <v>1.805673472071964</v>
       </c>
       <c r="F2039" t="n">
         <v>0.998260745952098</v>
@@ -48471,10 +48471,10 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.270750353398109</v>
+        <v>-4.276079728687338</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.852665370603219</v>
+        <v>1.850533620487527</v>
       </c>
       <c r="F2040" t="n">
         <v>1.010724961436452</v>
@@ -48494,10 +48494,10 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.079968992645702</v>
+        <v>-4.08529836793493</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.929107168382725</v>
+        <v>1.926975418267034</v>
       </c>
       <c r="F2041" t="n">
         <v>1.201506322188859</v>
@@ -48517,10 +48517,10 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.97300563479628</v>
+        <v>-3.978335010085509</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.95172935726009</v>
+        <v>1.949597607144399</v>
       </c>
       <c r="F2042" t="n">
         <v>1.259970930148661</v>
@@ -48540,10 +48540,10 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.917675046894518</v>
+        <v>-3.923004422183747</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.008828529032853</v>
+        <v>2.006696778917162</v>
       </c>
       <c r="F2043" t="n">
         <v>1.315301518050423</v>
@@ -48563,10 +48563,10 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.905620919981555</v>
+        <v>-3.910950295270784</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.007336747699476</v>
+        <v>2.005204997583784</v>
       </c>
       <c r="F2044" t="n">
         <v>1.327355644963386</v>
@@ -48586,10 +48586,10 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.946776039549776</v>
+        <v>-3.952105414839005</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.992755330056323</v>
+        <v>1.990623579940632</v>
       </c>
       <c r="F2045" t="n">
         <v>1.286200525395165</v>
@@ -48609,10 +48609,10 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.878727476858246</v>
+        <v>-3.884056852147475</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.032825781010818</v>
+        <v>2.030694030895127</v>
       </c>
       <c r="F2046" t="n">
         <v>1.354249088086695</v>
@@ -48632,10 +48632,10 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.110327870027747</v>
+        <v>-4.115657245316976</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.960388293916612</v>
+        <v>1.95825654380092</v>
       </c>
       <c r="F2047" t="n">
         <v>1.354249088086695</v>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.160379415556967</v>
+        <v>-4.165708790846196</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.923973911771806</v>
+        <v>1.921842161656115</v>
       </c>
       <c r="F2048" t="n">
         <v>1.354249088086695</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.335486248133412</v>
+        <v>-4.340815623422641</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.814183092334695</v>
+        <v>1.812051342219003</v>
       </c>
       <c r="F2049" t="n">
         <v>1.354249088086695</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.139386094702889</v>
+        <v>-4.144715469992118</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.899645772703844</v>
+        <v>1.897514022588152</v>
       </c>
       <c r="F2050" t="n">
         <v>1.550349241517218</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.986360702589605</v>
+        <v>-3.991690077878834</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.060026929122062</v>
+        <v>2.05789517900637</v>
       </c>
       <c r="F2051" t="n">
         <v>1.703374633630502</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.014668016462875</v>
+        <v>-4.019997391752104</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.236170228481047</v>
+        <v>2.234038478365355</v>
       </c>
       <c r="F2052" t="n">
         <v>1.703374633630502</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.181261241576397</v>
+        <v>-4.186590616865626</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.13893588978972</v>
+        <v>2.136804139674029</v>
       </c>
       <c r="F2053" t="n">
         <v>1.536781408516979</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.158225448214831</v>
+        <v>-4.16355482350406</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.151826609796065</v>
+        <v>2.149694859680373</v>
       </c>
       <c r="F2054" t="n">
         <v>1.536781408516979</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.128979467759135</v>
+        <v>-4.134308843048363</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.161143057101838</v>
+        <v>2.159011306986147</v>
       </c>
       <c r="F2055" t="n">
         <v>1.536781408516979</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.235905015636986</v>
+        <v>-4.241234390926214</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.115666077108333</v>
+        <v>2.113534326992641</v>
       </c>
       <c r="F2056" t="n">
         <v>1.429855860639128</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.380923574144235</v>
+        <v>-4.386252949433463</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.059087455848668</v>
+        <v>2.056955705732976</v>
       </c>
       <c r="F2057" t="n">
         <v>1.284837302131879</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.499265339928952</v>
+        <v>-4.504594715218181</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.111681988792534</v>
+        <v>2.109550238676842</v>
       </c>
       <c r="F2058" t="n">
         <v>1.295523340694769</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.523883824955894</v>
+        <v>-4.556005137538889</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099620291907696</v>
+        <v>2.086771766874498</v>
       </c>
       <c r="F2059" t="n">
         <v>1.295523340694769</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603303276163646</v>
+        <v>-4.63542458874664</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067755639498884</v>
+        <v>2.054907114465687</v>
       </c>
       <c r="F2060" t="n">
         <v>1.295523340694769</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.698766274080864</v>
+        <v>-4.730887586663858</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.02956433389004</v>
+        <v>2.016715808856842</v>
       </c>
       <c r="F2061" t="n">
         <v>1.295523340694769</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.634390363230149</v>
+        <v>-4.666511675813143</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053411094792937</v>
+        <v>2.040562569759739</v>
       </c>
       <c r="F2062" t="n">
         <v>1.359899251545485</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.689759525362343</v>
+        <v>-4.721880837945337</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036997247687786</v>
+        <v>2.024148722654588</v>
       </c>
       <c r="F2063" t="n">
         <v>1.359899251545485</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.73519730519317</v>
+        <v>-4.767318617776164</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.018360499098387</v>
+        <v>2.00551197406519</v>
       </c>
       <c r="F2064" t="n">
         <v>1.317054260867325</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.646990471045592</v>
+        <v>-4.679111783628586</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.073517625607737</v>
+        <v>2.06066910057454</v>
       </c>
       <c r="F2065" t="n">
         <v>1.317054260867325</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.540955475840282</v>
+        <v>-4.573076788423276</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.099632324214589</v>
+        <v>2.086783799181391</v>
       </c>
       <c r="F2066" t="n">
         <v>1.317054260867325</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.357743812707187</v>
+        <v>-4.389865125290181</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.175347938931873</v>
+        <v>2.162499413898675</v>
       </c>
       <c r="F2067" t="n">
         <v>1.317054260867325</v>
@@ -49115,10 +49115,10 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.286022365693336</v>
+        <v>-4.31814367827633</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.169827703585303</v>
+        <v>2.156979178552105</v>
       </c>
       <c r="F2068" t="n">
         <v>1.388775707881176</v>
@@ -49138,10 +49138,10 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.26364934008563</v>
+        <v>-4.295770652668624</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.125692659749557</v>
+        <v>2.112844134716359</v>
       </c>
       <c r="F2069" t="n">
         <v>1.400031458994077</v>
@@ -49161,10 +49161,10 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.296665635996375</v>
+        <v>-4.328786948579369</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.297684346270614</v>
+        <v>2.284835821237416</v>
       </c>
       <c r="F2070" t="n">
         <v>1.330594082327326</v>
@@ -49184,10 +49184,10 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.285138000346766</v>
+        <v>-4.31725931292976</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.294216626358707</v>
+        <v>2.281368101325509</v>
       </c>
       <c r="F2071" t="n">
         <v>1.389594740528688</v>
@@ -49207,10 +49207,10 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.382479501689135</v>
+        <v>-4.414600814272129</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258948138343547</v>
+        <v>2.24609961331035</v>
       </c>
       <c r="F2072" t="n">
         <v>1.3451745583632</v>
@@ -49230,10 +49230,10 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.468335531029101</v>
+        <v>-4.500456843612096</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.225856808800399</v>
+        <v>2.213008283767202</v>
       </c>
       <c r="F2073" t="n">
         <v>1.302798489137065</v>
@@ -49253,10 +49253,10 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.477172328445221</v>
+        <v>-4.509293641028215</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.204741291654453</v>
+        <v>2.191892766621256</v>
       </c>
       <c r="F2074" t="n">
         <v>1.295356316495714</v>
@@ -49276,10 +49276,10 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.568554891010679</v>
+        <v>-4.600676203593673</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.178352777673319</v>
+        <v>2.165504252640122</v>
       </c>
       <c r="F2075" t="n">
         <v>1.258791431776369</v>
@@ -49299,10 +49299,10 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.556848173023673</v>
+        <v>-4.588969485606667</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.285163722692389</v>
+        <v>2.272315197659191</v>
       </c>
       <c r="F2076" t="n">
         <v>1.270498149763376</v>
@@ -49322,10 +49322,10 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.457184668940011</v>
+        <v>-4.489305981523005</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.328061463057259</v>
+        <v>2.315212938024061</v>
       </c>
       <c r="F2077" t="n">
         <v>1.333685232967062</v>
@@ -49345,10 +49345,10 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.467500767106363</v>
+        <v>-4.499622079689357</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.536839857068776</v>
+        <v>2.523991332035578</v>
       </c>
       <c r="F2078" t="n">
         <v>1.333685232967062</v>
@@ -49368,10 +49368,10 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.46740679908899</v>
+        <v>-4.499528111671984</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.536056111187815</v>
+        <v>2.523207586154617</v>
       </c>
       <c r="F2079" t="n">
         <v>1.33405509431438</v>
@@ -49391,10 +49391,10 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.474625623288834</v>
+        <v>-4.506746935871829</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.527400567452231</v>
+        <v>2.514552042419033</v>
       </c>
       <c r="F2080" t="n">
         <v>1.33405509431438</v>
@@ -49414,10 +49414,10 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.473677200170796</v>
+        <v>-4.50579851275379</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.527779936699447</v>
+        <v>2.514931411666248</v>
       </c>
       <c r="F2081" t="n">
         <v>1.33405509431438</v>
@@ -49437,10 +49437,10 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.63074565842642</v>
+        <v>-4.662866971009414</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.477680161378289</v>
+        <v>2.464831636345091</v>
       </c>
       <c r="F2082" t="n">
         <v>1.33405509431438</v>
@@ -49460,10 +49460,10 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.624753411637609</v>
+        <v>-4.656874724220603</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.482023058518201</v>
+        <v>2.469174533485003</v>
       </c>
       <c r="F2083" t="n">
         <v>1.33405509431438</v>
@@ -49483,10 +49483,10 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.536195450506841</v>
+        <v>-4.568316763089835</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.511100378988277</v>
+        <v>2.498251853955079</v>
       </c>
       <c r="F2084" t="n">
         <v>1.33405509431438</v>
@@ -49506,10 +49506,10 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.518436373003767</v>
+        <v>-4.550557685586761</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.517512687428503</v>
+        <v>2.504664162395304</v>
       </c>
       <c r="F2085" t="n">
         <v>1.33405509431438</v>
@@ -49529,10 +49529,10 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.418806221954699</v>
+        <v>-4.450927534537693</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.570146933756716</v>
+        <v>2.557298408723518</v>
       </c>
       <c r="F2086" t="n">
         <v>1.433685245363448</v>
@@ -49552,10 +49552,10 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.46820573064371</v>
+        <v>-4.500327043226704</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.739541395779838</v>
+        <v>2.72669287074664</v>
       </c>
       <c r="F2087" t="n">
         <v>1.443944078795193</v>
@@ -49575,10 +49575,10 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.261521257001334</v>
+        <v>-4.293642569584328</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.809403858339651</v>
+        <v>2.796555333306453</v>
       </c>
       <c r="F2088" t="n">
         <v>1.650628552437568</v>
@@ -49598,10 +49598,10 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.29567815199886</v>
+        <v>-4.327799464581854</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.797742613994745</v>
+        <v>2.784894088961547</v>
       </c>
       <c r="F2089" t="n">
         <v>1.567044782896756</v>
@@ -49621,10 +49621,10 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.243603441986565</v>
+        <v>-4.235209985520398</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.172069611989331</v>
+        <v>3.175426994575798</v>
       </c>
       <c r="F2090" t="n">
         <v>1.567044782896756</v>
@@ -49644,10 +49644,10 @@
         <v>4.885557212133674</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.243603441986565</v>
+        <v>-4.235209985520398</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.172069611989331</v>
+        <v>3.175426994575798</v>
       </c>
       <c r="F2091" t="n">
         <v>1.567044782896756</v>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>176.9%</t>
+          <t>192.6%</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>421.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.1%</t>
+          <t>-586.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-58.7%</t>
+          <t>-60.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.4%</t>
+          <t>-321.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-67.3%</t>
+          <t>-74.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,21 +1433,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298395</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49181,19 +49181,19 @@
         <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.994037895045775</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.31725931292976</v>
+        <v>-4.352605278134021</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.281368101325509</v>
+        <v>2.252639359478418</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.389594740528688</v>
+        <v>1.31421286542973</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.842385095128374</v>
+        <v>4.782565614303613</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.997706007567563</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.414600814272129</v>
+        <v>-4.44994677947639</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.24609961331035</v>
+        <v>2.21737087146326</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.3451745583632</v>
+        <v>1.269792683264242</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.81940109835087</v>
+        <v>4.759581617526109</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.998957089760402</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.500456843612096</v>
+        <v>-4.535802808816356</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.213008283767202</v>
+        <v>2.184279541920111</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.302798489137065</v>
+        <v>1.227416614038107</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.795226539008027</v>
+        <v>4.735407058183266</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.981376291580903</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.509293641028215</v>
+        <v>-4.544639606232476</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.191892766621256</v>
+        <v>2.163164024774165</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.295356316495714</v>
+        <v>1.219974441396756</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.773180437243719</v>
+        <v>4.713360956418957</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.991540802625953</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.600676203593673</v>
+        <v>-4.636022168797934</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.165504252640122</v>
+        <v>2.136775510793031</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.258791431776369</v>
+        <v>1.183409556677411</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.761406017457161</v>
+        <v>4.7015865366324</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.093669060450221</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.588969485606667</v>
+        <v>-4.624315450810928</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.272315197659191</v>
+        <v>2.243586455812101</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.270498149763376</v>
+        <v>1.195116274664418</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.870558306073632</v>
+        <v>4.810738825248873</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.096701399181626</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.489305981523005</v>
+        <v>-4.524651946727266</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.315212938024061</v>
+        <v>2.286484196176971</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.333685232967062</v>
+        <v>1.258303357868104</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.911502894727249</v>
+        <v>4.851683413902489</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.309606232459684</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.499622079689357</v>
+        <v>-4.534968044893618</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.523991332035578</v>
+        <v>2.495262590188489</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.333685232967062</v>
+        <v>1.258303357868104</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.124407728005307</v>
+        <v>5.064588247180547</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.308784899371774</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.499528111671984</v>
+        <v>-4.534874076876245</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.523207586154617</v>
+        <v>2.494478844307528</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.123808311725787</v>
+        <v>5.063988830901027</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.303016885316127</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.506746935871829</v>
+        <v>-4.54209290107609</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.514552042419033</v>
+        <v>2.485823300571944</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.118040297670142</v>
+        <v>5.058220816845381</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.303016885316127</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.50579851275379</v>
+        <v>-4.541144477958051</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.514931411666248</v>
+        <v>2.486202669819159</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.118040297670142</v>
+        <v>5.058220816845381</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.31574449329722</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.662866971009414</v>
+        <v>-4.698212936213675</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.464831636345091</v>
+        <v>2.436102894498001</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.130767905651233</v>
+        <v>5.070948424826473</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.317690491721607</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.656874724220603</v>
+        <v>-4.692220689424864</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.469174533485003</v>
+        <v>2.440445791637914</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.13271390407562</v>
+        <v>5.072894423250861</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.311344627739376</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.568316763089835</v>
+        <v>-4.603662728294096</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.498251853955079</v>
+        <v>2.46952311210799</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.126368040093389</v>
+        <v>5.06654855926863</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.310653305178372</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.550557685586761</v>
+        <v>-4.585903650791022</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.504664162395304</v>
+        <v>2.475935420548215</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.33405509431438</v>
+        <v>1.258673219215422</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.125676717532386</v>
+        <v>5.065857236707625</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.323435491086959</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.450927534537693</v>
+        <v>-4.486273499741954</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.557298408723518</v>
+        <v>2.528569666876429</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.433685245363448</v>
+        <v>1.35830337026449</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.198236994070413</v>
+        <v>5.138417513245653</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.512589756585685</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.500327043226704</v>
+        <v>-4.535673008430965</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.72669287074664</v>
+        <v>2.697964128899551</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.443944078795193</v>
+        <v>1.368562203696235</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.393546559628186</v>
+        <v>5.333727078803426</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.499778429688547</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.293642569584328</v>
+        <v>-4.328988534788589</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.796555333306453</v>
+        <v>2.767826591459364</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.650628552437568</v>
+        <v>1.57524667733861</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.504745916916473</v>
+        <v>5.444926436091714</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.501779943342652</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.327799464581854</v>
+        <v>-4.363145429786115</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.784894088961547</v>
+        <v>2.756165347114458</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.567044782896756</v>
+        <v>1.491662907797798</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.456597168846091</v>
+        <v>5.396777688021331</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652383</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.855277057332319</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.235209985520398</v>
+        <v>-4.250771234678751</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.175426994575798</v>
+        <v>3.154612139147071</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.567044782896756</v>
+        <v>1.491662907797798</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.810094282835759</v>
+        <v>5.750274802010998</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.758104326857142</v>
+        <v>3.856261160438367</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.885557212133674</v>
+        <v>5.04239305379174</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.235209985520398</v>
+        <v>-4.250771234678751</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.175426994575798</v>
+        <v>3.154612139147071</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.567044782896756</v>
+        <v>1.491662907797798</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.878621009120041</v>
+        <v>5.035456850778107</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>192.6%</t>
+          <t>175.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.9%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.6%</t>
+          <t>-585.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-60.8%</t>
+          <t>-58.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.6%</t>
+          <t>-321.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-69.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>132.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>121.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>134.4%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.649643735309048</v>
+        <v>-3.626936104842089</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9930424371442095</v>
+        <v>1.002125489330993</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6932024866821638</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.605270603670479</v>
+        <v>-3.582562973203521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.010654557235073</v>
+        <v>1.019737609421857</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7375756183207324</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.627750954529364</v>
+        <v>-3.605043324062406</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9960562110301097</v>
+        <v>1.005139263216893</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7375756183207324</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.580095223968309</v>
+        <v>-3.55738759350135</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.021500260282337</v>
+        <v>1.03058331246912</v>
       </c>
       <c r="F1978" t="n">
         <v>0.785231348881788</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.479577065469554</v>
+        <v>-3.456869435002595</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.066599897056563</v>
+        <v>1.075682949243347</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8857495073805426</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.463671736037202</v>
+        <v>-3.440964105570242</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.059716701305377</v>
+        <v>1.06879975349216</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8066368466713036</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.418833334428804</v>
+        <v>-3.396125703961844</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.081749764559364</v>
+        <v>1.090832816746148</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8111802796161731</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.438331790670812</v>
+        <v>-3.415624160203853</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.078111321693639</v>
+        <v>1.087194373880423</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7630956383362688</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.394128953584911</v>
+        <v>-3.371421323117952</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.101672059055836</v>
+        <v>1.11075511124262</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8072984754221693</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.401688619421958</v>
+        <v>-3.378980988954999</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.097058193190265</v>
+        <v>1.106141245377049</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8621018794319886</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.243397201882686</v>
+        <v>-3.220689571415727</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.211622525389014</v>
+        <v>1.220705577575797</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8621018794319886</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.03575519824821</v>
+        <v>-3.013047567781251</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.293120031437057</v>
+        <v>1.302203083623841</v>
       </c>
       <c r="F1986" t="n">
         <v>1.069743883066465</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.984723105525682</v>
+        <v>-2.962015475058723</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.308481096764339</v>
+        <v>1.317564148951122</v>
       </c>
       <c r="F1987" t="n">
         <v>1.120775975788993</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.919498924398476</v>
+        <v>-2.896791293931517</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.351758173307926</v>
+        <v>1.36084122549471</v>
       </c>
       <c r="F1988" t="n">
         <v>1.186000156916198</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.882071904327342</v>
+        <v>-2.859364273860383</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.36268995363566</v>
+        <v>1.371773005822443</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19125169494538</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.880713919353797</v>
+        <v>-2.858006288886838</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.364489939956318</v>
+        <v>1.373572992143102</v>
       </c>
       <c r="F1990" t="n">
         <v>1.265589820483199</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.852300656253913</v>
+        <v>-2.829593025786954</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.536413016217482</v>
+        <v>1.545496068404266</v>
       </c>
       <c r="F1991" t="n">
         <v>1.20661425773677</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.7775183952289</v>
+        <v>-2.754810764761941</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.686438829845305</v>
+        <v>1.695521882032088</v>
       </c>
       <c r="F1992" t="n">
         <v>1.281396518761783</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.751434310965093</v>
+        <v>-2.787938832194419</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.688580439564687</v>
+        <v>1.673978631072956</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.663556397855972</v>
+        <v>-2.700060919085299</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.721924800392115</v>
+        <v>1.707322991900384</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.654663936462689</v>
+        <v>-2.691168457692015</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743036190676219</v>
+        <v>1.728434382184489</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.823140053432567</v>
+        <v>-2.859644574661893</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.667500791292852</v>
+        <v>1.652898982801121</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.376883860803127</v>
+        <v>-2.413388382032453</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.82727296553249</v>
+        <v>1.812671157040759</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.354162757119974</v>
+        <v>-2.390667278349301</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827025429502655</v>
+        <v>1.812423621010925</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.483364570414017</v>
+        <v>-2.519869091643343</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934250830036207</v>
+        <v>1.919649021544477</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.509238968888043</v>
+        <v>-2.545743490117369</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.960978893140243</v>
+        <v>1.946377084648513</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.502184278672869</v>
+        <v>-2.603733539886271</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.960476125215858</v>
+        <v>1.919856420730497</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.197420141431793</v>
+        <v>1.132375401447716</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.641131501867384</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.475233054346381</v>
+        <v>-2.576782315559783</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981262768591195</v>
+        <v>1.940643064105834</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.212300487459512</v>
+        <v>1.147255747475435</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.660065863128757</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.496777282177168</v>
+        <v>-2.59832654339057</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.15674820960384</v>
+        <v>2.116128505118479</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.212300487459512</v>
+        <v>1.147255747475435</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.844168995273717</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.51918539998204</v>
+        <v>-2.620734661195443</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.139901657384884</v>
+        <v>2.099281952899523</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.212300487459512</v>
+        <v>1.147255747475435</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.83628569017671</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.547409635559641</v>
+        <v>-2.648958896773043</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.130665962703481</v>
+        <v>2.090046258218121</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.230277239910821</v>
+        <v>1.165232499926744</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.849125741197132</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.55685056144817</v>
+        <v>-2.658399822661573</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183143310069917</v>
+        <v>2.142523605584556</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.352704357454212</v>
+        <v>1.287659617470136</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>3.978835729445015</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.645727192616644</v>
+        <v>-2.747276453830047</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.150483752147828</v>
+        <v>2.109864047662467</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>1.198782986301662</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.928400845289231</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.72205717021755</v>
+        <v>-2.823606431430953</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.118063574001241</v>
+        <v>2.077443869515879</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>1.198782986301662</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.926512658183006</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.815721114895092</v>
+        <v>-2.917270376108494</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.075418225733086</v>
+        <v>2.034798521247725</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.170163781608197</v>
+        <v>1.10511904162412</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.904161364969789</v>
+        <v>3.865134520979344</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.977289540422347</v>
+        <v>-3.078838801635749</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.009224865732337</v>
+        <v>1.968605161246976</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.043380857810317</v>
+        <v>0.978336117826241</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.826525620901214</v>
+        <v>3.787498776910768</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.085590202292466</v>
+        <v>-3.187139463505869</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.978978007850207</v>
+        <v>1.938358303364847</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.043380857810317</v>
+        <v>0.978336117826241</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.839599027767133</v>
+        <v>3.800572183776687</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.10339417401321</v>
+        <v>-3.204943435226613</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.96386161594485</v>
+        <v>1.923241911459489</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9728462349051163</v>
+        <v>0.9078014949210398</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.789283450806952</v>
+        <v>3.750256606816506</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.131294961122683</v>
+        <v>-3.232844222336086</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.951225342228063</v>
+        <v>1.910605637742702</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9382493107621815</v>
+        <v>0.873204570778105</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.767049337448193</v>
+        <v>3.728022493457747</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.253821063825577</v>
+        <v>-3.355370325038979</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.898979345124104</v>
+        <v>1.858359640638743</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8157232080592877</v>
+        <v>0.7506784680752111</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.690298119803656</v>
+        <v>3.65127127581321</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.484335560011166</v>
+        <v>-3.585884821224568</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.873479506240372</v>
+        <v>1.832859801755011</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5852087118736989</v>
+        <v>0.5201639718896224</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.618695381682806</v>
+        <v>3.57966853769236</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.83308064523561</v>
+        <v>-3.934629906449012</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.874293191152442</v>
+        <v>1.833673486667081</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4114160179707246</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.693758328333314</v>
+        <v>3.654731484342868</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.98706706301175</v>
+        <v>-4.088616324225153</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.881678893187625</v>
+        <v>1.841059188702264</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4114160179707246</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.762738597478954</v>
+        <v>3.723711753488508</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.191666497874759</v>
+        <v>-4.293215759088161</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.785890321362543</v>
+        <v>1.745270616877182</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4114160179707246</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.748789799599075</v>
+        <v>3.709762955608629</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.444141651882483</v>
+        <v>-4.545690913095886</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.696770748814867</v>
+        <v>1.656151044329506</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4114160179707246</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.760660288654489</v>
+        <v>3.721633444664043</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.737037408361895</v>
+        <v>-4.838586669575298</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.580822980742046</v>
+        <v>1.540203276256685</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4764607579548011</v>
+        <v>0.4114160179707246</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.761870823173433</v>
+        <v>3.722843979182987</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.923701536496703</v>
+        <v>-5.025250797710106</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.510279071715444</v>
+        <v>1.469659367230083</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4497217871302412</v>
+        <v>0.3846770471461647</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.749949182906018</v>
+        <v>3.710922338915573</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.069722223410666</v>
+        <v>-5.171271484624068</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.446948649686048</v>
+        <v>1.406328945200688</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4406386953363843</v>
+        <v>0.3755939553523077</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.739577180565893</v>
+        <v>3.700550336575448</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.16143623252025</v>
+        <v>-5.262985493733654</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.572467102741259</v>
+        <v>1.531847398255898</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4406386953363843</v>
+        <v>0.3755939553523077</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.901781237264938</v>
+        <v>3.862754393274492</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.19308789158022</v>
+        <v>-5.294637152793623</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.554653077081085</v>
+        <v>1.514033372595724</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4354702380919441</v>
+        <v>0.3704254981078675</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.893526800882088</v>
+        <v>3.854499956891642</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.275022709849103</v>
+        <v>-5.376571971062506</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.532108567342023</v>
+        <v>1.491488862856662</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4255354925048639</v>
+        <v>0.3604907525207873</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.897795371098331</v>
+        <v>3.858768527107885</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.37699883209751</v>
+        <v>-5.478548093310914</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.500243756898562</v>
+        <v>1.459624052413201</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3235593702564563</v>
+        <v>0.2585146302723798</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.845535336205189</v>
+        <v>3.806508492214743</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.266992548620289</v>
+        <v>-5.368541809833692</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.536399157533626</v>
+        <v>1.495779453048265</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3467639421737315</v>
+        <v>0.281719202189655</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.851610966599729</v>
+        <v>3.812584122609283</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.123932972879363</v>
+        <v>-5.225482234092766</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.597872998551971</v>
+        <v>1.55725329406661</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3547773687637108</v>
+        <v>0.2897326287796342</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.860669033275691</v>
+        <v>3.821642189285245</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.822486247407525</v>
+        <v>-4.924035508620928</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.725712571623242</v>
+        <v>1.685092867137881</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6562240942355481</v>
+        <v>0.5911793542514715</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.04879795144133</v>
+        <v>4.009771107450883</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.847076491642709</v>
+        <v>-4.948625752856112</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.716847651681879</v>
+        <v>1.676227947196518</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6562240942355481</v>
+        <v>0.5911793542514715</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.04976912919404</v>
+        <v>4.010742285203594</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.796038115636189</v>
+        <v>-4.897587376849592</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.738105906464243</v>
+        <v>1.697486201978882</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6562240942355481</v>
+        <v>0.5911793542514715</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.050612033573795</v>
+        <v>4.011585189583349</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.754898820769558</v>
+        <v>-4.856448081982961</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.773599723285041</v>
+        <v>1.732980018799679</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6973633891021789</v>
+        <v>0.6323186491181023</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.09433370936792</v>
+        <v>4.055306865377474</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.658263908750918</v>
+        <v>-4.759813169964321</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.628437684216431</v>
+        <v>1.58781797973107</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7939983011208188</v>
+        <v>0.7289535611367423</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.968498652703038</v>
+        <v>3.929471808712592</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.58922589780245</v>
+        <v>-4.690775159015853</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.659554932669782</v>
+        <v>1.618935228184421</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8630363120692869</v>
+        <v>0.7979915720852103</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.013423503346083</v>
+        <v>3.974396659355637</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.424729563611488</v>
+        <v>-4.526278824824892</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.70978028542225</v>
+        <v>1.669160580936889</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.027532646260249</v>
+        <v>0.9624879062761722</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.096548122936743</v>
+        <v>4.057521278946297</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.347630962069616</v>
+        <v>-4.449180223283019</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.739807436475429</v>
+        <v>1.699187731990067</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.027532646260249</v>
+        <v>0.9624879062761722</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.095735833373173</v>
+        <v>4.056708989382726</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.358016156959505</v>
+        <v>-4.459565418172908</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.745522137644545</v>
+        <v>1.704902433159184</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.017147451370359</v>
+        <v>0.9521027113862829</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.099373495564311</v>
+        <v>4.060346651573865</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.37660431568173</v>
+        <v>-4.478153576895133</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.80892387993208</v>
+        <v>1.768304175446719</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9985592926481339</v>
+        <v>0.9335145526640576</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.159057606107401</v>
+        <v>4.120030762116955</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.376902862377766</v>
+        <v>-4.478452123591169</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.805673472071964</v>
+        <v>1.765053767586603</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.998260745952098</v>
+        <v>0.9332160059680217</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.155747488908078</v>
+        <v>4.116720644917632</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.276079728687338</v>
+        <v>-4.377628989900741</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.850533620487527</v>
+        <v>1.809913916002166</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.010724961436452</v>
+        <v>0.9456802214523755</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.167756913138081</v>
+        <v>4.128730069147636</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.08529836793493</v>
+        <v>-4.186847629148334</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.926975418267034</v>
+        <v>1.886355713781672</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.201506322188859</v>
+        <v>1.136461582204783</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.282354983068069</v>
+        <v>4.243328139077623</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.978335010085509</v>
+        <v>-4.079884271298912</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.949597607144399</v>
+        <v>1.908977902659037</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.259970930148661</v>
+        <v>1.194926190164584</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.297270593581547</v>
+        <v>4.258243749591101</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.923004422183747</v>
+        <v>-4.02455368339715</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.006696778917162</v>
+        <v>1.966077074431801</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.315301518050423</v>
+        <v>1.250256778066346</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.365435882934663</v>
+        <v>4.326409038944217</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.910950295270784</v>
+        <v>-4.012499556484187</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.005204997583784</v>
+        <v>1.964585293098423</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.327355644963386</v>
+        <v>1.262310904979309</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.366354926983878</v>
+        <v>4.327328082993432</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.952105414839005</v>
+        <v>-4.053654676052408</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.990623579940632</v>
+        <v>1.950003875455271</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.286200525395165</v>
+        <v>1.221155785411088</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.343542485427081</v>
+        <v>4.304515641436636</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.884056852147475</v>
+        <v>-3.985606113360878</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.030694030895127</v>
+        <v>1.990074326409766</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.354249088086695</v>
+        <v>1.289204348102618</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.397222648919882</v>
+        <v>4.358195804929435</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.115657245316976</v>
+        <v>-4.217206506530379</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.95825654380092</v>
+        <v>1.917636839315559</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.354249088086695</v>
+        <v>1.289204348102618</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.417425319093476</v>
+        <v>4.37839847510303</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.165708790846196</v>
+        <v>-4.267258052059598</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.921842161656115</v>
+        <v>1.881222457170754</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.354249088086695</v>
+        <v>1.289204348102618</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.401031555160358</v>
+        <v>4.362004711169912</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.340815623422641</v>
+        <v>-4.442364884636042</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.812051342219003</v>
+        <v>1.771431637733643</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.354249088086695</v>
+        <v>1.289204348102618</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.361283468753824</v>
+        <v>4.322256624763378</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.144715469992118</v>
+        <v>-4.246264731205519</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.897514022588152</v>
+        <v>1.856894318102792</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.550349241517218</v>
+        <v>1.485304501533141</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.485966179809078</v>
+        <v>4.446939335818632</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.991690077878834</v>
+        <v>-4.093239339092235</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.05789517900637</v>
+        <v>2.01727547452101</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.703374633630502</v>
+        <v>1.638329893646425</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.676952414649953</v>
+        <v>4.637925570659507</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.019997391752104</v>
+        <v>-4.121546652965505</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.234038478365355</v>
+        <v>2.193418773879994</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.703374633630502</v>
+        <v>1.638329893646425</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.864418639558245</v>
+        <v>4.8253917955678</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.186590616865626</v>
+        <v>-4.288139878079027</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.136804139674029</v>
+        <v>2.096184435188668</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.536781408516979</v>
+        <v>1.471736668532903</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.733865655844215</v>
+        <v>4.694838811853769</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.16355482350406</v>
+        <v>-4.265104084717461</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.149694859680373</v>
+        <v>2.109075155195012</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.536781408516979</v>
+        <v>1.471736668532903</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.737542058505933</v>
+        <v>4.698515214515487</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.134308843048363</v>
+        <v>-4.235858104261765</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.159011306986147</v>
+        <v>2.118391602500786</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.536781408516979</v>
+        <v>1.471736668532903</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.735160113629428</v>
+        <v>4.696133269638982</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.241234390926214</v>
+        <v>-4.342783652139616</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.113534326992641</v>
+        <v>2.072914622507281</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.429855860639128</v>
+        <v>1.364811120655051</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.668298024060352</v>
+        <v>4.629271180069907</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.386252949433463</v>
+        <v>-4.487802210646865</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.056955705732976</v>
+        <v>2.016336001247616</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.284837302131879</v>
+        <v>1.219792562147803</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.582715691099237</v>
+        <v>4.543688847108792</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.504594715218181</v>
+        <v>-4.606143976431582</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.109550238676842</v>
+        <v>2.068930534191482</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.295523340694769</v>
+        <v>1.230478600710693</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.689058553494724</v>
+        <v>4.650031709504279</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.556005137538889</v>
+        <v>-4.65755439875229</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.086771766874498</v>
+        <v>2.046152062389138</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.295523340694769</v>
+        <v>1.230478600710693</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.686844250620664</v>
+        <v>4.647817406630217</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.63542458874664</v>
+        <v>-4.736973849960042</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.054907114465687</v>
+        <v>2.014287409980326</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.295523340694769</v>
+        <v>1.230478600710693</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.686747378694952</v>
+        <v>4.647720534704507</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298395</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.730887586663858</v>
+        <v>-4.832436847877259</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.016715808856842</v>
+        <v>1.976096104371482</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.295523340694769</v>
+        <v>1.230478600710693</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.686741272252996</v>
+        <v>4.64771442826255</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.666511675813143</v>
+        <v>-4.768060937026545</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.040562569759739</v>
+        <v>1.999942865274378</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.359899251545485</v>
+        <v>1.294854511561408</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.723463215326035</v>
+        <v>4.68443637133559</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.721880837945337</v>
+        <v>-4.823430099158738</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.024148722654588</v>
+        <v>1.983529018169228</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.359899251545485</v>
+        <v>1.294854511561408</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.729197033073762</v>
+        <v>4.690170189083316</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.767318617776164</v>
+        <v>-4.868867878989565</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.00551197406519</v>
+        <v>1.964892269579829</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.317054260867325</v>
+        <v>1.252009520883248</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.703028402009799</v>
+        <v>4.664001558019352</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.679111783628586</v>
+        <v>-4.780661044841987</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.06066910057454</v>
+        <v>2.020049396089179</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.317054260867325</v>
+        <v>1.252009520883248</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.722902794860118</v>
+        <v>4.683875950869671</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.573076788423276</v>
+        <v>-4.674626049636678</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.086783799181391</v>
+        <v>2.046164094696031</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.317054260867325</v>
+        <v>1.252009520883248</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.706603495384845</v>
+        <v>4.667576651394399</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.389865125290181</v>
+        <v>-4.491414386503583</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.162499413898675</v>
+        <v>2.121879709413315</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.317054260867325</v>
+        <v>1.252009520883248</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.709034444848891</v>
+        <v>4.670007600858445</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.31814367827633</v>
+        <v>-4.419692939489732</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.156979178552105</v>
+        <v>2.116359474066745</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.388775707881176</v>
+        <v>1.323730967897099</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.717858498905091</v>
+        <v>4.678831654914645</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.295770652668624</v>
+        <v>-4.397319913882026</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.112844134716359</v>
+        <v>2.072224430230999</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.400031458994077</v>
+        <v>1.334986719010001</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.671527695494003</v>
+        <v>4.632500851503558</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.328786948579369</v>
+        <v>-4.43033620979277</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.284835821237416</v>
+        <v>2.244216116752056</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.330594082327326</v>
+        <v>1.265549342343249</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.815063474379308</v>
+        <v>4.776036630388862</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.994037895045775</v>
+        <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.352605278134021</v>
+        <v>-4.418808574143162</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.252639359478418</v>
+        <v>2.240748396840148</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.31421286542973</v>
+        <v>1.324550000544612</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.782565614303613</v>
+        <v>4.803358251137928</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236293</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.997706007567563</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.44994677947639</v>
+        <v>-4.51615007548553</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.21737087146326</v>
+        <v>2.205479908824989</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.269792683264242</v>
+        <v>1.280129818379123</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.759581617526109</v>
+        <v>4.780374254360424</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.998957089760402</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.535802808816356</v>
+        <v>-4.602006104825497</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.184279541920111</v>
+        <v>2.172388579281841</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.227416614038107</v>
+        <v>1.237753749152988</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.735407058183266</v>
+        <v>4.756199695017581</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.981376291580903</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.544639606232476</v>
+        <v>-4.610842902241616</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.163164024774165</v>
+        <v>2.151273062135895</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.219974441396756</v>
+        <v>1.230311576511637</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.713360956418957</v>
+        <v>4.734153593253272</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.991540802625953</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.636022168797934</v>
+        <v>-4.702225464807075</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.136775510793031</v>
+        <v>2.124884548154761</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.183409556677411</v>
+        <v>1.193746691792293</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.7015865366324</v>
+        <v>4.722379173466715</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.093669060450221</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.624315450810928</v>
+        <v>-4.690518746820069</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.243586455812101</v>
+        <v>2.231695493173831</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.195116274664418</v>
+        <v>1.205453409779299</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.810738825248873</v>
+        <v>4.831531462083186</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.096701399181626</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.524651946727266</v>
+        <v>-4.590855242736406</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.286484196176971</v>
+        <v>2.274593233538701</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.258303357868104</v>
+        <v>1.268640492982986</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.851683413902489</v>
+        <v>4.872476050736803</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.309606232459684</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.534968044893618</v>
+        <v>-4.601171340902758</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.495262590188489</v>
+        <v>2.483371627550218</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.258303357868104</v>
+        <v>1.268640492982986</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.064588247180547</v>
+        <v>5.085380884014861</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.308784899371774</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.534874076876245</v>
+        <v>-4.601077372885386</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.494478844307528</v>
+        <v>2.482587881669256</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.063988830901027</v>
+        <v>5.084781467735342</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.303016885316127</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.54209290107609</v>
+        <v>-4.60829619708523</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.485823300571944</v>
+        <v>2.473932337933673</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.058220816845381</v>
+        <v>5.079013453679695</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.303016885316127</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.541144477958051</v>
+        <v>-4.607347773967192</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.486202669819159</v>
+        <v>2.474311707180888</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.058220816845381</v>
+        <v>5.079013453679695</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.31574449329722</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.698212936213675</v>
+        <v>-4.764416232222816</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.436102894498001</v>
+        <v>2.42421193185973</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.070948424826473</v>
+        <v>5.091741061660787</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.317690491721607</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.692220689424864</v>
+        <v>-4.758423985434004</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.440445791637914</v>
+        <v>2.428554828999643</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.072894423250861</v>
+        <v>5.093687060085175</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.311344627739376</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.603662728294096</v>
+        <v>-4.669866024303237</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.46952311210799</v>
+        <v>2.457632149469719</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.06654855926863</v>
+        <v>5.087341196102944</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.310653305178372</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.585903650791022</v>
+        <v>-4.652106946800163</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.475935420548215</v>
+        <v>2.464044457909944</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.258673219215422</v>
+        <v>1.269010354330304</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.065857236707625</v>
+        <v>5.08664987354194</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.323435491086959</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.486273499741954</v>
+        <v>-4.552476795751095</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.528569666876429</v>
+        <v>2.516678704238158</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.35830337026449</v>
+        <v>1.368640505379371</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.138417513245653</v>
+        <v>5.159210150079967</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.512589756585685</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.535673008430965</v>
+        <v>-4.601876304440106</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.697964128899551</v>
+        <v>2.68607316626128</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.368562203696235</v>
+        <v>1.378899338811116</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.333727078803426</v>
+        <v>5.35451971563774</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.499778429688547</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.328988534788589</v>
+        <v>-4.39519183079773</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.767826591459364</v>
+        <v>2.755935628821092</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.57524667733861</v>
+        <v>1.585583812453492</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.444926436091714</v>
+        <v>5.465719072926028</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.501779943342652</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.363145429786115</v>
+        <v>-4.429348725795256</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.756165347114458</v>
+        <v>2.744274384476187</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.491662907797798</v>
+        <v>1.502000042912679</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.396777688021331</v>
+        <v>5.417570324855645</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.855277057332319</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.250771234678751</v>
+        <v>-4.30205840901589</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.154612139147071</v>
+        <v>3.148687625177601</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.491662907797798</v>
+        <v>1.502000042912679</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.750274802010998</v>
+        <v>5.771067438845312</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.856261160438367</v>
+        <v>3.760899071527442</v>
       </c>
       <c r="C2091" t="n">
-        <v>5.04239305379174</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.250771234678751</v>
+        <v>-4.243014553469649</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.154612139147071</v>
+        <v>3.1768682789632</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.491662907797798</v>
+        <v>1.549590404358463</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.035456850778107</v>
+        <v>5.804184767279885</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240918.xlsx
+++ b/tame_output/ON/bt/strategyON_20240918.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>421.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.9%</t>
+          <t>-583.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-57.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-69.0%</t>
+          <t>-69.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>121.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>134.4%</t>
+          <t>134.2%</t>
         </is>
       </c>
     </row>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.787938832194419</v>
+        <v>-2.728726680498133</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.673978631072956</v>
+        <v>1.69766349175147</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.700060919085299</v>
+        <v>-2.640848767389013</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.707322991900384</v>
+        <v>1.731007852578898</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.691168457692015</v>
+        <v>-2.63195630599573</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.728434382184489</v>
+        <v>1.752119242863003</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.859644574661893</v>
+        <v>-2.800432422965608</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.652898982801121</v>
+        <v>1.676583843479636</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
@@ -47482,10 +47482,10 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.413388382032453</v>
+        <v>-2.354176230336168</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.812671157040759</v>
+        <v>1.836356017719273</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
@@ -47505,10 +47505,10 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.390667278349301</v>
+        <v>-2.331455126653015</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.812423621010925</v>
+        <v>1.836108481689439</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.519869091643343</v>
+        <v>-2.460656939947058</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.919649021544477</v>
+        <v>1.943333882222991</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
@@ -47551,10 +47551,10 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.545743490117369</v>
+        <v>-2.486531338421083</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.946377084648513</v>
+        <v>1.970061945327027</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.603733539886271</v>
+        <v>-2.547443340923047</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.919856420730497</v>
+        <v>1.942372500315787</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.132375401447716</v>
+        <v>1.129453448714655</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.641131501867384</v>
+        <v>3.639378330227547</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.576782315559783</v>
+        <v>-2.520492116596559</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.940643064105834</v>
+        <v>1.963159143691124</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.147255747475435</v>
+        <v>1.144333794742374</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.660065863128757</v>
+        <v>3.65831269148892</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.59832654339057</v>
+        <v>-2.542036344427347</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.116128505118479</v>
+        <v>2.138644584703768</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.147255747475435</v>
+        <v>1.144333794742374</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.844168995273717</v>
+        <v>3.84241582363388</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.620734661195443</v>
+        <v>-2.564444462232219</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.099281952899523</v>
+        <v>2.121798032484813</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.147255747475435</v>
+        <v>1.144333794742374</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.83628569017671</v>
+        <v>3.834532518536873</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.648958896773043</v>
+        <v>-2.592668697809819</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.090046258218121</v>
+        <v>2.11256233780341</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165232499926744</v>
+        <v>1.162310547193683</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.849125741197132</v>
+        <v>3.847372569557295</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.658399822661573</v>
+        <v>-2.602109623698349</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.142523605584556</v>
+        <v>2.165039685169845</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287659617470136</v>
+        <v>1.284737664737074</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.978835729445015</v>
+        <v>3.977082557805177</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.747276453830047</v>
+        <v>-2.690986254866823</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.109864047662467</v>
+        <v>2.132380127247757</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.198782986301662</v>
+        <v>1.1958610335686</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.928400845289231</v>
+        <v>3.926647673649394</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.823606431430953</v>
+        <v>-2.767316232467729</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.077443869515879</v>
+        <v>2.099959949101169</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.198782986301662</v>
+        <v>1.1958610335686</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.926512658183006</v>
+        <v>3.924759486543169</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.917270376108494</v>
+        <v>-2.86098017714527</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.034798521247725</v>
+        <v>2.057314600833015</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.10511904162412</v>
+        <v>1.102197088891059</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.865134520979344</v>
+        <v>3.863381349339507</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.078838801635749</v>
+        <v>-3.022548602672525</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.968605161246976</v>
+        <v>1.991121240832265</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.978336117826241</v>
+        <v>0.9754141650931795</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.787498776910768</v>
+        <v>3.785745605270932</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.187139463505869</v>
+        <v>-3.130849264542645</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.938358303364847</v>
+        <v>1.960874382950136</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.978336117826241</v>
+        <v>0.9754141650931795</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.800572183776687</v>
+        <v>3.79881901213685</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.204943435226613</v>
+        <v>-3.148653236263389</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.923241911459489</v>
+        <v>1.945757991044778</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9078014949210398</v>
+        <v>0.9048795421879783</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.750256606816506</v>
+        <v>3.748503435176669</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.232844222336086</v>
+        <v>-3.176554023372862</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.910605637742702</v>
+        <v>1.933121717327992</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.873204570778105</v>
+        <v>0.8702826180450435</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.728022493457747</v>
+        <v>3.72626932181791</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.355370325038979</v>
+        <v>-3.299080126075756</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.858359640638743</v>
+        <v>1.880875720224032</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7506784680752111</v>
+        <v>0.7477565153421496</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.65127127581321</v>
+        <v>3.649518104173373</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.585884821224568</v>
+        <v>-3.529594622261344</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.832859801755011</v>
+        <v>1.855375881340301</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5201639718896224</v>
+        <v>0.5172420191565609</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.57966853769236</v>
+        <v>3.577915366052523</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.934629906449012</v>
+        <v>-3.878339707485788</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.833673486667081</v>
+        <v>1.85618956625237</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4114160179707246</v>
+        <v>0.4084940652376631</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.654731484342868</v>
+        <v>3.652978312703032</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.088616324225153</v>
+        <v>-4.032326125261928</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.841059188702264</v>
+        <v>1.863575268287554</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4114160179707246</v>
+        <v>0.4084940652376631</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.723711753488508</v>
+        <v>3.721958581848671</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.293215759088161</v>
+        <v>-4.236925560124937</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.745270616877182</v>
+        <v>1.767786696462471</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4114160179707246</v>
+        <v>0.4084940652376631</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.709762955608629</v>
+        <v>3.708009783968792</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.545690913095886</v>
+        <v>-4.489400714132661</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.656151044329506</v>
+        <v>1.678667123914796</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4114160179707246</v>
+        <v>0.4084940652376631</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.721633444664043</v>
+        <v>3.719880273024206</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.838586669575298</v>
+        <v>-4.782296470612073</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.540203276256685</v>
+        <v>1.562719355841975</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4114160179707246</v>
+        <v>0.4084940652376631</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.722843979182987</v>
+        <v>3.72109080754315</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.025250797710106</v>
+        <v>-4.968960598746881</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.469659367230083</v>
+        <v>1.492175446815373</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3846770471461647</v>
+        <v>0.3817550944131032</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.710922338915573</v>
+        <v>3.709169167275736</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.171271484624068</v>
+        <v>-5.114981285660844</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.406328945200688</v>
+        <v>1.428845024785977</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3755939553523077</v>
+        <v>0.3726720026192462</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.700550336575448</v>
+        <v>3.698797164935611</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.262985493733654</v>
+        <v>-5.206695294770428</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.531847398255898</v>
+        <v>1.554363477841187</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3755939553523077</v>
+        <v>0.3726720026192462</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.862754393274492</v>
+        <v>3.861001221634655</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.294637152793623</v>
+        <v>-5.238346953830398</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.514033372595724</v>
+        <v>1.536549452181014</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3704254981078675</v>
+        <v>0.367503545374806</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.854499956891642</v>
+        <v>3.852746785251805</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.376571971062506</v>
+        <v>-5.320281772099281</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.491488862856662</v>
+        <v>1.514004942441952</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3604907525207873</v>
+        <v>0.3575687997877258</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.858768527107885</v>
+        <v>3.857015355468048</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.478548093310914</v>
+        <v>-5.422257894347688</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.459624052413201</v>
+        <v>1.482140131998491</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2585146302723798</v>
+        <v>0.2555926775393182</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.806508492214743</v>
+        <v>3.804755320574906</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.368541809833692</v>
+        <v>-5.312251610870467</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.495779453048265</v>
+        <v>1.518295532633555</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.281719202189655</v>
+        <v>0.2787972494565935</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.812584122609283</v>
+        <v>3.810830950969446</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.225482234092766</v>
+        <v>-5.169192035129541</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.55725329406661</v>
+        <v>1.5797693736519</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2897326287796342</v>
+        <v>0.2868106760465727</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.821642189285245</v>
+        <v>3.819889017645408</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.924035508620928</v>
+        <v>-4.867745309657703</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.685092867137881</v>
+        <v>1.707608946723171</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5911793542514715</v>
+        <v>0.58825740151841</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.009771107450883</v>
+        <v>4.008017935811046</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.948625752856112</v>
+        <v>-4.892335553892887</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.676227947196518</v>
+        <v>1.698744026781808</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5911793542514715</v>
+        <v>0.58825740151841</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.010742285203594</v>
+        <v>4.008989113563757</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.897587376849592</v>
+        <v>-4.841297177886367</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.697486201978882</v>
+        <v>1.720002281564172</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5911793542514715</v>
+        <v>0.58825740151841</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.011585189583349</v>
+        <v>4.009832017943513</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.856448081982961</v>
+        <v>-4.800157883019736</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.732980018799679</v>
+        <v>1.755496098384969</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6323186491181023</v>
+        <v>0.6293966963850408</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.055306865377474</v>
+        <v>4.053553693737636</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.759813169964321</v>
+        <v>-4.703522971001096</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.58781797973107</v>
+        <v>1.61033405931636</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7289535611367423</v>
+        <v>0.7260316084036808</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.929471808712592</v>
+        <v>3.927718637072755</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.690775159015853</v>
+        <v>-4.634484960052628</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.618935228184421</v>
+        <v>1.641451307769711</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7979915720852103</v>
+        <v>0.7950696193521488</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.974396659355637</v>
+        <v>3.9726434877158</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.526278824824892</v>
+        <v>-4.469988625861666</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.669160580936889</v>
+        <v>1.691676660522178</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9624879062761722</v>
+        <v>0.9595659535431107</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.057521278946297</v>
+        <v>4.055768107306459</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.449180223283019</v>
+        <v>-4.392890024319794</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.699187731990067</v>
+        <v>1.721703811575357</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9624879062761722</v>
+        <v>0.9595659535431107</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.056708989382726</v>
+        <v>4.05495581774289</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.459565418172908</v>
+        <v>-4.403275219209683</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.704902433159184</v>
+        <v>1.727418512744474</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9521027113862829</v>
+        <v>0.9491807586532214</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.060346651573865</v>
+        <v>4.058593479934029</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.478153576895133</v>
+        <v>-4.421863377931908</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.768304175446719</v>
+        <v>1.790820255032009</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9335145526640576</v>
+        <v>0.9305925999309961</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.120030762116955</v>
+        <v>4.118277590477119</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.478452123591169</v>
+        <v>-4.422161924627944</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.765053767586603</v>
+        <v>1.787569847171893</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9332160059680217</v>
+        <v>0.9302940532349602</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.116720644917632</v>
+        <v>4.114967473277796</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.377628989900741</v>
+        <v>-4.321338790937516</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.809913916002166</v>
+        <v>1.832429995587456</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9456802214523755</v>
+        <v>0.942758268719314</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.128730069147636</v>
+        <v>4.126976897507799</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.186847629148334</v>
+        <v>-4.130557430185108</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.886355713781672</v>
+        <v>1.908871793366962</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.136461582204783</v>
+        <v>1.133539629471721</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.243328139077623</v>
+        <v>4.241574967437787</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.079884271298912</v>
+        <v>-4.023594072335687</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.908977902659037</v>
+        <v>1.931493982244327</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.194926190164584</v>
+        <v>1.192004237431523</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.258243749591101</v>
+        <v>4.256490577951264</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.02455368339715</v>
+        <v>-3.968263484433925</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.966077074431801</v>
+        <v>1.98859315401709</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.250256778066346</v>
+        <v>1.247334825333285</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.326409038944217</v>
+        <v>4.324655867304379</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.012499556484187</v>
+        <v>-3.956209357520962</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.964585293098423</v>
+        <v>1.987101372683713</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.262310904979309</v>
+        <v>1.259388952246248</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.327328082993432</v>
+        <v>4.325574911353595</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.053654676052408</v>
+        <v>-3.997364477089183</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.950003875455271</v>
+        <v>1.972519955040561</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.221155785411088</v>
+        <v>1.218233832678027</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.304515641436636</v>
+        <v>4.302762469796798</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.985606113360878</v>
+        <v>-3.929315914397653</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.990074326409766</v>
+        <v>2.012590405995056</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.289204348102618</v>
+        <v>1.286282395369557</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.358195804929435</v>
+        <v>4.356442633289599</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.217206506530379</v>
+        <v>-4.160916307567154</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.917636839315559</v>
+        <v>1.940152918900849</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.289204348102618</v>
+        <v>1.286282395369557</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.37839847510303</v>
+        <v>4.376645303463193</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.267258052059598</v>
+        <v>-4.210967853096374</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.881222457170754</v>
+        <v>1.903738536756043</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.289204348102618</v>
+        <v>1.286282395369557</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.362004711169912</v>
+        <v>4.360251539530075</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.442364884636042</v>
+        <v>-4.386074685672819</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.771431637733643</v>
+        <v>1.793947717318932</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.289204348102618</v>
+        <v>1.286282395369557</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.322256624763378</v>
+        <v>4.320503453123542</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.246264731205519</v>
+        <v>-4.189974532242296</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.856894318102792</v>
+        <v>1.879410397688081</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.485304501533141</v>
+        <v>1.482382548800079</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.446939335818632</v>
+        <v>4.445186164178796</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.093239339092235</v>
+        <v>-4.036949140129011</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.01727547452101</v>
+        <v>2.0397915541063</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.638329893646425</v>
+        <v>1.635407940913364</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.637925570659507</v>
+        <v>4.63617239901967</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.121546652965505</v>
+        <v>-4.065256454002282</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.193418773879994</v>
+        <v>2.215934853465284</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.638329893646425</v>
+        <v>1.635407940913364</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.8253917955678</v>
+        <v>4.823638623927962</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.288139878079027</v>
+        <v>-4.231849679115804</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.096184435188668</v>
+        <v>2.118700514773958</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.471736668532903</v>
+        <v>1.468814715799841</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.694838811853769</v>
+        <v>4.693085640213932</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.265104084717461</v>
+        <v>-4.208813885754238</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.109075155195012</v>
+        <v>2.131591234780302</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.471736668532903</v>
+        <v>1.468814715799841</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.698515214515487</v>
+        <v>4.696762042875649</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.235858104261765</v>
+        <v>-4.179567905298541</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.118391602500786</v>
+        <v>2.140907682086076</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.471736668532903</v>
+        <v>1.468814715799841</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.696133269638982</v>
+        <v>4.694380097999145</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.342783652139616</v>
+        <v>-4.286493453176393</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.072914622507281</v>
+        <v>2.09543070209257</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.364811120655051</v>
+        <v>1.36188916792199</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.629271180069907</v>
+        <v>4.627518008430069</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.487802210646865</v>
+        <v>-4.431512011683641</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.016336001247616</v>
+        <v>2.038852080832905</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.219792562147803</v>
+        <v>1.216870609414741</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.543688847108792</v>
+        <v>4.541935675468954</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687011</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.606143976431582</v>
+        <v>-4.549853777468359</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068930534191482</v>
+        <v>2.091446613776771</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.230478600710693</v>
+        <v>1.227556647977631</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.650031709504279</v>
+        <v>4.648278537864441</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.65755439875229</v>
+        <v>-4.601264199789067</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.046152062389138</v>
+        <v>2.068668141974427</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.230478600710693</v>
+        <v>1.227556647977631</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.647817406630217</v>
+        <v>4.646064234990381</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.736973849960042</v>
+        <v>-4.680683650996818</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.014287409980326</v>
+        <v>2.036803489565616</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.230478600710693</v>
+        <v>1.227556647977631</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.647720534704507</v>
+        <v>4.64596736306467</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.832436847877259</v>
+        <v>-4.776146648914036</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.976096104371482</v>
+        <v>1.998612183956771</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.230478600710693</v>
+        <v>1.227556647977631</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.64771442826255</v>
+        <v>4.645961256622713</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.768060937026545</v>
+        <v>-4.711770738063321</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.999942865274378</v>
+        <v>2.022458944859668</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.294854511561408</v>
+        <v>1.291932558828347</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.68443637133559</v>
+        <v>4.682683199695752</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.823430099158738</v>
+        <v>-4.767139900195515</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.983529018169228</v>
+        <v>2.006045097754517</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.294854511561408</v>
+        <v>1.291932558828347</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.690170189083316</v>
+        <v>4.688417017443479</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.868867878989565</v>
+        <v>-4.812577680026342</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.964892269579829</v>
+        <v>1.987408349165118</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.252009520883248</v>
+        <v>1.249087568150187</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.664001558019352</v>
+        <v>4.662248386379516</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.780661044841987</v>
+        <v>-4.724370845878764</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.020049396089179</v>
+        <v>2.042565475674468</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.252009520883248</v>
+        <v>1.249087568150187</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.683875950869671</v>
+        <v>4.682122779229834</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.674626049636678</v>
+        <v>-4.618335850673454</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.046164094696031</v>
+        <v>2.06868017428132</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.252009520883248</v>
+        <v>1.249087568150187</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.667576651394399</v>
+        <v>4.665823479754562</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.491414386503583</v>
+        <v>-4.435124187540359</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.121879709413315</v>
+        <v>2.144395788998604</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.252009520883248</v>
+        <v>1.249087568150187</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.670007600858445</v>
+        <v>4.668254429218607</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.419692939489732</v>
+        <v>-4.363402740526508</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.116359474066745</v>
+        <v>2.138875553652034</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.323730967897099</v>
+        <v>1.320809015164038</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.678831654914645</v>
+        <v>4.677078483274808</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.397319913882026</v>
+        <v>-4.341029714918802</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.072224430230999</v>
+        <v>2.094740509816288</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.334986719010001</v>
+        <v>1.332064766276939</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.632500851503558</v>
+        <v>4.63074767986372</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.43033620979277</v>
+        <v>-4.374046010829547</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.244216116752056</v>
+        <v>2.266732196337345</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.265549342343249</v>
+        <v>1.262627389610188</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.776036630388862</v>
+        <v>4.774283458749025</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.418808574143162</v>
+        <v>-4.362518375179938</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.240748396840148</v>
+        <v>2.263264476425438</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.324550000544612</v>
+        <v>1.32162804781155</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.803358251137928</v>
+        <v>4.801605079498091</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236293</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.51615007548553</v>
+        <v>-4.459859876522307</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.205479908824989</v>
+        <v>2.227995988410279</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.280129818379123</v>
+        <v>1.277207865646062</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.780374254360424</v>
+        <v>4.778621082720587</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.602006104825497</v>
+        <v>-4.545715905862274</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.172388579281841</v>
+        <v>2.19490465886713</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.237753749152988</v>
+        <v>1.234831796419927</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.756199695017581</v>
+        <v>4.754446523377744</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.610842902241616</v>
+        <v>-4.554552703278393</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.151273062135895</v>
+        <v>2.173789141721184</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.230311576511637</v>
+        <v>1.227389623778576</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.734153593253272</v>
+        <v>4.732400421613436</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.702225464807075</v>
+        <v>-4.645935265843852</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.124884548154761</v>
+        <v>2.14740062774005</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.193746691792293</v>
+        <v>1.190824739059231</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.722379173466715</v>
+        <v>4.720626001826878</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.690518746820069</v>
+        <v>-4.634228547856845</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.231695493173831</v>
+        <v>2.25421157275912</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.205453409779299</v>
+        <v>1.202531457046238</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.831531462083186</v>
+        <v>4.829778290443349</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.590855242736406</v>
+        <v>-4.534565043773183</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.274593233538701</v>
+        <v>2.29710931312399</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.268640492982986</v>
+        <v>1.265718540249924</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.872476050736803</v>
+        <v>4.870722879096966</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.601171340902758</v>
+        <v>-4.544881141939535</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.483371627550218</v>
+        <v>2.505887707135507</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.268640492982986</v>
+        <v>1.265718540249924</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.085380884014861</v>
+        <v>5.083627712375024</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.601077372885386</v>
+        <v>-4.544787173922162</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.482587881669256</v>
+        <v>2.505103961254546</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.084781467735342</v>
+        <v>5.083028296095504</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.60829619708523</v>
+        <v>-4.552005998122007</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.473932337933673</v>
+        <v>2.496448417518962</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.079013453679695</v>
+        <v>5.077260282039858</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.607347773967192</v>
+        <v>-4.551057575003968</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.474311707180888</v>
+        <v>2.496827786766177</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.079013453679695</v>
+        <v>5.077260282039858</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.764416232222816</v>
+        <v>-4.708126033259592</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.42421193185973</v>
+        <v>2.44672801144502</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.091741061660787</v>
+        <v>5.08998789002095</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.758423985434004</v>
+        <v>-4.702133786470781</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.428554828999643</v>
+        <v>2.451070908584932</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.093687060085175</v>
+        <v>5.091933888445338</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.669866024303237</v>
+        <v>-4.613575825340013</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.457632149469719</v>
+        <v>2.480148229055008</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.087341196102944</v>
+        <v>5.085588024463107</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.652106946800163</v>
+        <v>-4.595816747836939</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.464044457909944</v>
+        <v>2.486560537495233</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.269010354330304</v>
+        <v>1.266088401597242</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.08664987354194</v>
+        <v>5.084896701902102</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.552476795751095</v>
+        <v>-4.496186596787871</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.516678704238158</v>
+        <v>2.539194783823447</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.368640505379371</v>
+        <v>1.36571855264631</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.159210150079967</v>
+        <v>5.15745697844013</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.601876304440106</v>
+        <v>-4.545586105476882</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.68607316626128</v>
+        <v>2.708589245846569</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.378899338811116</v>
+        <v>1.375977386078055</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.35451971563774</v>
+        <v>5.352766543997904</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.39519183079773</v>
+        <v>-4.338901631834506</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.755935628821092</v>
+        <v>2.778451708406382</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.585583812453492</v>
+        <v>1.58266185972043</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.465719072926028</v>
+        <v>5.463965901286191</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.429348725795256</v>
+        <v>-4.373058526832033</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.744274384476187</v>
+        <v>2.766790464061476</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.502000042912679</v>
+        <v>1.499078090179618</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.417570324855645</v>
+        <v>5.415817153215809</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.30205840901589</v>
+        <v>-4.280469047770576</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.148687625177601</v>
+        <v>3.157323369675726</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.502000042912679</v>
+        <v>1.499078090179618</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.771067438845312</v>
+        <v>5.769314267205475</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.760899071527442</v>
+        <v>3.760899071527444</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.243014553469649</v>
+        <v>-4.222203713444013</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.1768682789632</v>
+        <v>3.185192614973455</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.549590404358463</v>
+        <v>1.546209025074524</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.804184767279885</v>
+        <v>5.802155939709523</v>
       </c>
     </row>
   </sheetData>
